--- a/projects/finance-release/Operating_Plan.xlsx
+++ b/projects/finance-release/Operating_Plan.xlsx
@@ -2,15 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="Rd32d951c362845bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R08ce1fd075064a05"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail" sheetId="3" r:id="R62ec5c1b887642bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly" sheetId="4" r:id="Rfe3e2b4a641543ca"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance" sheetId="5" r:id="Rabde0e93cb1f4579"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source" sheetId="6" r:id="R1fa2a457998746f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="7" r:id="R5ecc36d749d74832"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="8" r:id="R6276fa1cddde4117"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="9" r:id="R382e21809cf44a70"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" r:id="R16667949a8574fe7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="2" r:id="R85f9ea5147e14e77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Detail" sheetId="3" r:id="R8cedccd88862437d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Monthly" sheetId="4" r:id="R317e98b23a854a43"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variance" sheetId="5" r:id="R04917137034e457c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Source" sheetId="6" r:id="Rf2498e57f0744c91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Review" sheetId="7" r:id="Re9159cddff634475"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Working Capital" sheetId="8" r:id="R8ca88b55ecb34b59"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Debt" sheetId="9" r:id="Re3240f59d8d64b31"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statements" sheetId="10" r:id="R95aa1d939d324307"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Actions" sheetId="11" r:id="R36b188617c2c4f87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Audit" sheetId="12" r:id="R8d05b9ed9a204804"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,12 +24,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="5">
+  <x:numFmts count="6">
     <x:numFmt numFmtId="200" formatCode="0.0%"/>
     <x:numFmt numFmtId="201" formatCode="mmm-yy"/>
     <x:numFmt numFmtId="202" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
     <x:numFmt numFmtId="203" formatCode="0.00"/>
     <x:numFmt numFmtId="204" formatCode="$#,##0;($#,##0);&quot;-&quot;"/>
+    <x:numFmt numFmtId="205" formatCode="0"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -105,7 +109,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="48">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -177,9 +181,25 @@
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="200" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="203" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="205" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="200" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="204" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="203" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="205" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -439,7 +459,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R24fc1b6a68f6402c"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R61d0c385d1a746da"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -855,7 +875,7 @@
       </x:c>
       <x:c r="D10" s="35" t="n">
         <x:f>'Monthly'!O22</x:f>
-        <x:v>282038.2316548526</x:v>
+        <x:v>508855.1978997918</x:v>
       </x:c>
       <x:c r="E10" s="5" t="str">
         <x:v>December</x:v>
@@ -879,7 +899,7 @@
       </x:c>
       <x:c r="D11" s="35" t="n">
         <x:f>MIN('Monthly'!J22:O22)</x:f>
-        <x:v>282038.2316548526</x:v>
+        <x:v>279760.08444999997</x:v>
       </x:c>
       <x:c r="E11" s="5" t="str">
         <x:v>Jul-Dec</x:v>
@@ -1255,7 +1275,7 @@
       <x:c r="F27" s="1"/>
       <x:c r="G27" s="1"/>
       <x:c r="H27" s="5" t="str">
-        <x:v>Synthetic case. Cash forecast excludes debt and financing.</x:v>
+        <x:v>Synthetic case. Statements include AR/AP lags, PP&amp;E, debt, interest and tax losses.</x:v>
       </x:c>
       <x:c r="I27" s="5"/>
       <x:c r="J27" s="5"/>
@@ -1926,7 +1946,3799 @@
     <x:mergeCell ref="H27:O28"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R2450dd81e70f4c54"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R10d857dd78ea4ec0"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="3" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="1"/>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="1"/>
+      <x:c r="E1" s="1"/>
+      <x:c r="F1" s="1"/>
+      <x:c r="G1" s="1"/>
+      <x:c r="H1" s="1"/>
+      <x:c r="I1" s="1"/>
+      <x:c r="J1" s="1"/>
+      <x:c r="K1" s="1"/>
+      <x:c r="L1" s="1"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="1"/>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="2" t="str">
+        <x:v>Forecast statements and balance sheet</x:v>
+      </x:c>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
+      <x:c r="L2" s="1"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3"/>
+      <x:c r="I3" s="3"/>
+      <x:c r="J3" s="3"/>
+      <x:c r="K3" s="3"/>
+      <x:c r="L3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1" t="str">
+        <x:v>Case selected</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:f>'Assumptions'!D4</x:f>
+        <x:v>Base</x:v>
+      </x:c>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+      <x:c r="K4" s="1"/>
+      <x:c r="L4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="1"/>
+      <x:c r="B5" s="1"/>
+      <x:c r="C5" s="1"/>
+      <x:c r="D5" s="1"/>
+      <x:c r="E5" s="1"/>
+      <x:c r="F5" s="1"/>
+      <x:c r="G5" s="1"/>
+      <x:c r="H5" s="1"/>
+      <x:c r="I5" s="1"/>
+      <x:c r="J5" s="1"/>
+      <x:c r="K5" s="1"/>
+      <x:c r="L5" s="1"/>
+    </x:row>
+    <x:row r="6" ht="22" customHeight="1">
+      <x:c r="A6" s="1"/>
+      <x:c r="B6" s="1"/>
+      <x:c r="C6" s="1"/>
+      <x:c r="D6" s="20" t="d">
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="d">
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="d">
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G6" s="20" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H6" s="20" t="d">
+        <x:v>2026-11-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I6" s="20" t="d">
+        <x:v>2026-12-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="J6" s="1"/>
+      <x:c r="K6" s="1"/>
+      <x:c r="L6" s="1"/>
+    </x:row>
+    <x:row r="7" ht="22" customHeight="1">
+      <x:c r="A7" s="1"/>
+      <x:c r="B7" s="1"/>
+      <x:c r="C7" s="1" t="str">
+        <x:v>Revenue</x:v>
+      </x:c>
+      <x:c r="D7" s="21" t="n">
+        <x:f>'Monthly'!J7</x:f>
+        <x:v>910447.8928</x:v>
+      </x:c>
+      <x:c r="E7" s="21" t="n">
+        <x:f>'Monthly'!K7</x:f>
+        <x:v>965634.71293132</x:v>
+      </x:c>
+      <x:c r="F7" s="21" t="n">
+        <x:f>'Monthly'!L7</x:f>
+        <x:v>965846.2469509438</x:v>
+      </x:c>
+      <x:c r="G7" s="21" t="n">
+        <x:f>'Monthly'!M7</x:f>
+        <x:v>1063956.4777685371</x:v>
+      </x:c>
+      <x:c r="H7" s="21" t="n">
+        <x:f>'Monthly'!N7</x:f>
+        <x:v>1146725.4969682184</x:v>
+      </x:c>
+      <x:c r="I7" s="21" t="n">
+        <x:f>'Monthly'!O7</x:f>
+        <x:v>1223869.8783387616</x:v>
+      </x:c>
+      <x:c r="J7" s="1"/>
+      <x:c r="K7" s="1"/>
+      <x:c r="L7" s="1"/>
+    </x:row>
+    <x:row r="8" ht="22" customHeight="1">
+      <x:c r="A8" s="1"/>
+      <x:c r="B8" s="1"/>
+      <x:c r="C8" s="1" t="str">
+        <x:v>Variable costs</x:v>
+      </x:c>
+      <x:c r="D8" s="21" t="n">
+        <x:f>'Monthly'!J8</x:f>
+        <x:v>495857.2799999999</x:v>
+      </x:c>
+      <x:c r="E8" s="21" t="n">
+        <x:f>'Monthly'!K8</x:f>
+        <x:v>529540.9504375</x:v>
+      </x:c>
+      <x:c r="F8" s="21" t="n">
+        <x:f>'Monthly'!L8</x:f>
+        <x:v>533321.9622759373</x:v>
+      </x:c>
+      <x:c r="G8" s="21" t="n">
+        <x:f>'Monthly'!M8</x:f>
+        <x:v>591505.4678485779</x:v>
+      </x:c>
+      <x:c r="H8" s="21" t="n">
+        <x:f>'Monthly'!N8</x:f>
+        <x:v>641920.9002589112</x:v>
+      </x:c>
+      <x:c r="I8" s="21" t="n">
+        <x:f>'Monthly'!O8</x:f>
+        <x:v>689814.0344479048</x:v>
+      </x:c>
+      <x:c r="J8" s="1"/>
+      <x:c r="K8" s="1"/>
+      <x:c r="L8" s="1"/>
+    </x:row>
+    <x:row r="9" ht="22" customHeight="1">
+      <x:c r="A9" s="1"/>
+      <x:c r="B9" s="1"/>
+      <x:c r="C9" s="1" t="str">
+        <x:v>Fixed cost</x:v>
+      </x:c>
+      <x:c r="D9" s="21" t="n">
+        <x:f>'Monthly'!J9</x:f>
+        <x:v>210272.92874999996</x:v>
+      </x:c>
+      <x:c r="E9" s="21" t="n">
+        <x:f>'Monthly'!K9</x:f>
+        <x:v>212323.45522500004</x:v>
+      </x:c>
+      <x:c r="F9" s="21" t="n">
+        <x:f>'Monthly'!L9</x:f>
+        <x:v>214393.76689220505</x:v>
+      </x:c>
+      <x:c r="G9" s="21" t="n">
+        <x:f>'Monthly'!M9</x:f>
+        <x:v>216484.05299904558</x:v>
+      </x:c>
+      <x:c r="H9" s="21" t="n">
+        <x:f>'Monthly'!N9</x:f>
+        <x:v>218594.50458997808</x:v>
+      </x:c>
+      <x:c r="I9" s="21" t="n">
+        <x:f>'Monthly'!O9</x:f>
+        <x:v>220725.31452344428</x:v>
+      </x:c>
+      <x:c r="J9" s="1"/>
+      <x:c r="K9" s="1"/>
+      <x:c r="L9" s="1"/>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="1"/>
+      <x:c r="B10" s="1"/>
+      <x:c r="C10" s="1" t="str">
+        <x:v>Opex</x:v>
+      </x:c>
+      <x:c r="D10" s="21" t="n">
+        <x:f>'Monthly'!J10</x:f>
+        <x:v>200650.32</x:v>
+      </x:c>
+      <x:c r="E10" s="21" t="n">
+        <x:f>'Monthly'!K10</x:f>
+        <x:v>205067.0016</x:v>
+      </x:c>
+      <x:c r="F10" s="21" t="n">
+        <x:f>'Monthly'!L10</x:f>
+        <x:v>209580.09033600002</x:v>
+      </x:c>
+      <x:c r="G10" s="21" t="n">
+        <x:f>'Monthly'!M10</x:f>
+        <x:v>214191.6758208</x:v>
+      </x:c>
+      <x:c r="H10" s="21" t="n">
+        <x:f>'Monthly'!N10</x:f>
+        <x:v>218903.89268885762</x:v>
+      </x:c>
+      <x:c r="I10" s="21" t="n">
+        <x:f>'Monthly'!O10</x:f>
+        <x:v>223718.9215613092</x:v>
+      </x:c>
+      <x:c r="J10" s="1"/>
+      <x:c r="K10" s="1"/>
+      <x:c r="L10" s="1"/>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="1"/>
+      <x:c r="B11" s="1"/>
+      <x:c r="C11" s="1" t="str">
+        <x:v>EBITDA</x:v>
+      </x:c>
+      <x:c r="D11" s="21" t="n">
+        <x:f>'Monthly'!J11</x:f>
+        <x:v>3667.364050000062</x:v>
+      </x:c>
+      <x:c r="E11" s="21" t="n">
+        <x:f>'Monthly'!K11</x:f>
+        <x:v>18703.305668819987</x:v>
+      </x:c>
+      <x:c r="F11" s="21" t="n">
+        <x:f>'Monthly'!L11</x:f>
+        <x:v>8550.427446801477</x:v>
+      </x:c>
+      <x:c r="G11" s="21" t="n">
+        <x:f>'Monthly'!M11</x:f>
+        <x:v>41775.28110011376</x:v>
+      </x:c>
+      <x:c r="H11" s="21" t="n">
+        <x:f>'Monthly'!N11</x:f>
+        <x:v>67306.19943047158</x:v>
+      </x:c>
+      <x:c r="I11" s="21" t="n">
+        <x:f>'Monthly'!O11</x:f>
+        <x:v>89611.60780610342</x:v>
+      </x:c>
+      <x:c r="J11" s="1"/>
+      <x:c r="K11" s="1"/>
+      <x:c r="L11" s="1"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="1"/>
+      <x:c r="B12" s="1"/>
+      <x:c r="C12" s="1" t="str">
+        <x:v>Existing asset depreciation</x:v>
+      </x:c>
+      <x:c r="D12" s="21" t="n">
+        <x:f>MIN('Assumptions'!$I$58,MAX(0,'Assumptions'!$I$47-'Assumptions'!$I$48-0*'Assumptions'!$I$58))</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="E12" s="21" t="n">
+        <x:f>MIN('Assumptions'!$I$58,MAX(0,'Assumptions'!$I$47-'Assumptions'!$I$48-1*'Assumptions'!$I$58))</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="F12" s="21" t="n">
+        <x:f>MIN('Assumptions'!$I$58,MAX(0,'Assumptions'!$I$47-'Assumptions'!$I$48-2*'Assumptions'!$I$58))</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="G12" s="21" t="n">
+        <x:f>MIN('Assumptions'!$I$58,MAX(0,'Assumptions'!$I$47-'Assumptions'!$I$48-3*'Assumptions'!$I$58))</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="H12" s="21" t="n">
+        <x:f>MIN('Assumptions'!$I$58,MAX(0,'Assumptions'!$I$47-'Assumptions'!$I$48-4*'Assumptions'!$I$58))</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="I12" s="21" t="n">
+        <x:f>MIN('Assumptions'!$I$58,MAX(0,'Assumptions'!$I$47-'Assumptions'!$I$48-5*'Assumptions'!$I$58))</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="J12" s="1"/>
+      <x:c r="K12" s="1"/>
+      <x:c r="L12" s="1"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="1"/>
+      <x:c r="B13" s="1"/>
+      <x:c r="C13" s="1" t="str">
+        <x:v>New asset depreciation</x:v>
+      </x:c>
+      <x:c r="D13" s="21" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E13" s="21" t="n">
+        <x:f>SUM(D32:D32)/'Assumptions'!$I$49</x:f>
+        <x:v>416.6666666666667</x:v>
+      </x:c>
+      <x:c r="F13" s="21" t="n">
+        <x:f>SUM(D32:E32)/'Assumptions'!$I$49</x:f>
+        <x:v>833.3333333333334</x:v>
+      </x:c>
+      <x:c r="G13" s="21" t="n">
+        <x:f>SUM(D32:F32)/'Assumptions'!$I$49</x:f>
+        <x:v>1250</x:v>
+      </x:c>
+      <x:c r="H13" s="21" t="n">
+        <x:f>SUM(D32:G32)/'Assumptions'!$I$49</x:f>
+        <x:v>1666.6666666666667</x:v>
+      </x:c>
+      <x:c r="I13" s="21" t="n">
+        <x:f>SUM(D32:H32)/'Assumptions'!$I$49</x:f>
+        <x:v>2083.3333333333335</x:v>
+      </x:c>
+      <x:c r="J13" s="1"/>
+      <x:c r="K13" s="1"/>
+      <x:c r="L13" s="1"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="1"/>
+      <x:c r="B14" s="1"/>
+      <x:c r="C14" s="1" t="str">
+        <x:v>Total depreciation</x:v>
+      </x:c>
+      <x:c r="D14" s="21" t="n">
+        <x:f>SUM(D12:D13)</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="E14" s="21" t="n">
+        <x:f>SUM(E12:E13)</x:f>
+        <x:v>20416.666666666668</x:v>
+      </x:c>
+      <x:c r="F14" s="21" t="n">
+        <x:f>SUM(F12:F13)</x:f>
+        <x:v>20833.333333333332</x:v>
+      </x:c>
+      <x:c r="G14" s="21" t="n">
+        <x:f>SUM(G12:G13)</x:f>
+        <x:v>21250</x:v>
+      </x:c>
+      <x:c r="H14" s="21" t="n">
+        <x:f>SUM(H12:H13)</x:f>
+        <x:v>21666.666666666668</x:v>
+      </x:c>
+      <x:c r="I14" s="21" t="n">
+        <x:f>SUM(I12:I13)</x:f>
+        <x:v>22083.333333333332</x:v>
+      </x:c>
+      <x:c r="J14" s="1"/>
+      <x:c r="K14" s="1"/>
+      <x:c r="L14" s="1"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="1"/>
+      <x:c r="B15" s="1"/>
+      <x:c r="C15" s="1" t="str">
+        <x:v>EBIT</x:v>
+      </x:c>
+      <x:c r="D15" s="21" t="n">
+        <x:f>D11-D14</x:f>
+        <x:v>-16332.635949999938</x:v>
+      </x:c>
+      <x:c r="E15" s="21" t="n">
+        <x:f>E11-E14</x:f>
+        <x:v>-1713.3609978466811</x:v>
+      </x:c>
+      <x:c r="F15" s="21" t="n">
+        <x:f>F11-F14</x:f>
+        <x:v>-12282.905886531855</x:v>
+      </x:c>
+      <x:c r="G15" s="21" t="n">
+        <x:f>G11-G14</x:f>
+        <x:v>20525.28110011376</x:v>
+      </x:c>
+      <x:c r="H15" s="21" t="n">
+        <x:f>H11-H14</x:f>
+        <x:v>45639.532763804906</x:v>
+      </x:c>
+      <x:c r="I15" s="21" t="n">
+        <x:f>I11-I14</x:f>
+        <x:v>67528.27447277009</x:v>
+      </x:c>
+      <x:c r="J15" s="1"/>
+      <x:c r="K15" s="1"/>
+      <x:c r="L15" s="1"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="1"/>
+      <x:c r="B16" s="1"/>
+      <x:c r="C16" s="1" t="str">
+        <x:v>Interest expense</x:v>
+      </x:c>
+      <x:c r="D16" s="21" t="n">
+        <x:f>'Debt'!D9</x:f>
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="E16" s="21" t="n">
+        <x:f>'Debt'!E9</x:f>
+        <x:v>3933.3333333333335</x:v>
+      </x:c>
+      <x:c r="F16" s="21" t="n">
+        <x:f>'Debt'!F9</x:f>
+        <x:v>3866.6666666666665</x:v>
+      </x:c>
+      <x:c r="G16" s="21" t="n">
+        <x:f>'Debt'!G9</x:f>
+        <x:v>3800</x:v>
+      </x:c>
+      <x:c r="H16" s="21" t="n">
+        <x:f>'Debt'!H9</x:f>
+        <x:v>3733.3333333333335</x:v>
+      </x:c>
+      <x:c r="I16" s="21" t="n">
+        <x:f>'Debt'!I9</x:f>
+        <x:v>3666.6666666666665</x:v>
+      </x:c>
+      <x:c r="J16" s="1"/>
+      <x:c r="K16" s="1"/>
+      <x:c r="L16" s="1"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="1"/>
+      <x:c r="B17" s="1"/>
+      <x:c r="C17" s="1" t="str">
+        <x:v>Pretax income</x:v>
+      </x:c>
+      <x:c r="D17" s="21" t="n">
+        <x:f>D15-D16</x:f>
+        <x:v>-20332.635949999938</x:v>
+      </x:c>
+      <x:c r="E17" s="21" t="n">
+        <x:f>E15-E16</x:f>
+        <x:v>-5646.694331180015</x:v>
+      </x:c>
+      <x:c r="F17" s="21" t="n">
+        <x:f>F15-F16</x:f>
+        <x:v>-16149.57255319852</x:v>
+      </x:c>
+      <x:c r="G17" s="21" t="n">
+        <x:f>G15-G16</x:f>
+        <x:v>16725.28110011376</x:v>
+      </x:c>
+      <x:c r="H17" s="21" t="n">
+        <x:f>H15-H16</x:f>
+        <x:v>41906.19943047157</x:v>
+      </x:c>
+      <x:c r="I17" s="21" t="n">
+        <x:f>I15-I16</x:f>
+        <x:v>63861.60780610343</x:v>
+      </x:c>
+      <x:c r="J17" s="1"/>
+      <x:c r="K17" s="1"/>
+      <x:c r="L17" s="1"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="1"/>
+      <x:c r="B18" s="1"/>
+      <x:c r="C18" s="1" t="str">
+        <x:v>Opening tax losses</x:v>
+      </x:c>
+      <x:c r="D18" s="21" t="n">
+        <x:f>'Assumptions'!I54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="21" t="n">
+        <x:f>D22</x:f>
+        <x:v>20332.635949999938</x:v>
+      </x:c>
+      <x:c r="F18" s="21" t="n">
+        <x:f>E22</x:f>
+        <x:v>25979.33028117995</x:v>
+      </x:c>
+      <x:c r="G18" s="21" t="n">
+        <x:f>F22</x:f>
+        <x:v>42128.902834378474</x:v>
+      </x:c>
+      <x:c r="H18" s="21" t="n">
+        <x:f>G22</x:f>
+        <x:v>25403.621734264714</x:v>
+      </x:c>
+      <x:c r="I18" s="21" t="n">
+        <x:f>H22</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J18" s="1"/>
+      <x:c r="K18" s="1"/>
+      <x:c r="L18" s="1"/>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19" s="1"/>
+      <x:c r="B19" s="1"/>
+      <x:c r="C19" s="1" t="str">
+        <x:v>Tax losses used</x:v>
+      </x:c>
+      <x:c r="D19" s="21" t="n">
+        <x:f>MIN(D18,MAX(0,D17))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E19" s="21" t="n">
+        <x:f>MIN(E18,MAX(0,E17))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="21" t="n">
+        <x:f>MIN(F18,MAX(0,F17))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="21" t="n">
+        <x:f>MIN(G18,MAX(0,G17))</x:f>
+        <x:v>16725.28110011376</x:v>
+      </x:c>
+      <x:c r="H19" s="21" t="n">
+        <x:f>MIN(H18,MAX(0,H17))</x:f>
+        <x:v>25403.621734264714</x:v>
+      </x:c>
+      <x:c r="I19" s="21" t="n">
+        <x:f>MIN(I18,MAX(0,I17))</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J19" s="1"/>
+      <x:c r="K19" s="1"/>
+      <x:c r="L19" s="1"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="1"/>
+      <x:c r="B20" s="1"/>
+      <x:c r="C20" s="1" t="str">
+        <x:v>Taxable income</x:v>
+      </x:c>
+      <x:c r="D20" s="21" t="n">
+        <x:f>MAX(0,D17-D19)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E20" s="21" t="n">
+        <x:f>MAX(0,E17-E19)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F20" s="21" t="n">
+        <x:f>MAX(0,F17-F19)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G20" s="21" t="n">
+        <x:f>MAX(0,G17-G19)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H20" s="21" t="n">
+        <x:f>MAX(0,H17-H19)</x:f>
+        <x:v>16502.577696206856</x:v>
+      </x:c>
+      <x:c r="I20" s="21" t="n">
+        <x:f>MAX(0,I17-I19)</x:f>
+        <x:v>63861.60780610343</x:v>
+      </x:c>
+      <x:c r="J20" s="1"/>
+      <x:c r="K20" s="1"/>
+      <x:c r="L20" s="1"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="1"/>
+      <x:c r="B21" s="1"/>
+      <x:c r="C21" s="1" t="str">
+        <x:v>Cash tax / expense</x:v>
+      </x:c>
+      <x:c r="D21" s="21" t="n">
+        <x:f>D20*'Assumptions'!$I$55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E21" s="21" t="n">
+        <x:f>E20*'Assumptions'!$I$55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F21" s="21" t="n">
+        <x:f>F20*'Assumptions'!$I$55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G21" s="21" t="n">
+        <x:f>G20*'Assumptions'!$I$55</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H21" s="21" t="n">
+        <x:f>H20*'Assumptions'!$I$55</x:f>
+        <x:v>4125.644424051714</x:v>
+      </x:c>
+      <x:c r="I21" s="21" t="n">
+        <x:f>I20*'Assumptions'!$I$55</x:f>
+        <x:v>15965.401951525857</x:v>
+      </x:c>
+      <x:c r="J21" s="1"/>
+      <x:c r="K21" s="1"/>
+      <x:c r="L21" s="1"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="1"/>
+      <x:c r="B22" s="1"/>
+      <x:c r="C22" s="1" t="str">
+        <x:v>Closing tax losses</x:v>
+      </x:c>
+      <x:c r="D22" s="21" t="n">
+        <x:f>D18-D19+MAX(0,-D17)</x:f>
+        <x:v>20332.635949999938</x:v>
+      </x:c>
+      <x:c r="E22" s="21" t="n">
+        <x:f>E18-E19+MAX(0,-E17)</x:f>
+        <x:v>25979.33028117995</x:v>
+      </x:c>
+      <x:c r="F22" s="21" t="n">
+        <x:f>F18-F19+MAX(0,-F17)</x:f>
+        <x:v>42128.902834378474</x:v>
+      </x:c>
+      <x:c r="G22" s="21" t="n">
+        <x:f>G18-G19+MAX(0,-G17)</x:f>
+        <x:v>25403.621734264714</x:v>
+      </x:c>
+      <x:c r="H22" s="21" t="n">
+        <x:f>H18-H19+MAX(0,-H17)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I22" s="21" t="n">
+        <x:f>I18-I19+MAX(0,-I17)</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J22" s="1"/>
+      <x:c r="K22" s="1"/>
+      <x:c r="L22" s="1"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="1"/>
+      <x:c r="B23" s="1"/>
+      <x:c r="C23" s="1" t="str">
+        <x:v>Net income</x:v>
+      </x:c>
+      <x:c r="D23" s="21" t="n">
+        <x:f>D17-D21</x:f>
+        <x:v>-20332.635949999938</x:v>
+      </x:c>
+      <x:c r="E23" s="21" t="n">
+        <x:f>E17-E21</x:f>
+        <x:v>-5646.694331180015</x:v>
+      </x:c>
+      <x:c r="F23" s="21" t="n">
+        <x:f>F17-F21</x:f>
+        <x:v>-16149.57255319852</x:v>
+      </x:c>
+      <x:c r="G23" s="21" t="n">
+        <x:f>G17-G21</x:f>
+        <x:v>16725.28110011376</x:v>
+      </x:c>
+      <x:c r="H23" s="21" t="n">
+        <x:f>H17-H21</x:f>
+        <x:v>37780.555006419854</x:v>
+      </x:c>
+      <x:c r="I23" s="21" t="n">
+        <x:f>I17-I21</x:f>
+        <x:v>47896.20585457757</x:v>
+      </x:c>
+      <x:c r="J23" s="1"/>
+      <x:c r="K23" s="1"/>
+      <x:c r="L23" s="1"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="1"/>
+      <x:c r="D24" s="21"/>
+      <x:c r="E24" s="21"/>
+      <x:c r="F24" s="21"/>
+      <x:c r="G24" s="21"/>
+      <x:c r="H24" s="21"/>
+      <x:c r="I24" s="21"/>
+      <x:c r="J24" s="1"/>
+      <x:c r="K24" s="1"/>
+      <x:c r="L24" s="1"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="1"/>
+      <x:c r="B25" s="1"/>
+      <x:c r="C25" s="1"/>
+      <x:c r="D25" s="21"/>
+      <x:c r="E25" s="21"/>
+      <x:c r="F25" s="21"/>
+      <x:c r="G25" s="21"/>
+      <x:c r="H25" s="21"/>
+      <x:c r="I25" s="21"/>
+      <x:c r="J25" s="1"/>
+      <x:c r="K25" s="1"/>
+      <x:c r="L25" s="1"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="1" t="str">
+        <x:v>Opening cash</x:v>
+      </x:c>
+      <x:c r="D26" s="21" t="n">
+        <x:f>'Assumptions'!I56</x:f>
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="E26" s="21" t="n">
+        <x:f>D35</x:f>
+        <x:v>279760.08444999997</x:v>
+      </x:c>
+      <x:c r="F26" s="21" t="n">
+        <x:f>E35</x:f>
+        <x:v>613936.9876257466</x:v>
+      </x:c>
+      <x:c r="G26" s="21" t="n">
+        <x:f>F35</x:f>
+        <x:v>579833.9217972502</x:v>
+      </x:c>
+      <x:c r="H26" s="21" t="n">
+        <x:f>G35</x:f>
+        <x:v>538297.129168527</x:v>
+      </x:c>
+      <x:c r="I26" s="21" t="n">
+        <x:f>H35</x:f>
+        <x:v>516064.2795652597</x:v>
+      </x:c>
+      <x:c r="J26" s="1"/>
+      <x:c r="K26" s="1"/>
+      <x:c r="L26" s="1"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="1"/>
+      <x:c r="B27" s="1"/>
+      <x:c r="C27" s="1" t="str">
+        <x:v>Net income</x:v>
+      </x:c>
+      <x:c r="D27" s="21" t="n">
+        <x:f>D23</x:f>
+        <x:v>-20332.635949999938</x:v>
+      </x:c>
+      <x:c r="E27" s="21" t="n">
+        <x:f>E23</x:f>
+        <x:v>-5646.694331180015</x:v>
+      </x:c>
+      <x:c r="F27" s="21" t="n">
+        <x:f>F23</x:f>
+        <x:v>-16149.57255319852</x:v>
+      </x:c>
+      <x:c r="G27" s="21" t="n">
+        <x:f>G23</x:f>
+        <x:v>16725.28110011376</x:v>
+      </x:c>
+      <x:c r="H27" s="21" t="n">
+        <x:f>H23</x:f>
+        <x:v>37780.555006419854</x:v>
+      </x:c>
+      <x:c r="I27" s="21" t="n">
+        <x:f>I23</x:f>
+        <x:v>47896.20585457757</x:v>
+      </x:c>
+      <x:c r="J27" s="1"/>
+      <x:c r="K27" s="1"/>
+      <x:c r="L27" s="1"/>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" s="1"/>
+      <x:c r="B28" s="1"/>
+      <x:c r="C28" s="1" t="str">
+        <x:v>Depreciation add-back</x:v>
+      </x:c>
+      <x:c r="D28" s="21" t="n">
+        <x:f>D14</x:f>
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="E28" s="21" t="n">
+        <x:f>E14</x:f>
+        <x:v>20416.666666666668</x:v>
+      </x:c>
+      <x:c r="F28" s="21" t="n">
+        <x:f>F14</x:f>
+        <x:v>20833.333333333332</x:v>
+      </x:c>
+      <x:c r="G28" s="21" t="n">
+        <x:f>G14</x:f>
+        <x:v>21250</x:v>
+      </x:c>
+      <x:c r="H28" s="21" t="n">
+        <x:f>H14</x:f>
+        <x:v>21666.666666666668</x:v>
+      </x:c>
+      <x:c r="I28" s="21" t="n">
+        <x:f>I14</x:f>
+        <x:v>22083.333333333332</x:v>
+      </x:c>
+      <x:c r="J28" s="1"/>
+      <x:c r="K28" s="1"/>
+      <x:c r="L28" s="1"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" s="1"/>
+      <x:c r="B29" s="1"/>
+      <x:c r="C29" s="1" t="str">
+        <x:v>Change in AR</x:v>
+      </x:c>
+      <x:c r="D29" s="21" t="n">
+        <x:f>'Working Capital'!D14-'Working Capital'!D13</x:f>
+        <x:v>132835.91960000014</x:v>
+      </x:c>
+      <x:c r="E29" s="21" t="n">
+        <x:f>'Working Capital'!E14-'Working Capital'!E13</x:f>
+        <x:v>-337565.09562150994</x:v>
+      </x:c>
+      <x:c r="F29" s="21" t="n">
+        <x:f>'Working Capital'!F14-'Working Capital'!F13</x:f>
+        <x:v>5677.33252784994</x:v>
+      </x:c>
+      <x:c r="G29" s="21" t="n">
+        <x:f>'Working Capital'!G14-'Working Capital'!G13</x:f>
+        <x:v>73603.82651515724</x:v>
+      </x:c>
+      <x:c r="H29" s="21" t="n">
+        <x:f>'Working Capital'!H14-'Working Capital'!H13</x:f>
+        <x:v>71887.78748152044</x:v>
+      </x:c>
+      <x:c r="I29" s="21" t="n">
+        <x:f>'Working Capital'!I14-'Working Capital'!I13</x:f>
+        <x:v>66135.18794787559</x:v>
+      </x:c>
+      <x:c r="J29" s="1"/>
+      <x:c r="K29" s="1"/>
+      <x:c r="L29" s="1"/>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
+      <x:c r="A30" s="1"/>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="1" t="str">
+        <x:v>Change in AP</x:v>
+      </x:c>
+      <x:c r="D30" s="21" t="n">
+        <x:f>'Working Capital'!D22-'Working Capital'!D21</x:f>
+        <x:v>-52071.359999999986</x:v>
+      </x:c>
+      <x:c r="E30" s="21" t="n">
+        <x:f>'Working Capital'!E22-'Working Capital'!E21</x:f>
+        <x:v>16841.835218750057</x:v>
+      </x:c>
+      <x:c r="F30" s="21" t="n">
+        <x:f>'Working Capital'!F22-'Working Capital'!F21</x:f>
+        <x:v>1890.5059192186454</x:v>
+      </x:c>
+      <x:c r="G30" s="21" t="n">
+        <x:f>'Working Capital'!G22-'Working Capital'!G21</x:f>
+        <x:v>29091.752786320285</x:v>
+      </x:c>
+      <x:c r="H30" s="21" t="n">
+        <x:f>'Working Capital'!H22-'Working Capital'!H21</x:f>
+        <x:v>25207.716205166653</x:v>
+      </x:c>
+      <x:c r="I30" s="21" t="n">
+        <x:f>'Working Capital'!I22-'Working Capital'!I21</x:f>
+        <x:v>23946.5670944968</x:v>
+      </x:c>
+      <x:c r="J30" s="1"/>
+      <x:c r="K30" s="1"/>
+      <x:c r="L30" s="1"/>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
+      <x:c r="A31" s="1"/>
+      <x:c r="B31" s="1"/>
+      <x:c r="C31" s="1" t="str">
+        <x:v>Operating cash flow</x:v>
+      </x:c>
+      <x:c r="D31" s="21" t="n">
+        <x:f>SUM(D27:D28)-D29+D30</x:f>
+        <x:v>-185239.91555000006</x:v>
+      </x:c>
+      <x:c r="E31" s="21" t="n">
+        <x:f>SUM(E27:E28)-E29+E30</x:f>
+        <x:v>369176.9031757467</x:v>
+      </x:c>
+      <x:c r="F31" s="21" t="n">
+        <x:f>SUM(F27:F28)-F29+F30</x:f>
+        <x:v>896.9341715035171</x:v>
+      </x:c>
+      <x:c r="G31" s="21" t="n">
+        <x:f>SUM(G27:G28)-G29+G30</x:f>
+        <x:v>-6536.792628723197</x:v>
+      </x:c>
+      <x:c r="H31" s="21" t="n">
+        <x:f>SUM(H27:H28)-H29+H30</x:f>
+        <x:v>12767.15039673273</x:v>
+      </x:c>
+      <x:c r="I31" s="21" t="n">
+        <x:f>SUM(I27:I28)-I29+I30</x:f>
+        <x:v>27790.91833453212</x:v>
+      </x:c>
+      <x:c r="J31" s="1"/>
+      <x:c r="K31" s="1"/>
+      <x:c r="L31" s="1"/>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
+      <x:c r="A32" s="1"/>
+      <x:c r="B32" s="1"/>
+      <x:c r="C32" s="1" t="str">
+        <x:v>Cash capex</x:v>
+      </x:c>
+      <x:c r="D32" s="21" t="n">
+        <x:f>'Assumptions'!$I$57</x:f>
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="E32" s="21" t="n">
+        <x:f>'Assumptions'!$I$57</x:f>
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="F32" s="21" t="n">
+        <x:f>'Assumptions'!$I$57</x:f>
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="G32" s="21" t="n">
+        <x:f>'Assumptions'!$I$57</x:f>
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="H32" s="21" t="n">
+        <x:f>'Assumptions'!$I$57</x:f>
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="I32" s="21" t="n">
+        <x:f>'Assumptions'!$I$57</x:f>
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="J32" s="1"/>
+      <x:c r="K32" s="1"/>
+      <x:c r="L32" s="1"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="1"/>
+      <x:c r="B33" s="1"/>
+      <x:c r="C33" s="1" t="str">
+        <x:v>Debt principal repayment</x:v>
+      </x:c>
+      <x:c r="D33" s="21" t="n">
+        <x:f>'Debt'!D10</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E33" s="21" t="n">
+        <x:f>'Debt'!E10</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F33" s="21" t="n">
+        <x:f>'Debt'!F10</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="G33" s="21" t="n">
+        <x:f>'Debt'!G10</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="H33" s="21" t="n">
+        <x:f>'Debt'!H10</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="I33" s="21" t="n">
+        <x:f>'Debt'!I10</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="J33" s="1"/>
+      <x:c r="K33" s="1"/>
+      <x:c r="L33" s="1"/>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="1"/>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="1" t="str">
+        <x:v>Net change in cash</x:v>
+      </x:c>
+      <x:c r="D34" s="21" t="n">
+        <x:f>D31-SUM(D32:D33)</x:f>
+        <x:v>-220239.91555000006</x:v>
+      </x:c>
+      <x:c r="E34" s="21" t="n">
+        <x:f>E31-SUM(E32:E33)</x:f>
+        <x:v>334176.9031757467</x:v>
+      </x:c>
+      <x:c r="F34" s="21" t="n">
+        <x:f>F31-SUM(F32:F33)</x:f>
+        <x:v>-34103.06582849648</x:v>
+      </x:c>
+      <x:c r="G34" s="21" t="n">
+        <x:f>G31-SUM(G32:G33)</x:f>
+        <x:v>-41536.7926287232</x:v>
+      </x:c>
+      <x:c r="H34" s="21" t="n">
+        <x:f>H31-SUM(H32:H33)</x:f>
+        <x:v>-22232.84960326727</x:v>
+      </x:c>
+      <x:c r="I34" s="21" t="n">
+        <x:f>I31-SUM(I32:I33)</x:f>
+        <x:v>-7209.081665467878</x:v>
+      </x:c>
+      <x:c r="J34" s="1"/>
+      <x:c r="K34" s="1"/>
+      <x:c r="L34" s="1"/>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35" s="1"/>
+      <x:c r="B35" s="1"/>
+      <x:c r="C35" s="1" t="str">
+        <x:v>Closing cash</x:v>
+      </x:c>
+      <x:c r="D35" s="21" t="n">
+        <x:f>SUM(D26,D34)</x:f>
+        <x:v>279760.08444999997</x:v>
+      </x:c>
+      <x:c r="E35" s="21" t="n">
+        <x:f>SUM(E26,E34)</x:f>
+        <x:v>613936.9876257466</x:v>
+      </x:c>
+      <x:c r="F35" s="21" t="n">
+        <x:f>SUM(F26,F34)</x:f>
+        <x:v>579833.9217972502</x:v>
+      </x:c>
+      <x:c r="G35" s="21" t="n">
+        <x:f>SUM(G26,G34)</x:f>
+        <x:v>538297.129168527</x:v>
+      </x:c>
+      <x:c r="H35" s="21" t="n">
+        <x:f>SUM(H26,H34)</x:f>
+        <x:v>516064.2795652597</x:v>
+      </x:c>
+      <x:c r="I35" s="21" t="n">
+        <x:f>SUM(I26,I34)</x:f>
+        <x:v>508855.1978997918</x:v>
+      </x:c>
+      <x:c r="J35" s="1"/>
+      <x:c r="K35" s="1"/>
+      <x:c r="L35" s="1"/>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36" s="1"/>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="1"/>
+      <x:c r="D36" s="21"/>
+      <x:c r="E36" s="21"/>
+      <x:c r="F36" s="21"/>
+      <x:c r="G36" s="21"/>
+      <x:c r="H36" s="21"/>
+      <x:c r="I36" s="21"/>
+      <x:c r="J36" s="1"/>
+      <x:c r="K36" s="1"/>
+      <x:c r="L36" s="1"/>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="1"/>
+      <x:c r="B37" s="1"/>
+      <x:c r="C37" s="1"/>
+      <x:c r="D37" s="21"/>
+      <x:c r="E37" s="21"/>
+      <x:c r="F37" s="21"/>
+      <x:c r="G37" s="21"/>
+      <x:c r="H37" s="21"/>
+      <x:c r="I37" s="21"/>
+      <x:c r="J37" s="1"/>
+      <x:c r="K37" s="1"/>
+      <x:c r="L37" s="1"/>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="1"/>
+      <x:c r="B38" s="1"/>
+      <x:c r="C38" s="1" t="str">
+        <x:v>Cash</x:v>
+      </x:c>
+      <x:c r="D38" s="21" t="n">
+        <x:f>D35</x:f>
+        <x:v>279760.08444999997</x:v>
+      </x:c>
+      <x:c r="E38" s="21" t="n">
+        <x:f>E35</x:f>
+        <x:v>613936.9876257466</x:v>
+      </x:c>
+      <x:c r="F38" s="21" t="n">
+        <x:f>F35</x:f>
+        <x:v>579833.9217972502</x:v>
+      </x:c>
+      <x:c r="G38" s="21" t="n">
+        <x:f>G35</x:f>
+        <x:v>538297.129168527</x:v>
+      </x:c>
+      <x:c r="H38" s="21" t="n">
+        <x:f>H35</x:f>
+        <x:v>516064.2795652597</x:v>
+      </x:c>
+      <x:c r="I38" s="21" t="n">
+        <x:f>I35</x:f>
+        <x:v>508855.1978997918</x:v>
+      </x:c>
+      <x:c r="J38" s="1"/>
+      <x:c r="K38" s="1"/>
+      <x:c r="L38" s="1"/>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
+      <x:c r="A39" s="1"/>
+      <x:c r="B39" s="1"/>
+      <x:c r="C39" s="1" t="str">
+        <x:v>AR</x:v>
+      </x:c>
+      <x:c r="D39" s="21" t="n">
+        <x:f>'Working Capital'!D14</x:f>
+        <x:v>1152835.9196000001</x:v>
+      </x:c>
+      <x:c r="E39" s="21" t="n">
+        <x:f>'Working Capital'!E14</x:f>
+        <x:v>815270.8239784902</x:v>
+      </x:c>
+      <x:c r="F39" s="21" t="n">
+        <x:f>'Working Capital'!F14</x:f>
+        <x:v>820948.1565063401</x:v>
+      </x:c>
+      <x:c r="G39" s="21" t="n">
+        <x:f>'Working Capital'!G14</x:f>
+        <x:v>894551.9830214974</x:v>
+      </x:c>
+      <x:c r="H39" s="21" t="n">
+        <x:f>'Working Capital'!H14</x:f>
+        <x:v>966439.7705030178</x:v>
+      </x:c>
+      <x:c r="I39" s="21" t="n">
+        <x:f>'Working Capital'!I14</x:f>
+        <x:v>1032574.9584508934</x:v>
+      </x:c>
+      <x:c r="J39" s="1"/>
+      <x:c r="K39" s="1"/>
+      <x:c r="L39" s="1"/>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
+      <x:c r="A40" s="1"/>
+      <x:c r="B40" s="1"/>
+      <x:c r="C40" s="1" t="str">
+        <x:v>Gross PP&amp;E</x:v>
+      </x:c>
+      <x:c r="D40" s="21" t="n">
+        <x:f>'Assumptions'!I47+D32</x:f>
+        <x:v>1225000</x:v>
+      </x:c>
+      <x:c r="E40" s="21" t="n">
+        <x:f>D40+E32</x:f>
+        <x:v>1250000</x:v>
+      </x:c>
+      <x:c r="F40" s="21" t="n">
+        <x:f>E40+F32</x:f>
+        <x:v>1275000</x:v>
+      </x:c>
+      <x:c r="G40" s="21" t="n">
+        <x:f>F40+G32</x:f>
+        <x:v>1300000</x:v>
+      </x:c>
+      <x:c r="H40" s="21" t="n">
+        <x:f>G40+H32</x:f>
+        <x:v>1325000</x:v>
+      </x:c>
+      <x:c r="I40" s="21" t="n">
+        <x:f>H40+I32</x:f>
+        <x:v>1350000</x:v>
+      </x:c>
+      <x:c r="J40" s="1"/>
+      <x:c r="K40" s="1"/>
+      <x:c r="L40" s="1"/>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
+      <x:c r="A41" s="1"/>
+      <x:c r="B41" s="1"/>
+      <x:c r="C41" s="1" t="str">
+        <x:v>Accumulated depreciation</x:v>
+      </x:c>
+      <x:c r="D41" s="21" t="n">
+        <x:f>'Assumptions'!I48+D14</x:f>
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="E41" s="21" t="n">
+        <x:f>D41+E14</x:f>
+        <x:v>520416.6666666667</x:v>
+      </x:c>
+      <x:c r="F41" s="21" t="n">
+        <x:f>E41+F14</x:f>
+        <x:v>541250</x:v>
+      </x:c>
+      <x:c r="G41" s="21" t="n">
+        <x:f>F41+G14</x:f>
+        <x:v>562500</x:v>
+      </x:c>
+      <x:c r="H41" s="21" t="n">
+        <x:f>G41+H14</x:f>
+        <x:v>584166.6666666666</x:v>
+      </x:c>
+      <x:c r="I41" s="21" t="n">
+        <x:f>H41+I14</x:f>
+        <x:v>606250</x:v>
+      </x:c>
+      <x:c r="J41" s="1"/>
+      <x:c r="K41" s="1"/>
+      <x:c r="L41" s="1"/>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
+      <x:c r="A42" s="1"/>
+      <x:c r="B42" s="1"/>
+      <x:c r="C42" s="1" t="str">
+        <x:v>Net PP&amp;E</x:v>
+      </x:c>
+      <x:c r="D42" s="21" t="n">
+        <x:f>D40-D41</x:f>
+        <x:v>725000</x:v>
+      </x:c>
+      <x:c r="E42" s="21" t="n">
+        <x:f>E40-E41</x:f>
+        <x:v>729583.3333333333</x:v>
+      </x:c>
+      <x:c r="F42" s="21" t="n">
+        <x:f>F40-F41</x:f>
+        <x:v>733750</x:v>
+      </x:c>
+      <x:c r="G42" s="21" t="n">
+        <x:f>G40-G41</x:f>
+        <x:v>737500</x:v>
+      </x:c>
+      <x:c r="H42" s="21" t="n">
+        <x:f>H40-H41</x:f>
+        <x:v>740833.3333333334</x:v>
+      </x:c>
+      <x:c r="I42" s="21" t="n">
+        <x:f>I40-I41</x:f>
+        <x:v>743750</x:v>
+      </x:c>
+      <x:c r="J42" s="1"/>
+      <x:c r="K42" s="1"/>
+      <x:c r="L42" s="1"/>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
+      <x:c r="A43" s="1"/>
+      <x:c r="B43" s="1"/>
+      <x:c r="C43" s="1" t="str">
+        <x:v>Total assets</x:v>
+      </x:c>
+      <x:c r="D43" s="21" t="n">
+        <x:f>SUM(D38:D39,D42)</x:f>
+        <x:v>2157596.00405</x:v>
+      </x:c>
+      <x:c r="E43" s="21" t="n">
+        <x:f>SUM(E38:E39,E42)</x:f>
+        <x:v>2158791.14493757</x:v>
+      </x:c>
+      <x:c r="F43" s="21" t="n">
+        <x:f>SUM(F38:F39,F42)</x:f>
+        <x:v>2134532.0783035904</x:v>
+      </x:c>
+      <x:c r="G43" s="21" t="n">
+        <x:f>SUM(G38:G39,G42)</x:f>
+        <x:v>2170349.1121900245</x:v>
+      </x:c>
+      <x:c r="H43" s="21" t="n">
+        <x:f>SUM(H38:H39,H42)</x:f>
+        <x:v>2223337.383401611</x:v>
+      </x:c>
+      <x:c r="I43" s="21" t="n">
+        <x:f>SUM(I38:I39,I42)</x:f>
+        <x:v>2285180.1563506853</x:v>
+      </x:c>
+      <x:c r="J43" s="1"/>
+      <x:c r="K43" s="1"/>
+      <x:c r="L43" s="1"/>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
+      <x:c r="A44" s="1"/>
+      <x:c r="B44" s="1"/>
+      <x:c r="C44" s="1"/>
+      <x:c r="D44" s="21"/>
+      <x:c r="E44" s="21"/>
+      <x:c r="F44" s="21"/>
+      <x:c r="G44" s="21"/>
+      <x:c r="H44" s="21"/>
+      <x:c r="I44" s="21"/>
+      <x:c r="J44" s="1"/>
+      <x:c r="K44" s="1"/>
+      <x:c r="L44" s="1"/>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="1"/>
+      <x:c r="B45" s="1"/>
+      <x:c r="C45" s="1" t="str">
+        <x:v>AP</x:v>
+      </x:c>
+      <x:c r="D45" s="21" t="n">
+        <x:f>'Working Capital'!D22</x:f>
+        <x:v>247928.64</x:v>
+      </x:c>
+      <x:c r="E45" s="21" t="n">
+        <x:f>'Working Capital'!E22</x:f>
+        <x:v>264770.47521875007</x:v>
+      </x:c>
+      <x:c r="F45" s="21" t="n">
+        <x:f>'Working Capital'!F22</x:f>
+        <x:v>266660.9811379687</x:v>
+      </x:c>
+      <x:c r="G45" s="21" t="n">
+        <x:f>'Working Capital'!G22</x:f>
+        <x:v>295752.733924289</x:v>
+      </x:c>
+      <x:c r="H45" s="21" t="n">
+        <x:f>'Working Capital'!H22</x:f>
+        <x:v>320960.45012945565</x:v>
+      </x:c>
+      <x:c r="I45" s="21" t="n">
+        <x:f>'Working Capital'!I22</x:f>
+        <x:v>344907.01722395245</x:v>
+      </x:c>
+      <x:c r="J45" s="1"/>
+      <x:c r="K45" s="1"/>
+      <x:c r="L45" s="1"/>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
+      <x:c r="A46" s="1"/>
+      <x:c r="B46" s="1"/>
+      <x:c r="C46" s="1" t="str">
+        <x:v>Debt</x:v>
+      </x:c>
+      <x:c r="D46" s="21" t="n">
+        <x:f>'Debt'!D11</x:f>
+        <x:v>590000</x:v>
+      </x:c>
+      <x:c r="E46" s="21" t="n">
+        <x:f>'Debt'!E11</x:f>
+        <x:v>580000</x:v>
+      </x:c>
+      <x:c r="F46" s="21" t="n">
+        <x:f>'Debt'!F11</x:f>
+        <x:v>570000</x:v>
+      </x:c>
+      <x:c r="G46" s="21" t="n">
+        <x:f>'Debt'!G11</x:f>
+        <x:v>560000</x:v>
+      </x:c>
+      <x:c r="H46" s="21" t="n">
+        <x:f>'Debt'!H11</x:f>
+        <x:v>550000</x:v>
+      </x:c>
+      <x:c r="I46" s="21" t="n">
+        <x:f>'Debt'!I11</x:f>
+        <x:v>540000</x:v>
+      </x:c>
+      <x:c r="J46" s="1"/>
+      <x:c r="K46" s="1"/>
+      <x:c r="L46" s="1"/>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="1"/>
+      <x:c r="B47" s="1"/>
+      <x:c r="C47" s="1" t="str">
+        <x:v>Total liabilities</x:v>
+      </x:c>
+      <x:c r="D47" s="21" t="n">
+        <x:f>SUM(D45:D46)</x:f>
+        <x:v>837928.64</x:v>
+      </x:c>
+      <x:c r="E47" s="21" t="n">
+        <x:f>SUM(E45:E46)</x:f>
+        <x:v>844770.4752187501</x:v>
+      </x:c>
+      <x:c r="F47" s="21" t="n">
+        <x:f>SUM(F45:F46)</x:f>
+        <x:v>836660.9811379687</x:v>
+      </x:c>
+      <x:c r="G47" s="21" t="n">
+        <x:f>SUM(G45:G46)</x:f>
+        <x:v>855752.733924289</x:v>
+      </x:c>
+      <x:c r="H47" s="21" t="n">
+        <x:f>SUM(H45:H46)</x:f>
+        <x:v>870960.4501294557</x:v>
+      </x:c>
+      <x:c r="I47" s="21" t="n">
+        <x:f>SUM(I45:I46)</x:f>
+        <x:v>884907.0172239525</x:v>
+      </x:c>
+      <x:c r="J47" s="1"/>
+      <x:c r="K47" s="1"/>
+      <x:c r="L47" s="1"/>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
+      <x:c r="A48" s="1"/>
+      <x:c r="B48" s="1"/>
+      <x:c r="C48" s="1"/>
+      <x:c r="D48" s="21"/>
+      <x:c r="E48" s="21"/>
+      <x:c r="F48" s="21"/>
+      <x:c r="G48" s="21"/>
+      <x:c r="H48" s="21"/>
+      <x:c r="I48" s="21"/>
+      <x:c r="J48" s="1"/>
+      <x:c r="K48" s="1"/>
+      <x:c r="L48" s="1"/>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="1"/>
+      <x:c r="B49" s="1"/>
+      <x:c r="C49" s="1" t="str">
+        <x:v>Share capital</x:v>
+      </x:c>
+      <x:c r="D49" s="21" t="n">
+        <x:f>'Assumptions'!$I$53</x:f>
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="E49" s="21" t="n">
+        <x:f>'Assumptions'!$I$53</x:f>
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="F49" s="21" t="n">
+        <x:f>'Assumptions'!$I$53</x:f>
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="G49" s="21" t="n">
+        <x:f>'Assumptions'!$I$53</x:f>
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="H49" s="21" t="n">
+        <x:f>'Assumptions'!$I$53</x:f>
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="I49" s="21" t="n">
+        <x:f>'Assumptions'!$I$53</x:f>
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="J49" s="1"/>
+      <x:c r="K49" s="1"/>
+      <x:c r="L49" s="1"/>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="1"/>
+      <x:c r="B50" s="1"/>
+      <x:c r="C50" s="1" t="str">
+        <x:v>Opening retained earnings</x:v>
+      </x:c>
+      <x:c r="D50" s="21" t="n">
+        <x:f>SUM('Assumptions'!I56,'Assumptions'!I41,'Assumptions'!I47)-SUM('Assumptions'!I48,'Assumptions'!I45,'Assumptions'!I50,'Assumptions'!I53)</x:f>
+        <x:v>840000</x:v>
+      </x:c>
+      <x:c r="E50" s="21" t="n">
+        <x:f>D52</x:f>
+        <x:v>819667.3640500001</x:v>
+      </x:c>
+      <x:c r="F50" s="21" t="n">
+        <x:f>E52</x:f>
+        <x:v>814020.66971882</x:v>
+      </x:c>
+      <x:c r="G50" s="21" t="n">
+        <x:f>F52</x:f>
+        <x:v>797871.0971656215</x:v>
+      </x:c>
+      <x:c r="H50" s="21" t="n">
+        <x:f>G52</x:f>
+        <x:v>814596.3782657352</x:v>
+      </x:c>
+      <x:c r="I50" s="21" t="n">
+        <x:f>H52</x:f>
+        <x:v>852376.9332721551</x:v>
+      </x:c>
+      <x:c r="J50" s="1"/>
+      <x:c r="K50" s="1"/>
+      <x:c r="L50" s="1"/>
+    </x:row>
+    <x:row r="51" ht="22" customHeight="1">
+      <x:c r="A51" s="1"/>
+      <x:c r="B51" s="1"/>
+      <x:c r="C51" s="1" t="str">
+        <x:v>Net income to retained earnings</x:v>
+      </x:c>
+      <x:c r="D51" s="21" t="n">
+        <x:f>D23</x:f>
+        <x:v>-20332.635949999938</x:v>
+      </x:c>
+      <x:c r="E51" s="21" t="n">
+        <x:f>E23</x:f>
+        <x:v>-5646.694331180015</x:v>
+      </x:c>
+      <x:c r="F51" s="21" t="n">
+        <x:f>F23</x:f>
+        <x:v>-16149.57255319852</x:v>
+      </x:c>
+      <x:c r="G51" s="21" t="n">
+        <x:f>G23</x:f>
+        <x:v>16725.28110011376</x:v>
+      </x:c>
+      <x:c r="H51" s="21" t="n">
+        <x:f>H23</x:f>
+        <x:v>37780.555006419854</x:v>
+      </x:c>
+      <x:c r="I51" s="21" t="n">
+        <x:f>I23</x:f>
+        <x:v>47896.20585457757</x:v>
+      </x:c>
+      <x:c r="J51" s="1"/>
+      <x:c r="K51" s="1"/>
+      <x:c r="L51" s="1"/>
+    </x:row>
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="1"/>
+      <x:c r="B52" s="1"/>
+      <x:c r="C52" s="1" t="str">
+        <x:v>Closing retained earnings</x:v>
+      </x:c>
+      <x:c r="D52" s="21" t="n">
+        <x:f>SUM(D50:D51)</x:f>
+        <x:v>819667.3640500001</x:v>
+      </x:c>
+      <x:c r="E52" s="21" t="n">
+        <x:f>SUM(E50:E51)</x:f>
+        <x:v>814020.66971882</x:v>
+      </x:c>
+      <x:c r="F52" s="21" t="n">
+        <x:f>SUM(F50:F51)</x:f>
+        <x:v>797871.0971656215</x:v>
+      </x:c>
+      <x:c r="G52" s="21" t="n">
+        <x:f>SUM(G50:G51)</x:f>
+        <x:v>814596.3782657352</x:v>
+      </x:c>
+      <x:c r="H52" s="21" t="n">
+        <x:f>SUM(H50:H51)</x:f>
+        <x:v>852376.9332721551</x:v>
+      </x:c>
+      <x:c r="I52" s="21" t="n">
+        <x:f>SUM(I50:I51)</x:f>
+        <x:v>900273.1391267327</x:v>
+      </x:c>
+      <x:c r="J52" s="1"/>
+      <x:c r="K52" s="1"/>
+      <x:c r="L52" s="1"/>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="1"/>
+      <x:c r="B53" s="1"/>
+      <x:c r="C53" s="1" t="str">
+        <x:v>Total equity</x:v>
+      </x:c>
+      <x:c r="D53" s="21" t="n">
+        <x:f>SUM(D49,D52)</x:f>
+        <x:v>1319667.36405</x:v>
+      </x:c>
+      <x:c r="E53" s="21" t="n">
+        <x:f>SUM(E49,E52)</x:f>
+        <x:v>1314020.6697188201</x:v>
+      </x:c>
+      <x:c r="F53" s="21" t="n">
+        <x:f>SUM(F49,F52)</x:f>
+        <x:v>1297871.0971656214</x:v>
+      </x:c>
+      <x:c r="G53" s="21" t="n">
+        <x:f>SUM(G49,G52)</x:f>
+        <x:v>1314596.3782657352</x:v>
+      </x:c>
+      <x:c r="H53" s="21" t="n">
+        <x:f>SUM(H49,H52)</x:f>
+        <x:v>1352376.933272155</x:v>
+      </x:c>
+      <x:c r="I53" s="21" t="n">
+        <x:f>SUM(I49,I52)</x:f>
+        <x:v>1400273.1391267327</x:v>
+      </x:c>
+      <x:c r="J53" s="1"/>
+      <x:c r="K53" s="1"/>
+      <x:c r="L53" s="1"/>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="1"/>
+      <x:c r="B54" s="1"/>
+      <x:c r="C54" s="1" t="str">
+        <x:v>Liabilities and equity</x:v>
+      </x:c>
+      <x:c r="D54" s="21" t="n">
+        <x:f>SUM(D47,D53)</x:f>
+        <x:v>2157596.00405</x:v>
+      </x:c>
+      <x:c r="E54" s="21" t="n">
+        <x:f>SUM(E47,E53)</x:f>
+        <x:v>2158791.14493757</x:v>
+      </x:c>
+      <x:c r="F54" s="21" t="n">
+        <x:f>SUM(F47,F53)</x:f>
+        <x:v>2134532.07830359</x:v>
+      </x:c>
+      <x:c r="G54" s="21" t="n">
+        <x:f>SUM(G47,G53)</x:f>
+        <x:v>2170349.112190024</x:v>
+      </x:c>
+      <x:c r="H54" s="21" t="n">
+        <x:f>SUM(H47,H53)</x:f>
+        <x:v>2223337.383401611</x:v>
+      </x:c>
+      <x:c r="I54" s="21" t="n">
+        <x:f>SUM(I47,I53)</x:f>
+        <x:v>2285180.1563506853</x:v>
+      </x:c>
+      <x:c r="J54" s="1"/>
+      <x:c r="K54" s="1"/>
+      <x:c r="L54" s="1"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="1"/>
+      <x:c r="B55" s="1"/>
+      <x:c r="C55" s="1" t="str">
+        <x:v>Balance sheet difference</x:v>
+      </x:c>
+      <x:c r="D55" s="23" t="n">
+        <x:f>D43-D54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E55" s="23" t="n">
+        <x:f>E43-E54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F55" s="23" t="n">
+        <x:f>F43-F54</x:f>
+        <x:v>4.656612873077393e-10</x:v>
+      </x:c>
+      <x:c r="G55" s="23" t="n">
+        <x:f>G43-G54</x:f>
+        <x:v>4.656612873077393e-10</x:v>
+      </x:c>
+      <x:c r="H55" s="23" t="n">
+        <x:f>H43-H54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I55" s="23" t="n">
+        <x:f>I43-I54</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="J55" s="1"/>
+      <x:c r="K55" s="1"/>
+      <x:c r="L55" s="1"/>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="1"/>
+      <x:c r="B56" s="1"/>
+      <x:c r="C56" s="1"/>
+      <x:c r="D56" s="1"/>
+      <x:c r="E56" s="1"/>
+      <x:c r="F56" s="1"/>
+      <x:c r="G56" s="1"/>
+      <x:c r="H56" s="1"/>
+      <x:c r="I56" s="1"/>
+      <x:c r="J56" s="1"/>
+      <x:c r="K56" s="1"/>
+      <x:c r="L56" s="1"/>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="1"/>
+      <x:c r="B57" s="1"/>
+      <x:c r="C57" s="1"/>
+      <x:c r="D57" s="1"/>
+      <x:c r="E57" s="1"/>
+      <x:c r="F57" s="1"/>
+      <x:c r="G57" s="1"/>
+      <x:c r="H57" s="1"/>
+      <x:c r="I57" s="1"/>
+      <x:c r="J57" s="1"/>
+      <x:c r="K57" s="1"/>
+      <x:c r="L57" s="1"/>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="1"/>
+      <x:c r="B58" s="1"/>
+      <x:c r="C58" s="1"/>
+      <x:c r="D58" s="1"/>
+      <x:c r="E58" s="1"/>
+      <x:c r="F58" s="1"/>
+      <x:c r="G58" s="1"/>
+      <x:c r="H58" s="1"/>
+      <x:c r="I58" s="1"/>
+      <x:c r="J58" s="1"/>
+      <x:c r="K58" s="1"/>
+      <x:c r="L58" s="1"/>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="1"/>
+      <x:c r="B59" s="1"/>
+      <x:c r="C59" s="5" t="str">
+        <x:v>Simplified tax-loss offsets assume full usability. No deferred tax assets, inventory or dividends.</x:v>
+      </x:c>
+      <x:c r="D59" s="5"/>
+      <x:c r="E59" s="5"/>
+      <x:c r="F59" s="5"/>
+      <x:c r="G59" s="5"/>
+      <x:c r="H59" s="5"/>
+      <x:c r="I59" s="5"/>
+      <x:c r="J59" s="1"/>
+      <x:c r="K59" s="1"/>
+      <x:c r="L59" s="1"/>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="1"/>
+      <x:c r="B60" s="1"/>
+      <x:c r="C60" s="5"/>
+      <x:c r="D60" s="5"/>
+      <x:c r="E60" s="5"/>
+      <x:c r="F60" s="5"/>
+      <x:c r="G60" s="5"/>
+      <x:c r="H60" s="5"/>
+      <x:c r="I60" s="5"/>
+      <x:c r="J60" s="1"/>
+      <x:c r="K60" s="1"/>
+      <x:c r="L60" s="1"/>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="1"/>
+      <x:c r="B61" s="1"/>
+      <x:c r="C61" s="5"/>
+      <x:c r="D61" s="5"/>
+      <x:c r="E61" s="5"/>
+      <x:c r="F61" s="5"/>
+      <x:c r="G61" s="5"/>
+      <x:c r="H61" s="5"/>
+      <x:c r="I61" s="5"/>
+      <x:c r="J61" s="1"/>
+      <x:c r="K61" s="1"/>
+      <x:c r="L61" s="1"/>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="1"/>
+      <x:c r="B62" s="1"/>
+      <x:c r="C62" s="1"/>
+      <x:c r="D62" s="1"/>
+      <x:c r="E62" s="1"/>
+      <x:c r="F62" s="1"/>
+      <x:c r="G62" s="1"/>
+      <x:c r="H62" s="1"/>
+      <x:c r="I62" s="1"/>
+      <x:c r="J62" s="1"/>
+      <x:c r="K62" s="1"/>
+      <x:c r="L62" s="1"/>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="1"/>
+      <x:c r="B63" s="1"/>
+      <x:c r="C63" s="1"/>
+      <x:c r="D63" s="1"/>
+      <x:c r="E63" s="1"/>
+      <x:c r="F63" s="1"/>
+      <x:c r="G63" s="1"/>
+      <x:c r="H63" s="1"/>
+      <x:c r="I63" s="1"/>
+      <x:c r="J63" s="1"/>
+      <x:c r="K63" s="1"/>
+      <x:c r="L63" s="1"/>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="1"/>
+      <x:c r="B64" s="1"/>
+      <x:c r="C64" s="1"/>
+      <x:c r="D64" s="1"/>
+      <x:c r="E64" s="1"/>
+      <x:c r="F64" s="1"/>
+      <x:c r="G64" s="1"/>
+      <x:c r="H64" s="1"/>
+      <x:c r="I64" s="1"/>
+      <x:c r="J64" s="1"/>
+      <x:c r="K64" s="1"/>
+      <x:c r="L64" s="1"/>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="1"/>
+      <x:c r="B65" s="1"/>
+      <x:c r="C65" s="1"/>
+      <x:c r="D65" s="1"/>
+      <x:c r="E65" s="1"/>
+      <x:c r="F65" s="1"/>
+      <x:c r="G65" s="1"/>
+      <x:c r="H65" s="1"/>
+      <x:c r="I65" s="1"/>
+      <x:c r="J65" s="1"/>
+      <x:c r="K65" s="1"/>
+      <x:c r="L65" s="1"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="D4:F4"/>
+    <x:mergeCell ref="C59:I61"/>
+  </x:mergeCells>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="3" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="27" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="27" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="27" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="27" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="1"/>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="1"/>
+      <x:c r="E1" s="1"/>
+      <x:c r="F1" s="1"/>
+      <x:c r="G1" s="1"/>
+      <x:c r="H1" s="1"/>
+      <x:c r="I1" s="1"/>
+      <x:c r="J1" s="1"/>
+      <x:c r="K1" s="1"/>
+      <x:c r="L1" s="1"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="1"/>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="2" t="str">
+        <x:v>Decision ownership and approval</x:v>
+      </x:c>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
+      <x:c r="L2" s="1"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3"/>
+      <x:c r="I3" s="3"/>
+      <x:c r="J3" s="3"/>
+      <x:c r="K3" s="3"/>
+      <x:c r="L3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1" t="str">
+        <x:v>Roles and deadlines are proposed within a synthetic case.</x:v>
+      </x:c>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+      <x:c r="K4" s="1"/>
+      <x:c r="L4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="1"/>
+      <x:c r="B5" s="1"/>
+      <x:c r="C5" s="1"/>
+      <x:c r="D5" s="1"/>
+      <x:c r="E5" s="1"/>
+      <x:c r="F5" s="1"/>
+      <x:c r="G5" s="1"/>
+      <x:c r="H5" s="1"/>
+      <x:c r="I5" s="1"/>
+      <x:c r="J5" s="1"/>
+      <x:c r="K5" s="1"/>
+      <x:c r="L5" s="1"/>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="1"/>
+      <x:c r="B6" s="1"/>
+      <x:c r="C6" s="14" t="str">
+        <x:v>Action</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>Proposed owner</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>Due from approval</x:v>
+      </x:c>
+      <x:c r="F6" s="14" t="str">
+        <x:v>Trigger / evidence</x:v>
+      </x:c>
+      <x:c r="G6" s="14" t="str">
+        <x:v>Approval needed</x:v>
+      </x:c>
+      <x:c r="H6" s="14" t="str">
+        <x:v>Status</x:v>
+      </x:c>
+      <x:c r="I6" s="14" t="str">
+        <x:v>Evidence link</x:v>
+      </x:c>
+      <x:c r="J6" s="1"/>
+      <x:c r="K6" s="1"/>
+      <x:c r="L6" s="1"/>
+    </x:row>
+    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A7" s="1"/>
+      <x:c r="B7" s="1"/>
+      <x:c r="C7" s="5" t="str">
+        <x:v>Validate price and cost assumptions</x:v>
+      </x:c>
+      <x:c r="D7" s="5" t="str">
+        <x:v>Finance + Sales</x:v>
+      </x:c>
+      <x:c r="E7" s="5" t="str">
+        <x:v>Day 5</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="str">
+        <x:v>July driver variance reconciled</x:v>
+      </x:c>
+      <x:c r="G7" s="5" t="str">
+        <x:v>Finance lead</x:v>
+      </x:c>
+      <x:c r="H7" s="5" t="str">
+        <x:v>Proposed</x:v>
+      </x:c>
+      <x:c r="I7" s="5" t="str"/>
+      <x:c r="J7" s="1"/>
+      <x:c r="K7" s="1"/>
+      <x:c r="L7" s="1"/>
+    </x:row>
+    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A8" s="1"/>
+      <x:c r="B8" s="1"/>
+      <x:c r="C8" s="5" t="str">
+        <x:v>Review low-margin contracts</x:v>
+      </x:c>
+      <x:c r="D8" s="5" t="str">
+        <x:v>Commercial + Operations</x:v>
+      </x:c>
+      <x:c r="E8" s="5" t="str">
+        <x:v>Day 10</x:v>
+      </x:c>
+      <x:c r="F8" s="5" t="str">
+        <x:v>EBITDA margin below 3%</x:v>
+      </x:c>
+      <x:c r="G8" s="5" t="str">
+        <x:v>Commercial lead</x:v>
+      </x:c>
+      <x:c r="H8" s="5" t="str">
+        <x:v>Proposed</x:v>
+      </x:c>
+      <x:c r="I8" s="5" t="str"/>
+      <x:c r="J8" s="1"/>
+      <x:c r="K8" s="1"/>
+      <x:c r="L8" s="1"/>
+    </x:row>
+    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A9" s="1"/>
+      <x:c r="B9" s="1"/>
+      <x:c r="C9" s="5" t="str">
+        <x:v>Reforecast and approve actions</x:v>
+      </x:c>
+      <x:c r="D9" s="5" t="str">
+        <x:v>Finance lead</x:v>
+      </x:c>
+      <x:c r="E9" s="5" t="str">
+        <x:v>Monthly close + 5 days</x:v>
+      </x:c>
+      <x:c r="F9" s="5" t="str">
+        <x:v>Volume misses plan &gt;5%</x:v>
+      </x:c>
+      <x:c r="G9" s="5" t="str">
+        <x:v>Business unit lead</x:v>
+      </x:c>
+      <x:c r="H9" s="5" t="str">
+        <x:v>Proposed</x:v>
+      </x:c>
+      <x:c r="I9" s="5" t="str"/>
+      <x:c r="J9" s="1"/>
+      <x:c r="K9" s="1"/>
+      <x:c r="L9" s="1"/>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="1"/>
+      <x:c r="B10" s="1"/>
+      <x:c r="C10" s="5" t="str">
+        <x:v>Monitor cash and capex</x:v>
+      </x:c>
+      <x:c r="D10" s="5" t="str">
+        <x:v>Treasury + Operations</x:v>
+      </x:c>
+      <x:c r="E10" s="5" t="str">
+        <x:v>Weekly</x:v>
+      </x:c>
+      <x:c r="F10" s="5" t="str">
+        <x:v>Cash below $250,000</x:v>
+      </x:c>
+      <x:c r="G10" s="5" t="str">
+        <x:v>Finance lead</x:v>
+      </x:c>
+      <x:c r="H10" s="5" t="str">
+        <x:v>Proposed</x:v>
+      </x:c>
+      <x:c r="I10" s="5" t="str"/>
+      <x:c r="J10" s="1"/>
+      <x:c r="K10" s="1"/>
+      <x:c r="L10" s="1"/>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="1"/>
+      <x:c r="B11" s="1"/>
+      <x:c r="C11" s="1"/>
+      <x:c r="D11" s="1"/>
+      <x:c r="E11" s="1"/>
+      <x:c r="F11" s="1"/>
+      <x:c r="G11" s="1"/>
+      <x:c r="H11" s="1"/>
+      <x:c r="I11" s="1"/>
+      <x:c r="J11" s="1"/>
+      <x:c r="K11" s="1"/>
+      <x:c r="L11" s="1"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="1"/>
+      <x:c r="B12" s="1"/>
+      <x:c r="C12" s="1"/>
+      <x:c r="D12" s="1"/>
+      <x:c r="E12" s="1"/>
+      <x:c r="F12" s="1"/>
+      <x:c r="G12" s="1"/>
+      <x:c r="H12" s="1"/>
+      <x:c r="I12" s="1"/>
+      <x:c r="J12" s="1"/>
+      <x:c r="K12" s="1"/>
+      <x:c r="L12" s="1"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="1"/>
+      <x:c r="B13" s="1"/>
+      <x:c r="C13" s="1"/>
+      <x:c r="D13" s="1"/>
+      <x:c r="E13" s="1"/>
+      <x:c r="F13" s="1"/>
+      <x:c r="G13" s="1"/>
+      <x:c r="H13" s="1"/>
+      <x:c r="I13" s="1"/>
+      <x:c r="J13" s="1"/>
+      <x:c r="K13" s="1"/>
+      <x:c r="L13" s="1"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="1"/>
+      <x:c r="B14" s="1"/>
+      <x:c r="C14" s="1"/>
+      <x:c r="D14" s="1"/>
+      <x:c r="E14" s="1"/>
+      <x:c r="F14" s="1"/>
+      <x:c r="G14" s="1"/>
+      <x:c r="H14" s="1"/>
+      <x:c r="I14" s="1"/>
+      <x:c r="J14" s="1"/>
+      <x:c r="K14" s="1"/>
+      <x:c r="L14" s="1"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="1"/>
+      <x:c r="B15" s="1"/>
+      <x:c r="C15" s="1"/>
+      <x:c r="D15" s="1"/>
+      <x:c r="E15" s="1"/>
+      <x:c r="F15" s="1"/>
+      <x:c r="G15" s="1"/>
+      <x:c r="H15" s="1"/>
+      <x:c r="I15" s="1"/>
+      <x:c r="J15" s="1"/>
+      <x:c r="K15" s="1"/>
+      <x:c r="L15" s="1"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="1"/>
+      <x:c r="B16" s="1"/>
+      <x:c r="C16" s="1"/>
+      <x:c r="D16" s="1"/>
+      <x:c r="E16" s="1"/>
+      <x:c r="F16" s="1"/>
+      <x:c r="G16" s="1"/>
+      <x:c r="H16" s="1"/>
+      <x:c r="I16" s="1"/>
+      <x:c r="J16" s="1"/>
+      <x:c r="K16" s="1"/>
+      <x:c r="L16" s="1"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="1"/>
+      <x:c r="B17" s="1"/>
+      <x:c r="C17" s="1"/>
+      <x:c r="D17" s="1"/>
+      <x:c r="E17" s="1"/>
+      <x:c r="F17" s="1"/>
+      <x:c r="G17" s="1"/>
+      <x:c r="H17" s="1"/>
+      <x:c r="I17" s="1"/>
+      <x:c r="J17" s="1"/>
+      <x:c r="K17" s="1"/>
+      <x:c r="L17" s="1"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="1"/>
+      <x:c r="B18" s="1"/>
+      <x:c r="C18" s="1"/>
+      <x:c r="D18" s="1"/>
+      <x:c r="E18" s="1"/>
+      <x:c r="F18" s="1"/>
+      <x:c r="G18" s="1"/>
+      <x:c r="H18" s="1"/>
+      <x:c r="I18" s="1"/>
+      <x:c r="J18" s="1"/>
+      <x:c r="K18" s="1"/>
+      <x:c r="L18" s="1"/>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19" s="1"/>
+      <x:c r="B19" s="1"/>
+      <x:c r="C19" s="1"/>
+      <x:c r="D19" s="1"/>
+      <x:c r="E19" s="1"/>
+      <x:c r="F19" s="1"/>
+      <x:c r="G19" s="1"/>
+      <x:c r="H19" s="1"/>
+      <x:c r="I19" s="1"/>
+      <x:c r="J19" s="1"/>
+      <x:c r="K19" s="1"/>
+      <x:c r="L19" s="1"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="1"/>
+      <x:c r="B20" s="1"/>
+      <x:c r="C20" s="1"/>
+      <x:c r="D20" s="1"/>
+      <x:c r="E20" s="1"/>
+      <x:c r="F20" s="1"/>
+      <x:c r="G20" s="1"/>
+      <x:c r="H20" s="1"/>
+      <x:c r="I20" s="1"/>
+      <x:c r="J20" s="1"/>
+      <x:c r="K20" s="1"/>
+      <x:c r="L20" s="1"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="1"/>
+      <x:c r="B21" s="1"/>
+      <x:c r="C21" s="1"/>
+      <x:c r="D21" s="1"/>
+      <x:c r="E21" s="1"/>
+      <x:c r="F21" s="1"/>
+      <x:c r="G21" s="1"/>
+      <x:c r="H21" s="1"/>
+      <x:c r="I21" s="1"/>
+      <x:c r="J21" s="1"/>
+      <x:c r="K21" s="1"/>
+      <x:c r="L21" s="1"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="1"/>
+      <x:c r="B22" s="1"/>
+      <x:c r="C22" s="1"/>
+      <x:c r="D22" s="1"/>
+      <x:c r="E22" s="1"/>
+      <x:c r="F22" s="1"/>
+      <x:c r="G22" s="1"/>
+      <x:c r="H22" s="1"/>
+      <x:c r="I22" s="1"/>
+      <x:c r="J22" s="1"/>
+      <x:c r="K22" s="1"/>
+      <x:c r="L22" s="1"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="1"/>
+      <x:c r="B23" s="1"/>
+      <x:c r="C23" s="1"/>
+      <x:c r="D23" s="1"/>
+      <x:c r="E23" s="1"/>
+      <x:c r="F23" s="1"/>
+      <x:c r="G23" s="1"/>
+      <x:c r="H23" s="1"/>
+      <x:c r="I23" s="1"/>
+      <x:c r="J23" s="1"/>
+      <x:c r="K23" s="1"/>
+      <x:c r="L23" s="1"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="1"/>
+      <x:c r="D24" s="1"/>
+      <x:c r="E24" s="1"/>
+      <x:c r="F24" s="1"/>
+      <x:c r="G24" s="1"/>
+      <x:c r="H24" s="1"/>
+      <x:c r="I24" s="1"/>
+      <x:c r="J24" s="1"/>
+      <x:c r="K24" s="1"/>
+      <x:c r="L24" s="1"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="1"/>
+      <x:c r="B25" s="1"/>
+      <x:c r="C25" s="1"/>
+      <x:c r="D25" s="1"/>
+      <x:c r="E25" s="1"/>
+      <x:c r="F25" s="1"/>
+      <x:c r="G25" s="1"/>
+      <x:c r="H25" s="1"/>
+      <x:c r="I25" s="1"/>
+      <x:c r="J25" s="1"/>
+      <x:c r="K25" s="1"/>
+      <x:c r="L25" s="1"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="1"/>
+      <x:c r="D26" s="1"/>
+      <x:c r="E26" s="1"/>
+      <x:c r="F26" s="1"/>
+      <x:c r="G26" s="1"/>
+      <x:c r="H26" s="1"/>
+      <x:c r="I26" s="1"/>
+      <x:c r="J26" s="1"/>
+      <x:c r="K26" s="1"/>
+      <x:c r="L26" s="1"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="1"/>
+      <x:c r="B27" s="1"/>
+      <x:c r="C27" s="1"/>
+      <x:c r="D27" s="1"/>
+      <x:c r="E27" s="1"/>
+      <x:c r="F27" s="1"/>
+      <x:c r="G27" s="1"/>
+      <x:c r="H27" s="1"/>
+      <x:c r="I27" s="1"/>
+      <x:c r="J27" s="1"/>
+      <x:c r="K27" s="1"/>
+      <x:c r="L27" s="1"/>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" s="1"/>
+      <x:c r="B28" s="1"/>
+      <x:c r="C28" s="1"/>
+      <x:c r="D28" s="1"/>
+      <x:c r="E28" s="1"/>
+      <x:c r="F28" s="1"/>
+      <x:c r="G28" s="1"/>
+      <x:c r="H28" s="1"/>
+      <x:c r="I28" s="1"/>
+      <x:c r="J28" s="1"/>
+      <x:c r="K28" s="1"/>
+      <x:c r="L28" s="1"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" s="1"/>
+      <x:c r="B29" s="1"/>
+      <x:c r="C29" s="1"/>
+      <x:c r="D29" s="1"/>
+      <x:c r="E29" s="1"/>
+      <x:c r="F29" s="1"/>
+      <x:c r="G29" s="1"/>
+      <x:c r="H29" s="1"/>
+      <x:c r="I29" s="1"/>
+      <x:c r="J29" s="1"/>
+      <x:c r="K29" s="1"/>
+      <x:c r="L29" s="1"/>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
+      <x:c r="A30" s="1"/>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="1"/>
+      <x:c r="D30" s="1"/>
+      <x:c r="E30" s="1"/>
+      <x:c r="F30" s="1"/>
+      <x:c r="G30" s="1"/>
+      <x:c r="H30" s="1"/>
+      <x:c r="I30" s="1"/>
+      <x:c r="J30" s="1"/>
+      <x:c r="K30" s="1"/>
+      <x:c r="L30" s="1"/>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
+      <x:c r="A31" s="1"/>
+      <x:c r="B31" s="1"/>
+      <x:c r="C31" s="1"/>
+      <x:c r="D31" s="1"/>
+      <x:c r="E31" s="1"/>
+      <x:c r="F31" s="1"/>
+      <x:c r="G31" s="1"/>
+      <x:c r="H31" s="1"/>
+      <x:c r="I31" s="1"/>
+      <x:c r="J31" s="1"/>
+      <x:c r="K31" s="1"/>
+      <x:c r="L31" s="1"/>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
+      <x:c r="A32" s="1"/>
+      <x:c r="B32" s="1"/>
+      <x:c r="C32" s="1"/>
+      <x:c r="D32" s="1"/>
+      <x:c r="E32" s="1"/>
+      <x:c r="F32" s="1"/>
+      <x:c r="G32" s="1"/>
+      <x:c r="H32" s="1"/>
+      <x:c r="I32" s="1"/>
+      <x:c r="J32" s="1"/>
+      <x:c r="K32" s="1"/>
+      <x:c r="L32" s="1"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="1"/>
+      <x:c r="B33" s="1"/>
+      <x:c r="C33" s="1"/>
+      <x:c r="D33" s="1"/>
+      <x:c r="E33" s="1"/>
+      <x:c r="F33" s="1"/>
+      <x:c r="G33" s="1"/>
+      <x:c r="H33" s="1"/>
+      <x:c r="I33" s="1"/>
+      <x:c r="J33" s="1"/>
+      <x:c r="K33" s="1"/>
+      <x:c r="L33" s="1"/>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="1"/>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="1"/>
+      <x:c r="D34" s="1"/>
+      <x:c r="E34" s="1"/>
+      <x:c r="F34" s="1"/>
+      <x:c r="G34" s="1"/>
+      <x:c r="H34" s="1"/>
+      <x:c r="I34" s="1"/>
+      <x:c r="J34" s="1"/>
+      <x:c r="K34" s="1"/>
+      <x:c r="L34" s="1"/>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35" s="1"/>
+      <x:c r="B35" s="1"/>
+      <x:c r="C35" s="1"/>
+      <x:c r="D35" s="1"/>
+      <x:c r="E35" s="1"/>
+      <x:c r="F35" s="1"/>
+      <x:c r="G35" s="1"/>
+      <x:c r="H35" s="1"/>
+      <x:c r="I35" s="1"/>
+      <x:c r="J35" s="1"/>
+      <x:c r="K35" s="1"/>
+      <x:c r="L35" s="1"/>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36" s="1"/>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="1"/>
+      <x:c r="D36" s="1"/>
+      <x:c r="E36" s="1"/>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1"/>
+      <x:c r="H36" s="1"/>
+      <x:c r="I36" s="1"/>
+      <x:c r="J36" s="1"/>
+      <x:c r="K36" s="1"/>
+      <x:c r="L36" s="1"/>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="1"/>
+      <x:c r="B37" s="1"/>
+      <x:c r="C37" s="1"/>
+      <x:c r="D37" s="1"/>
+      <x:c r="E37" s="1"/>
+      <x:c r="F37" s="1"/>
+      <x:c r="G37" s="1"/>
+      <x:c r="H37" s="1"/>
+      <x:c r="I37" s="1"/>
+      <x:c r="J37" s="1"/>
+      <x:c r="K37" s="1"/>
+      <x:c r="L37" s="1"/>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="1"/>
+      <x:c r="B38" s="1"/>
+      <x:c r="C38" s="1"/>
+      <x:c r="D38" s="1"/>
+      <x:c r="E38" s="1"/>
+      <x:c r="F38" s="1"/>
+      <x:c r="G38" s="1"/>
+      <x:c r="H38" s="1"/>
+      <x:c r="I38" s="1"/>
+      <x:c r="J38" s="1"/>
+      <x:c r="K38" s="1"/>
+      <x:c r="L38" s="1"/>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
+      <x:c r="A39" s="1"/>
+      <x:c r="B39" s="1"/>
+      <x:c r="C39" s="1"/>
+      <x:c r="D39" s="1"/>
+      <x:c r="E39" s="1"/>
+      <x:c r="F39" s="1"/>
+      <x:c r="G39" s="1"/>
+      <x:c r="H39" s="1"/>
+      <x:c r="I39" s="1"/>
+      <x:c r="J39" s="1"/>
+      <x:c r="K39" s="1"/>
+      <x:c r="L39" s="1"/>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
+      <x:c r="A40" s="1"/>
+      <x:c r="B40" s="1"/>
+      <x:c r="C40" s="1"/>
+      <x:c r="D40" s="1"/>
+      <x:c r="E40" s="1"/>
+      <x:c r="F40" s="1"/>
+      <x:c r="G40" s="1"/>
+      <x:c r="H40" s="1"/>
+      <x:c r="I40" s="1"/>
+      <x:c r="J40" s="1"/>
+      <x:c r="K40" s="1"/>
+      <x:c r="L40" s="1"/>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
+      <x:c r="A41" s="1"/>
+      <x:c r="B41" s="1"/>
+      <x:c r="C41" s="1"/>
+      <x:c r="D41" s="1"/>
+      <x:c r="E41" s="1"/>
+      <x:c r="F41" s="1"/>
+      <x:c r="G41" s="1"/>
+      <x:c r="H41" s="1"/>
+      <x:c r="I41" s="1"/>
+      <x:c r="J41" s="1"/>
+      <x:c r="K41" s="1"/>
+      <x:c r="L41" s="1"/>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
+      <x:c r="A42" s="1"/>
+      <x:c r="B42" s="1"/>
+      <x:c r="C42" s="1"/>
+      <x:c r="D42" s="1"/>
+      <x:c r="E42" s="1"/>
+      <x:c r="F42" s="1"/>
+      <x:c r="G42" s="1"/>
+      <x:c r="H42" s="1"/>
+      <x:c r="I42" s="1"/>
+      <x:c r="J42" s="1"/>
+      <x:c r="K42" s="1"/>
+      <x:c r="L42" s="1"/>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
+      <x:c r="A43" s="1"/>
+      <x:c r="B43" s="1"/>
+      <x:c r="C43" s="1"/>
+      <x:c r="D43" s="1"/>
+      <x:c r="E43" s="1"/>
+      <x:c r="F43" s="1"/>
+      <x:c r="G43" s="1"/>
+      <x:c r="H43" s="1"/>
+      <x:c r="I43" s="1"/>
+      <x:c r="J43" s="1"/>
+      <x:c r="K43" s="1"/>
+      <x:c r="L43" s="1"/>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
+      <x:c r="A44" s="1"/>
+      <x:c r="B44" s="1"/>
+      <x:c r="C44" s="1"/>
+      <x:c r="D44" s="1"/>
+      <x:c r="E44" s="1"/>
+      <x:c r="F44" s="1"/>
+      <x:c r="G44" s="1"/>
+      <x:c r="H44" s="1"/>
+      <x:c r="I44" s="1"/>
+      <x:c r="J44" s="1"/>
+      <x:c r="K44" s="1"/>
+      <x:c r="L44" s="1"/>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="1"/>
+      <x:c r="B45" s="1"/>
+      <x:c r="C45" s="1"/>
+      <x:c r="D45" s="1"/>
+      <x:c r="E45" s="1"/>
+      <x:c r="F45" s="1"/>
+      <x:c r="G45" s="1"/>
+      <x:c r="H45" s="1"/>
+      <x:c r="I45" s="1"/>
+      <x:c r="J45" s="1"/>
+      <x:c r="K45" s="1"/>
+      <x:c r="L45" s="1"/>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
+      <x:c r="A46" s="1"/>
+      <x:c r="B46" s="1"/>
+      <x:c r="C46" s="1"/>
+      <x:c r="D46" s="1"/>
+      <x:c r="E46" s="1"/>
+      <x:c r="F46" s="1"/>
+      <x:c r="G46" s="1"/>
+      <x:c r="H46" s="1"/>
+      <x:c r="I46" s="1"/>
+      <x:c r="J46" s="1"/>
+      <x:c r="K46" s="1"/>
+      <x:c r="L46" s="1"/>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="1"/>
+      <x:c r="B47" s="1"/>
+      <x:c r="C47" s="1"/>
+      <x:c r="D47" s="1"/>
+      <x:c r="E47" s="1"/>
+      <x:c r="F47" s="1"/>
+      <x:c r="G47" s="1"/>
+      <x:c r="H47" s="1"/>
+      <x:c r="I47" s="1"/>
+      <x:c r="J47" s="1"/>
+      <x:c r="K47" s="1"/>
+      <x:c r="L47" s="1"/>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
+      <x:c r="A48" s="1"/>
+      <x:c r="B48" s="1"/>
+      <x:c r="C48" s="1"/>
+      <x:c r="D48" s="1"/>
+      <x:c r="E48" s="1"/>
+      <x:c r="F48" s="1"/>
+      <x:c r="G48" s="1"/>
+      <x:c r="H48" s="1"/>
+      <x:c r="I48" s="1"/>
+      <x:c r="J48" s="1"/>
+      <x:c r="K48" s="1"/>
+      <x:c r="L48" s="1"/>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="1"/>
+      <x:c r="B49" s="1"/>
+      <x:c r="C49" s="1"/>
+      <x:c r="D49" s="1"/>
+      <x:c r="E49" s="1"/>
+      <x:c r="F49" s="1"/>
+      <x:c r="G49" s="1"/>
+      <x:c r="H49" s="1"/>
+      <x:c r="I49" s="1"/>
+      <x:c r="J49" s="1"/>
+      <x:c r="K49" s="1"/>
+      <x:c r="L49" s="1"/>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="1"/>
+      <x:c r="B50" s="1"/>
+      <x:c r="C50" s="1"/>
+      <x:c r="D50" s="1"/>
+      <x:c r="E50" s="1"/>
+      <x:c r="F50" s="1"/>
+      <x:c r="G50" s="1"/>
+      <x:c r="H50" s="1"/>
+      <x:c r="I50" s="1"/>
+      <x:c r="J50" s="1"/>
+      <x:c r="K50" s="1"/>
+      <x:c r="L50" s="1"/>
+    </x:row>
+    <x:row r="51" ht="22" customHeight="1">
+      <x:c r="A51" s="1"/>
+      <x:c r="B51" s="1"/>
+      <x:c r="C51" s="1"/>
+      <x:c r="D51" s="1"/>
+      <x:c r="E51" s="1"/>
+      <x:c r="F51" s="1"/>
+      <x:c r="G51" s="1"/>
+      <x:c r="H51" s="1"/>
+      <x:c r="I51" s="1"/>
+      <x:c r="J51" s="1"/>
+      <x:c r="K51" s="1"/>
+      <x:c r="L51" s="1"/>
+    </x:row>
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="1"/>
+      <x:c r="B52" s="1"/>
+      <x:c r="C52" s="1"/>
+      <x:c r="D52" s="1"/>
+      <x:c r="E52" s="1"/>
+      <x:c r="F52" s="1"/>
+      <x:c r="G52" s="1"/>
+      <x:c r="H52" s="1"/>
+      <x:c r="I52" s="1"/>
+      <x:c r="J52" s="1"/>
+      <x:c r="K52" s="1"/>
+      <x:c r="L52" s="1"/>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="1"/>
+      <x:c r="B53" s="1"/>
+      <x:c r="C53" s="1"/>
+      <x:c r="D53" s="1"/>
+      <x:c r="E53" s="1"/>
+      <x:c r="F53" s="1"/>
+      <x:c r="G53" s="1"/>
+      <x:c r="H53" s="1"/>
+      <x:c r="I53" s="1"/>
+      <x:c r="J53" s="1"/>
+      <x:c r="K53" s="1"/>
+      <x:c r="L53" s="1"/>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="1"/>
+      <x:c r="B54" s="1"/>
+      <x:c r="C54" s="1"/>
+      <x:c r="D54" s="1"/>
+      <x:c r="E54" s="1"/>
+      <x:c r="F54" s="1"/>
+      <x:c r="G54" s="1"/>
+      <x:c r="H54" s="1"/>
+      <x:c r="I54" s="1"/>
+      <x:c r="J54" s="1"/>
+      <x:c r="K54" s="1"/>
+      <x:c r="L54" s="1"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="1"/>
+      <x:c r="B55" s="1"/>
+      <x:c r="C55" s="1"/>
+      <x:c r="D55" s="1"/>
+      <x:c r="E55" s="1"/>
+      <x:c r="F55" s="1"/>
+      <x:c r="G55" s="1"/>
+      <x:c r="H55" s="1"/>
+      <x:c r="I55" s="1"/>
+      <x:c r="J55" s="1"/>
+      <x:c r="K55" s="1"/>
+      <x:c r="L55" s="1"/>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="1"/>
+      <x:c r="B56" s="1"/>
+      <x:c r="C56" s="1"/>
+      <x:c r="D56" s="1"/>
+      <x:c r="E56" s="1"/>
+      <x:c r="F56" s="1"/>
+      <x:c r="G56" s="1"/>
+      <x:c r="H56" s="1"/>
+      <x:c r="I56" s="1"/>
+      <x:c r="J56" s="1"/>
+      <x:c r="K56" s="1"/>
+      <x:c r="L56" s="1"/>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="1"/>
+      <x:c r="B57" s="1"/>
+      <x:c r="C57" s="1"/>
+      <x:c r="D57" s="1"/>
+      <x:c r="E57" s="1"/>
+      <x:c r="F57" s="1"/>
+      <x:c r="G57" s="1"/>
+      <x:c r="H57" s="1"/>
+      <x:c r="I57" s="1"/>
+      <x:c r="J57" s="1"/>
+      <x:c r="K57" s="1"/>
+      <x:c r="L57" s="1"/>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="1"/>
+      <x:c r="B58" s="1"/>
+      <x:c r="C58" s="1"/>
+      <x:c r="D58" s="1"/>
+      <x:c r="E58" s="1"/>
+      <x:c r="F58" s="1"/>
+      <x:c r="G58" s="1"/>
+      <x:c r="H58" s="1"/>
+      <x:c r="I58" s="1"/>
+      <x:c r="J58" s="1"/>
+      <x:c r="K58" s="1"/>
+      <x:c r="L58" s="1"/>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="1"/>
+      <x:c r="B59" s="1"/>
+      <x:c r="C59" s="1"/>
+      <x:c r="D59" s="1"/>
+      <x:c r="E59" s="1"/>
+      <x:c r="F59" s="1"/>
+      <x:c r="G59" s="1"/>
+      <x:c r="H59" s="1"/>
+      <x:c r="I59" s="1"/>
+      <x:c r="J59" s="1"/>
+      <x:c r="K59" s="1"/>
+      <x:c r="L59" s="1"/>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="1"/>
+      <x:c r="B60" s="1"/>
+      <x:c r="C60" s="1"/>
+      <x:c r="D60" s="1"/>
+      <x:c r="E60" s="1"/>
+      <x:c r="F60" s="1"/>
+      <x:c r="G60" s="1"/>
+      <x:c r="H60" s="1"/>
+      <x:c r="I60" s="1"/>
+      <x:c r="J60" s="1"/>
+      <x:c r="K60" s="1"/>
+      <x:c r="L60" s="1"/>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="1"/>
+      <x:c r="B61" s="1"/>
+      <x:c r="C61" s="1"/>
+      <x:c r="D61" s="1"/>
+      <x:c r="E61" s="1"/>
+      <x:c r="F61" s="1"/>
+      <x:c r="G61" s="1"/>
+      <x:c r="H61" s="1"/>
+      <x:c r="I61" s="1"/>
+      <x:c r="J61" s="1"/>
+      <x:c r="K61" s="1"/>
+      <x:c r="L61" s="1"/>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="1"/>
+      <x:c r="B62" s="1"/>
+      <x:c r="C62" s="1"/>
+      <x:c r="D62" s="1"/>
+      <x:c r="E62" s="1"/>
+      <x:c r="F62" s="1"/>
+      <x:c r="G62" s="1"/>
+      <x:c r="H62" s="1"/>
+      <x:c r="I62" s="1"/>
+      <x:c r="J62" s="1"/>
+      <x:c r="K62" s="1"/>
+      <x:c r="L62" s="1"/>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="1"/>
+      <x:c r="B63" s="1"/>
+      <x:c r="C63" s="1"/>
+      <x:c r="D63" s="1"/>
+      <x:c r="E63" s="1"/>
+      <x:c r="F63" s="1"/>
+      <x:c r="G63" s="1"/>
+      <x:c r="H63" s="1"/>
+      <x:c r="I63" s="1"/>
+      <x:c r="J63" s="1"/>
+      <x:c r="K63" s="1"/>
+      <x:c r="L63" s="1"/>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="1"/>
+      <x:c r="B64" s="1"/>
+      <x:c r="C64" s="1"/>
+      <x:c r="D64" s="1"/>
+      <x:c r="E64" s="1"/>
+      <x:c r="F64" s="1"/>
+      <x:c r="G64" s="1"/>
+      <x:c r="H64" s="1"/>
+      <x:c r="I64" s="1"/>
+      <x:c r="J64" s="1"/>
+      <x:c r="K64" s="1"/>
+      <x:c r="L64" s="1"/>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="1"/>
+      <x:c r="B65" s="1"/>
+      <x:c r="C65" s="1"/>
+      <x:c r="D65" s="1"/>
+      <x:c r="E65" s="1"/>
+      <x:c r="F65" s="1"/>
+      <x:c r="G65" s="1"/>
+      <x:c r="H65" s="1"/>
+      <x:c r="I65" s="1"/>
+      <x:c r="J65" s="1"/>
+      <x:c r="K65" s="1"/>
+      <x:c r="L65" s="1"/>
+    </x:row>
+  </x:sheetData>
+  <x:mergeCells>
+    <x:mergeCell ref="C4:I4"/>
+  </x:mergeCells>
+  <x:dataValidations count="1">
+    <x:dataValidation type="list" sqref="H7:H10">
+      <x:formula1>"Proposed,In progress,Completed,Blocked"</x:formula1>
+    </x:dataValidation>
+  </x:dataValidations>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="3" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="3" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="22" customHeight="1">
+      <x:c r="A1" s="1"/>
+      <x:c r="B1" s="1"/>
+      <x:c r="C1" s="1"/>
+      <x:c r="D1" s="1"/>
+      <x:c r="E1" s="1"/>
+      <x:c r="F1" s="1"/>
+      <x:c r="G1" s="1"/>
+      <x:c r="H1" s="1"/>
+      <x:c r="I1" s="1"/>
+      <x:c r="J1" s="1"/>
+      <x:c r="K1" s="1"/>
+      <x:c r="L1" s="1"/>
+    </x:row>
+    <x:row r="2" ht="22" customHeight="1">
+      <x:c r="A2" s="1"/>
+      <x:c r="B2" s="1"/>
+      <x:c r="C2" s="2" t="str">
+        <x:v>Reconciliation checks</x:v>
+      </x:c>
+      <x:c r="D2" s="1"/>
+      <x:c r="E2" s="1"/>
+      <x:c r="F2" s="1"/>
+      <x:c r="G2" s="1"/>
+      <x:c r="H2" s="1"/>
+      <x:c r="I2" s="1"/>
+      <x:c r="J2" s="1"/>
+      <x:c r="K2" s="1"/>
+      <x:c r="L2" s="1"/>
+    </x:row>
+    <x:row r="3" ht="22" customHeight="1">
+      <x:c r="A3" s="1"/>
+      <x:c r="B3" s="1"/>
+      <x:c r="C3" s="3"/>
+      <x:c r="D3" s="3"/>
+      <x:c r="E3" s="3"/>
+      <x:c r="F3" s="3"/>
+      <x:c r="G3" s="3"/>
+      <x:c r="H3" s="3"/>
+      <x:c r="I3" s="3"/>
+      <x:c r="J3" s="3"/>
+      <x:c r="K3" s="3"/>
+      <x:c r="L3" s="3"/>
+    </x:row>
+    <x:row r="4" ht="22" customHeight="1">
+      <x:c r="A4" s="1"/>
+      <x:c r="B4" s="1"/>
+      <x:c r="C4" s="1"/>
+      <x:c r="D4" s="1"/>
+      <x:c r="E4" s="1"/>
+      <x:c r="F4" s="1"/>
+      <x:c r="G4" s="1"/>
+      <x:c r="H4" s="1"/>
+      <x:c r="I4" s="1"/>
+      <x:c r="J4" s="1"/>
+      <x:c r="K4" s="1"/>
+      <x:c r="L4" s="1"/>
+    </x:row>
+    <x:row r="5" ht="22" customHeight="1">
+      <x:c r="A5" s="1"/>
+      <x:c r="B5" s="1"/>
+      <x:c r="C5" s="1"/>
+      <x:c r="D5" s="1"/>
+      <x:c r="E5" s="1"/>
+      <x:c r="F5" s="1"/>
+      <x:c r="G5" s="1"/>
+      <x:c r="H5" s="1"/>
+      <x:c r="I5" s="1"/>
+      <x:c r="J5" s="1"/>
+      <x:c r="K5" s="1"/>
+      <x:c r="L5" s="1"/>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="1"/>
+      <x:c r="B6" s="1"/>
+      <x:c r="C6" s="14" t="str">
+        <x:v>Check</x:v>
+      </x:c>
+      <x:c r="D6" s="14" t="str">
+        <x:v>Difference</x:v>
+      </x:c>
+      <x:c r="E6" s="14" t="str">
+        <x:v>Tolerance (USD)</x:v>
+      </x:c>
+      <x:c r="F6" s="1"/>
+      <x:c r="G6" s="1"/>
+      <x:c r="H6" s="1"/>
+      <x:c r="I6" s="1"/>
+      <x:c r="J6" s="1"/>
+      <x:c r="K6" s="1"/>
+      <x:c r="L6" s="1"/>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="1"/>
+      <x:c r="B7" s="1"/>
+      <x:c r="C7" s="5" t="str">
+        <x:v>July bridge</x:v>
+      </x:c>
+      <x:c r="D7" s="18" t="n">
+        <x:f>'Variance'!D13-'Variance'!D12-'Variance'!D14</x:f>
+        <x:v>1.291482476517558e-10</x:v>
+      </x:c>
+      <x:c r="E7" s="18" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="F7" s="1"/>
+      <x:c r="G7" s="1"/>
+      <x:c r="H7" s="1"/>
+      <x:c r="I7" s="1"/>
+      <x:c r="J7" s="1"/>
+      <x:c r="K7" s="1"/>
+      <x:c r="L7" s="1"/>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="1"/>
+      <x:c r="B8" s="1"/>
+      <x:c r="C8" s="5" t="str">
+        <x:v>Cash roll-forward</x:v>
+      </x:c>
+      <x:c r="D8" s="18" t="n">
+        <x:f>'Monthly'!O22-'Assumptions'!I56-SUM('Monthly'!J20:O20)</x:f>
+        <x:v>2.9103830456733704e-11</x:v>
+      </x:c>
+      <x:c r="E8" s="18" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="F8" s="1"/>
+      <x:c r="G8" s="1"/>
+      <x:c r="H8" s="1"/>
+      <x:c r="I8" s="1"/>
+      <x:c r="J8" s="1"/>
+      <x:c r="K8" s="1"/>
+      <x:c r="L8" s="1"/>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="1"/>
+      <x:c r="B9" s="1"/>
+      <x:c r="C9" s="5" t="str">
+        <x:v>H1 revenue to raw inputs</x:v>
+      </x:c>
+      <x:c r="D9" s="18" t="n">
+        <x:f>SUM('Monthly'!D7:I7)-SUMPRODUCT('Source'!E7:E24,'Source'!F7:F24)</x:f>
+        <x:v>-9.313225746154785e-10</x:v>
+      </x:c>
+      <x:c r="E9" s="18" t="n">
+        <x:v>0.01</x:v>
+      </x:c>
+      <x:c r="F9" s="1"/>
+      <x:c r="G9" s="1"/>
+      <x:c r="H9" s="1"/>
+      <x:c r="I9" s="1"/>
+      <x:c r="J9" s="1"/>
+      <x:c r="K9" s="1"/>
+      <x:c r="L9" s="1"/>
+    </x:row>
+    <x:row r="10" ht="22" customHeight="1">
+      <x:c r="A10" s="1"/>
+      <x:c r="B10" s="1"/>
+      <x:c r="C10" s="1"/>
+      <x:c r="D10" s="1"/>
+      <x:c r="E10" s="1"/>
+      <x:c r="F10" s="1"/>
+      <x:c r="G10" s="1"/>
+      <x:c r="H10" s="1"/>
+      <x:c r="I10" s="1"/>
+      <x:c r="J10" s="1"/>
+      <x:c r="K10" s="1"/>
+      <x:c r="L10" s="1"/>
+    </x:row>
+    <x:row r="11" ht="22" customHeight="1">
+      <x:c r="A11" s="1"/>
+      <x:c r="B11" s="1"/>
+      <x:c r="C11" s="1"/>
+      <x:c r="D11" s="1"/>
+      <x:c r="E11" s="1"/>
+      <x:c r="F11" s="1"/>
+      <x:c r="G11" s="1"/>
+      <x:c r="H11" s="1"/>
+      <x:c r="I11" s="1"/>
+      <x:c r="J11" s="1"/>
+      <x:c r="K11" s="1"/>
+      <x:c r="L11" s="1"/>
+    </x:row>
+    <x:row r="12" ht="22" customHeight="1">
+      <x:c r="A12" s="1"/>
+      <x:c r="B12" s="1"/>
+      <x:c r="C12" s="1"/>
+      <x:c r="D12" s="1"/>
+      <x:c r="E12" s="1"/>
+      <x:c r="F12" s="1"/>
+      <x:c r="G12" s="1"/>
+      <x:c r="H12" s="1"/>
+      <x:c r="I12" s="1"/>
+      <x:c r="J12" s="1"/>
+      <x:c r="K12" s="1"/>
+      <x:c r="L12" s="1"/>
+    </x:row>
+    <x:row r="13" ht="22" customHeight="1">
+      <x:c r="A13" s="1"/>
+      <x:c r="B13" s="1"/>
+      <x:c r="C13" s="1"/>
+      <x:c r="D13" s="1"/>
+      <x:c r="E13" s="1"/>
+      <x:c r="F13" s="1"/>
+      <x:c r="G13" s="1"/>
+      <x:c r="H13" s="1"/>
+      <x:c r="I13" s="1"/>
+      <x:c r="J13" s="1"/>
+      <x:c r="K13" s="1"/>
+      <x:c r="L13" s="1"/>
+    </x:row>
+    <x:row r="14" ht="22" customHeight="1">
+      <x:c r="A14" s="1"/>
+      <x:c r="B14" s="1"/>
+      <x:c r="C14" s="1"/>
+      <x:c r="D14" s="1"/>
+      <x:c r="E14" s="1"/>
+      <x:c r="F14" s="1"/>
+      <x:c r="G14" s="1"/>
+      <x:c r="H14" s="1"/>
+      <x:c r="I14" s="1"/>
+      <x:c r="J14" s="1"/>
+      <x:c r="K14" s="1"/>
+      <x:c r="L14" s="1"/>
+    </x:row>
+    <x:row r="15" ht="22" customHeight="1">
+      <x:c r="A15" s="1"/>
+      <x:c r="B15" s="1"/>
+      <x:c r="C15" s="1"/>
+      <x:c r="D15" s="1"/>
+      <x:c r="E15" s="1"/>
+      <x:c r="F15" s="1"/>
+      <x:c r="G15" s="1"/>
+      <x:c r="H15" s="1"/>
+      <x:c r="I15" s="1"/>
+      <x:c r="J15" s="1"/>
+      <x:c r="K15" s="1"/>
+      <x:c r="L15" s="1"/>
+    </x:row>
+    <x:row r="16" ht="22" customHeight="1">
+      <x:c r="A16" s="1"/>
+      <x:c r="B16" s="1"/>
+      <x:c r="C16" s="1"/>
+      <x:c r="D16" s="1"/>
+      <x:c r="E16" s="1"/>
+      <x:c r="F16" s="1"/>
+      <x:c r="G16" s="1"/>
+      <x:c r="H16" s="1"/>
+      <x:c r="I16" s="1"/>
+      <x:c r="J16" s="1"/>
+      <x:c r="K16" s="1"/>
+      <x:c r="L16" s="1"/>
+    </x:row>
+    <x:row r="17" ht="22" customHeight="1">
+      <x:c r="A17" s="1"/>
+      <x:c r="B17" s="1"/>
+      <x:c r="C17" s="1"/>
+      <x:c r="D17" s="1"/>
+      <x:c r="E17" s="1"/>
+      <x:c r="F17" s="1"/>
+      <x:c r="G17" s="1"/>
+      <x:c r="H17" s="1"/>
+      <x:c r="I17" s="1"/>
+      <x:c r="J17" s="1"/>
+      <x:c r="K17" s="1"/>
+      <x:c r="L17" s="1"/>
+    </x:row>
+    <x:row r="18" ht="22" customHeight="1">
+      <x:c r="A18" s="1"/>
+      <x:c r="B18" s="1"/>
+      <x:c r="C18" s="1"/>
+      <x:c r="D18" s="1"/>
+      <x:c r="E18" s="1"/>
+      <x:c r="F18" s="1"/>
+      <x:c r="G18" s="1"/>
+      <x:c r="H18" s="1"/>
+      <x:c r="I18" s="1"/>
+      <x:c r="J18" s="1"/>
+      <x:c r="K18" s="1"/>
+      <x:c r="L18" s="1"/>
+    </x:row>
+    <x:row r="19" ht="22" customHeight="1">
+      <x:c r="A19" s="1"/>
+      <x:c r="B19" s="1"/>
+      <x:c r="C19" s="1"/>
+      <x:c r="D19" s="1"/>
+      <x:c r="E19" s="1"/>
+      <x:c r="F19" s="1"/>
+      <x:c r="G19" s="1"/>
+      <x:c r="H19" s="1"/>
+      <x:c r="I19" s="1"/>
+      <x:c r="J19" s="1"/>
+      <x:c r="K19" s="1"/>
+      <x:c r="L19" s="1"/>
+    </x:row>
+    <x:row r="20" ht="22" customHeight="1">
+      <x:c r="A20" s="1"/>
+      <x:c r="B20" s="1"/>
+      <x:c r="C20" s="1"/>
+      <x:c r="D20" s="1"/>
+      <x:c r="E20" s="1"/>
+      <x:c r="F20" s="1"/>
+      <x:c r="G20" s="1"/>
+      <x:c r="H20" s="1"/>
+      <x:c r="I20" s="1"/>
+      <x:c r="J20" s="1"/>
+      <x:c r="K20" s="1"/>
+      <x:c r="L20" s="1"/>
+    </x:row>
+    <x:row r="21" ht="22" customHeight="1">
+      <x:c r="A21" s="1"/>
+      <x:c r="B21" s="1"/>
+      <x:c r="C21" s="1"/>
+      <x:c r="D21" s="1"/>
+      <x:c r="E21" s="1"/>
+      <x:c r="F21" s="1"/>
+      <x:c r="G21" s="1"/>
+      <x:c r="H21" s="1"/>
+      <x:c r="I21" s="1"/>
+      <x:c r="J21" s="1"/>
+      <x:c r="K21" s="1"/>
+      <x:c r="L21" s="1"/>
+    </x:row>
+    <x:row r="22" ht="22" customHeight="1">
+      <x:c r="A22" s="1"/>
+      <x:c r="B22" s="1"/>
+      <x:c r="C22" s="1"/>
+      <x:c r="D22" s="1"/>
+      <x:c r="E22" s="1"/>
+      <x:c r="F22" s="1"/>
+      <x:c r="G22" s="1"/>
+      <x:c r="H22" s="1"/>
+      <x:c r="I22" s="1"/>
+      <x:c r="J22" s="1"/>
+      <x:c r="K22" s="1"/>
+      <x:c r="L22" s="1"/>
+    </x:row>
+    <x:row r="23" ht="22" customHeight="1">
+      <x:c r="A23" s="1"/>
+      <x:c r="B23" s="1"/>
+      <x:c r="C23" s="1"/>
+      <x:c r="D23" s="1"/>
+      <x:c r="E23" s="1"/>
+      <x:c r="F23" s="1"/>
+      <x:c r="G23" s="1"/>
+      <x:c r="H23" s="1"/>
+      <x:c r="I23" s="1"/>
+      <x:c r="J23" s="1"/>
+      <x:c r="K23" s="1"/>
+      <x:c r="L23" s="1"/>
+    </x:row>
+    <x:row r="24" ht="22" customHeight="1">
+      <x:c r="A24" s="1"/>
+      <x:c r="B24" s="1"/>
+      <x:c r="C24" s="1"/>
+      <x:c r="D24" s="1"/>
+      <x:c r="E24" s="1"/>
+      <x:c r="F24" s="1"/>
+      <x:c r="G24" s="1"/>
+      <x:c r="H24" s="1"/>
+      <x:c r="I24" s="1"/>
+      <x:c r="J24" s="1"/>
+      <x:c r="K24" s="1"/>
+      <x:c r="L24" s="1"/>
+    </x:row>
+    <x:row r="25" ht="22" customHeight="1">
+      <x:c r="A25" s="1"/>
+      <x:c r="B25" s="1"/>
+      <x:c r="C25" s="1"/>
+      <x:c r="D25" s="1"/>
+      <x:c r="E25" s="1"/>
+      <x:c r="F25" s="1"/>
+      <x:c r="G25" s="1"/>
+      <x:c r="H25" s="1"/>
+      <x:c r="I25" s="1"/>
+      <x:c r="J25" s="1"/>
+      <x:c r="K25" s="1"/>
+      <x:c r="L25" s="1"/>
+    </x:row>
+    <x:row r="26" ht="22" customHeight="1">
+      <x:c r="A26" s="1"/>
+      <x:c r="B26" s="1"/>
+      <x:c r="C26" s="1"/>
+      <x:c r="D26" s="1"/>
+      <x:c r="E26" s="1"/>
+      <x:c r="F26" s="1"/>
+      <x:c r="G26" s="1"/>
+      <x:c r="H26" s="1"/>
+      <x:c r="I26" s="1"/>
+      <x:c r="J26" s="1"/>
+      <x:c r="K26" s="1"/>
+      <x:c r="L26" s="1"/>
+    </x:row>
+    <x:row r="27" ht="22" customHeight="1">
+      <x:c r="A27" s="1"/>
+      <x:c r="B27" s="1"/>
+      <x:c r="C27" s="1"/>
+      <x:c r="D27" s="1"/>
+      <x:c r="E27" s="1"/>
+      <x:c r="F27" s="1"/>
+      <x:c r="G27" s="1"/>
+      <x:c r="H27" s="1"/>
+      <x:c r="I27" s="1"/>
+      <x:c r="J27" s="1"/>
+      <x:c r="K27" s="1"/>
+      <x:c r="L27" s="1"/>
+    </x:row>
+    <x:row r="28" ht="22" customHeight="1">
+      <x:c r="A28" s="1"/>
+      <x:c r="B28" s="1"/>
+      <x:c r="C28" s="1"/>
+      <x:c r="D28" s="1"/>
+      <x:c r="E28" s="1"/>
+      <x:c r="F28" s="1"/>
+      <x:c r="G28" s="1"/>
+      <x:c r="H28" s="1"/>
+      <x:c r="I28" s="1"/>
+      <x:c r="J28" s="1"/>
+      <x:c r="K28" s="1"/>
+      <x:c r="L28" s="1"/>
+    </x:row>
+    <x:row r="29" ht="22" customHeight="1">
+      <x:c r="A29" s="1"/>
+      <x:c r="B29" s="1"/>
+      <x:c r="C29" s="1"/>
+      <x:c r="D29" s="1"/>
+      <x:c r="E29" s="1"/>
+      <x:c r="F29" s="1"/>
+      <x:c r="G29" s="1"/>
+      <x:c r="H29" s="1"/>
+      <x:c r="I29" s="1"/>
+      <x:c r="J29" s="1"/>
+      <x:c r="K29" s="1"/>
+      <x:c r="L29" s="1"/>
+    </x:row>
+    <x:row r="30" ht="22" customHeight="1">
+      <x:c r="A30" s="1"/>
+      <x:c r="B30" s="1"/>
+      <x:c r="C30" s="1"/>
+      <x:c r="D30" s="1"/>
+      <x:c r="E30" s="1"/>
+      <x:c r="F30" s="1"/>
+      <x:c r="G30" s="1"/>
+      <x:c r="H30" s="1"/>
+      <x:c r="I30" s="1"/>
+      <x:c r="J30" s="1"/>
+      <x:c r="K30" s="1"/>
+      <x:c r="L30" s="1"/>
+    </x:row>
+    <x:row r="31" ht="22" customHeight="1">
+      <x:c r="A31" s="1"/>
+      <x:c r="B31" s="1"/>
+      <x:c r="C31" s="1"/>
+      <x:c r="D31" s="1"/>
+      <x:c r="E31" s="1"/>
+      <x:c r="F31" s="1"/>
+      <x:c r="G31" s="1"/>
+      <x:c r="H31" s="1"/>
+      <x:c r="I31" s="1"/>
+      <x:c r="J31" s="1"/>
+      <x:c r="K31" s="1"/>
+      <x:c r="L31" s="1"/>
+    </x:row>
+    <x:row r="32" ht="22" customHeight="1">
+      <x:c r="A32" s="1"/>
+      <x:c r="B32" s="1"/>
+      <x:c r="C32" s="1"/>
+      <x:c r="D32" s="1"/>
+      <x:c r="E32" s="1"/>
+      <x:c r="F32" s="1"/>
+      <x:c r="G32" s="1"/>
+      <x:c r="H32" s="1"/>
+      <x:c r="I32" s="1"/>
+      <x:c r="J32" s="1"/>
+      <x:c r="K32" s="1"/>
+      <x:c r="L32" s="1"/>
+    </x:row>
+    <x:row r="33" ht="22" customHeight="1">
+      <x:c r="A33" s="1"/>
+      <x:c r="B33" s="1"/>
+      <x:c r="C33" s="1"/>
+      <x:c r="D33" s="1"/>
+      <x:c r="E33" s="1"/>
+      <x:c r="F33" s="1"/>
+      <x:c r="G33" s="1"/>
+      <x:c r="H33" s="1"/>
+      <x:c r="I33" s="1"/>
+      <x:c r="J33" s="1"/>
+      <x:c r="K33" s="1"/>
+      <x:c r="L33" s="1"/>
+    </x:row>
+    <x:row r="34" ht="22" customHeight="1">
+      <x:c r="A34" s="1"/>
+      <x:c r="B34" s="1"/>
+      <x:c r="C34" s="1"/>
+      <x:c r="D34" s="1"/>
+      <x:c r="E34" s="1"/>
+      <x:c r="F34" s="1"/>
+      <x:c r="G34" s="1"/>
+      <x:c r="H34" s="1"/>
+      <x:c r="I34" s="1"/>
+      <x:c r="J34" s="1"/>
+      <x:c r="K34" s="1"/>
+      <x:c r="L34" s="1"/>
+    </x:row>
+    <x:row r="35" ht="22" customHeight="1">
+      <x:c r="A35" s="1"/>
+      <x:c r="B35" s="1"/>
+      <x:c r="C35" s="1"/>
+      <x:c r="D35" s="1"/>
+      <x:c r="E35" s="1"/>
+      <x:c r="F35" s="1"/>
+      <x:c r="G35" s="1"/>
+      <x:c r="H35" s="1"/>
+      <x:c r="I35" s="1"/>
+      <x:c r="J35" s="1"/>
+      <x:c r="K35" s="1"/>
+      <x:c r="L35" s="1"/>
+    </x:row>
+    <x:row r="36" ht="22" customHeight="1">
+      <x:c r="A36" s="1"/>
+      <x:c r="B36" s="1"/>
+      <x:c r="C36" s="1"/>
+      <x:c r="D36" s="1"/>
+      <x:c r="E36" s="1"/>
+      <x:c r="F36" s="1"/>
+      <x:c r="G36" s="1"/>
+      <x:c r="H36" s="1"/>
+      <x:c r="I36" s="1"/>
+      <x:c r="J36" s="1"/>
+      <x:c r="K36" s="1"/>
+      <x:c r="L36" s="1"/>
+    </x:row>
+    <x:row r="37" ht="22" customHeight="1">
+      <x:c r="A37" s="1"/>
+      <x:c r="B37" s="1"/>
+      <x:c r="C37" s="1"/>
+      <x:c r="D37" s="1"/>
+      <x:c r="E37" s="1"/>
+      <x:c r="F37" s="1"/>
+      <x:c r="G37" s="1"/>
+      <x:c r="H37" s="1"/>
+      <x:c r="I37" s="1"/>
+      <x:c r="J37" s="1"/>
+      <x:c r="K37" s="1"/>
+      <x:c r="L37" s="1"/>
+    </x:row>
+    <x:row r="38" ht="22" customHeight="1">
+      <x:c r="A38" s="1"/>
+      <x:c r="B38" s="1"/>
+      <x:c r="C38" s="1"/>
+      <x:c r="D38" s="1"/>
+      <x:c r="E38" s="1"/>
+      <x:c r="F38" s="1"/>
+      <x:c r="G38" s="1"/>
+      <x:c r="H38" s="1"/>
+      <x:c r="I38" s="1"/>
+      <x:c r="J38" s="1"/>
+      <x:c r="K38" s="1"/>
+      <x:c r="L38" s="1"/>
+    </x:row>
+    <x:row r="39" ht="22" customHeight="1">
+      <x:c r="A39" s="1"/>
+      <x:c r="B39" s="1"/>
+      <x:c r="C39" s="1"/>
+      <x:c r="D39" s="1"/>
+      <x:c r="E39" s="1"/>
+      <x:c r="F39" s="1"/>
+      <x:c r="G39" s="1"/>
+      <x:c r="H39" s="1"/>
+      <x:c r="I39" s="1"/>
+      <x:c r="J39" s="1"/>
+      <x:c r="K39" s="1"/>
+      <x:c r="L39" s="1"/>
+    </x:row>
+    <x:row r="40" ht="22" customHeight="1">
+      <x:c r="A40" s="1"/>
+      <x:c r="B40" s="1"/>
+      <x:c r="C40" s="1"/>
+      <x:c r="D40" s="1"/>
+      <x:c r="E40" s="1"/>
+      <x:c r="F40" s="1"/>
+      <x:c r="G40" s="1"/>
+      <x:c r="H40" s="1"/>
+      <x:c r="I40" s="1"/>
+      <x:c r="J40" s="1"/>
+      <x:c r="K40" s="1"/>
+      <x:c r="L40" s="1"/>
+    </x:row>
+    <x:row r="41" ht="22" customHeight="1">
+      <x:c r="A41" s="1"/>
+      <x:c r="B41" s="1"/>
+      <x:c r="C41" s="1"/>
+      <x:c r="D41" s="1"/>
+      <x:c r="E41" s="1"/>
+      <x:c r="F41" s="1"/>
+      <x:c r="G41" s="1"/>
+      <x:c r="H41" s="1"/>
+      <x:c r="I41" s="1"/>
+      <x:c r="J41" s="1"/>
+      <x:c r="K41" s="1"/>
+      <x:c r="L41" s="1"/>
+    </x:row>
+    <x:row r="42" ht="22" customHeight="1">
+      <x:c r="A42" s="1"/>
+      <x:c r="B42" s="1"/>
+      <x:c r="C42" s="1"/>
+      <x:c r="D42" s="1"/>
+      <x:c r="E42" s="1"/>
+      <x:c r="F42" s="1"/>
+      <x:c r="G42" s="1"/>
+      <x:c r="H42" s="1"/>
+      <x:c r="I42" s="1"/>
+      <x:c r="J42" s="1"/>
+      <x:c r="K42" s="1"/>
+      <x:c r="L42" s="1"/>
+    </x:row>
+    <x:row r="43" ht="22" customHeight="1">
+      <x:c r="A43" s="1"/>
+      <x:c r="B43" s="1"/>
+      <x:c r="C43" s="1"/>
+      <x:c r="D43" s="1"/>
+      <x:c r="E43" s="1"/>
+      <x:c r="F43" s="1"/>
+      <x:c r="G43" s="1"/>
+      <x:c r="H43" s="1"/>
+      <x:c r="I43" s="1"/>
+      <x:c r="J43" s="1"/>
+      <x:c r="K43" s="1"/>
+      <x:c r="L43" s="1"/>
+    </x:row>
+    <x:row r="44" ht="22" customHeight="1">
+      <x:c r="A44" s="1"/>
+      <x:c r="B44" s="1"/>
+      <x:c r="C44" s="1"/>
+      <x:c r="D44" s="1"/>
+      <x:c r="E44" s="1"/>
+      <x:c r="F44" s="1"/>
+      <x:c r="G44" s="1"/>
+      <x:c r="H44" s="1"/>
+      <x:c r="I44" s="1"/>
+      <x:c r="J44" s="1"/>
+      <x:c r="K44" s="1"/>
+      <x:c r="L44" s="1"/>
+    </x:row>
+    <x:row r="45" ht="22" customHeight="1">
+      <x:c r="A45" s="1"/>
+      <x:c r="B45" s="1"/>
+      <x:c r="C45" s="1"/>
+      <x:c r="D45" s="1"/>
+      <x:c r="E45" s="1"/>
+      <x:c r="F45" s="1"/>
+      <x:c r="G45" s="1"/>
+      <x:c r="H45" s="1"/>
+      <x:c r="I45" s="1"/>
+      <x:c r="J45" s="1"/>
+      <x:c r="K45" s="1"/>
+      <x:c r="L45" s="1"/>
+    </x:row>
+    <x:row r="46" ht="22" customHeight="1">
+      <x:c r="A46" s="1"/>
+      <x:c r="B46" s="1"/>
+      <x:c r="C46" s="1"/>
+      <x:c r="D46" s="1"/>
+      <x:c r="E46" s="1"/>
+      <x:c r="F46" s="1"/>
+      <x:c r="G46" s="1"/>
+      <x:c r="H46" s="1"/>
+      <x:c r="I46" s="1"/>
+      <x:c r="J46" s="1"/>
+      <x:c r="K46" s="1"/>
+      <x:c r="L46" s="1"/>
+    </x:row>
+    <x:row r="47" ht="22" customHeight="1">
+      <x:c r="A47" s="1"/>
+      <x:c r="B47" s="1"/>
+      <x:c r="C47" s="1"/>
+      <x:c r="D47" s="1"/>
+      <x:c r="E47" s="1"/>
+      <x:c r="F47" s="1"/>
+      <x:c r="G47" s="1"/>
+      <x:c r="H47" s="1"/>
+      <x:c r="I47" s="1"/>
+      <x:c r="J47" s="1"/>
+      <x:c r="K47" s="1"/>
+      <x:c r="L47" s="1"/>
+    </x:row>
+    <x:row r="48" ht="22" customHeight="1">
+      <x:c r="A48" s="1"/>
+      <x:c r="B48" s="1"/>
+      <x:c r="C48" s="1"/>
+      <x:c r="D48" s="1"/>
+      <x:c r="E48" s="1"/>
+      <x:c r="F48" s="1"/>
+      <x:c r="G48" s="1"/>
+      <x:c r="H48" s="1"/>
+      <x:c r="I48" s="1"/>
+      <x:c r="J48" s="1"/>
+      <x:c r="K48" s="1"/>
+      <x:c r="L48" s="1"/>
+    </x:row>
+    <x:row r="49" ht="22" customHeight="1">
+      <x:c r="A49" s="1"/>
+      <x:c r="B49" s="1"/>
+      <x:c r="C49" s="1"/>
+      <x:c r="D49" s="1"/>
+      <x:c r="E49" s="1"/>
+      <x:c r="F49" s="1"/>
+      <x:c r="G49" s="1"/>
+      <x:c r="H49" s="1"/>
+      <x:c r="I49" s="1"/>
+      <x:c r="J49" s="1"/>
+      <x:c r="K49" s="1"/>
+      <x:c r="L49" s="1"/>
+    </x:row>
+    <x:row r="50" ht="22" customHeight="1">
+      <x:c r="A50" s="1"/>
+      <x:c r="B50" s="1"/>
+      <x:c r="C50" s="1"/>
+      <x:c r="D50" s="1"/>
+      <x:c r="E50" s="1"/>
+      <x:c r="F50" s="1"/>
+      <x:c r="G50" s="1"/>
+      <x:c r="H50" s="1"/>
+      <x:c r="I50" s="1"/>
+      <x:c r="J50" s="1"/>
+      <x:c r="K50" s="1"/>
+      <x:c r="L50" s="1"/>
+    </x:row>
+    <x:row r="51" ht="22" customHeight="1">
+      <x:c r="A51" s="1"/>
+      <x:c r="B51" s="1"/>
+      <x:c r="C51" s="1"/>
+      <x:c r="D51" s="1"/>
+      <x:c r="E51" s="1"/>
+      <x:c r="F51" s="1"/>
+      <x:c r="G51" s="1"/>
+      <x:c r="H51" s="1"/>
+      <x:c r="I51" s="1"/>
+      <x:c r="J51" s="1"/>
+      <x:c r="K51" s="1"/>
+      <x:c r="L51" s="1"/>
+    </x:row>
+    <x:row r="52" ht="22" customHeight="1">
+      <x:c r="A52" s="1"/>
+      <x:c r="B52" s="1"/>
+      <x:c r="C52" s="1"/>
+      <x:c r="D52" s="1"/>
+      <x:c r="E52" s="1"/>
+      <x:c r="F52" s="1"/>
+      <x:c r="G52" s="1"/>
+      <x:c r="H52" s="1"/>
+      <x:c r="I52" s="1"/>
+      <x:c r="J52" s="1"/>
+      <x:c r="K52" s="1"/>
+      <x:c r="L52" s="1"/>
+    </x:row>
+    <x:row r="53" ht="22" customHeight="1">
+      <x:c r="A53" s="1"/>
+      <x:c r="B53" s="1"/>
+      <x:c r="C53" s="1"/>
+      <x:c r="D53" s="1"/>
+      <x:c r="E53" s="1"/>
+      <x:c r="F53" s="1"/>
+      <x:c r="G53" s="1"/>
+      <x:c r="H53" s="1"/>
+      <x:c r="I53" s="1"/>
+      <x:c r="J53" s="1"/>
+      <x:c r="K53" s="1"/>
+      <x:c r="L53" s="1"/>
+    </x:row>
+    <x:row r="54" ht="22" customHeight="1">
+      <x:c r="A54" s="1"/>
+      <x:c r="B54" s="1"/>
+      <x:c r="C54" s="1"/>
+      <x:c r="D54" s="1"/>
+      <x:c r="E54" s="1"/>
+      <x:c r="F54" s="1"/>
+      <x:c r="G54" s="1"/>
+      <x:c r="H54" s="1"/>
+      <x:c r="I54" s="1"/>
+      <x:c r="J54" s="1"/>
+      <x:c r="K54" s="1"/>
+      <x:c r="L54" s="1"/>
+    </x:row>
+    <x:row r="55" ht="22" customHeight="1">
+      <x:c r="A55" s="1"/>
+      <x:c r="B55" s="1"/>
+      <x:c r="C55" s="1"/>
+      <x:c r="D55" s="1"/>
+      <x:c r="E55" s="1"/>
+      <x:c r="F55" s="1"/>
+      <x:c r="G55" s="1"/>
+      <x:c r="H55" s="1"/>
+      <x:c r="I55" s="1"/>
+      <x:c r="J55" s="1"/>
+      <x:c r="K55" s="1"/>
+      <x:c r="L55" s="1"/>
+    </x:row>
+    <x:row r="56" ht="22" customHeight="1">
+      <x:c r="A56" s="1"/>
+      <x:c r="B56" s="1"/>
+      <x:c r="C56" s="1"/>
+      <x:c r="D56" s="1"/>
+      <x:c r="E56" s="1"/>
+      <x:c r="F56" s="1"/>
+      <x:c r="G56" s="1"/>
+      <x:c r="H56" s="1"/>
+      <x:c r="I56" s="1"/>
+      <x:c r="J56" s="1"/>
+      <x:c r="K56" s="1"/>
+      <x:c r="L56" s="1"/>
+    </x:row>
+    <x:row r="57" ht="22" customHeight="1">
+      <x:c r="A57" s="1"/>
+      <x:c r="B57" s="1"/>
+      <x:c r="C57" s="1"/>
+      <x:c r="D57" s="1"/>
+      <x:c r="E57" s="1"/>
+      <x:c r="F57" s="1"/>
+      <x:c r="G57" s="1"/>
+      <x:c r="H57" s="1"/>
+      <x:c r="I57" s="1"/>
+      <x:c r="J57" s="1"/>
+      <x:c r="K57" s="1"/>
+      <x:c r="L57" s="1"/>
+    </x:row>
+    <x:row r="58" ht="22" customHeight="1">
+      <x:c r="A58" s="1"/>
+      <x:c r="B58" s="1"/>
+      <x:c r="C58" s="1"/>
+      <x:c r="D58" s="1"/>
+      <x:c r="E58" s="1"/>
+      <x:c r="F58" s="1"/>
+      <x:c r="G58" s="1"/>
+      <x:c r="H58" s="1"/>
+      <x:c r="I58" s="1"/>
+      <x:c r="J58" s="1"/>
+      <x:c r="K58" s="1"/>
+      <x:c r="L58" s="1"/>
+    </x:row>
+    <x:row r="59" ht="22" customHeight="1">
+      <x:c r="A59" s="1"/>
+      <x:c r="B59" s="1"/>
+      <x:c r="C59" s="1"/>
+      <x:c r="D59" s="1"/>
+      <x:c r="E59" s="1"/>
+      <x:c r="F59" s="1"/>
+      <x:c r="G59" s="1"/>
+      <x:c r="H59" s="1"/>
+      <x:c r="I59" s="1"/>
+      <x:c r="J59" s="1"/>
+      <x:c r="K59" s="1"/>
+      <x:c r="L59" s="1"/>
+    </x:row>
+    <x:row r="60" ht="22" customHeight="1">
+      <x:c r="A60" s="1"/>
+      <x:c r="B60" s="1"/>
+      <x:c r="C60" s="1"/>
+      <x:c r="D60" s="1"/>
+      <x:c r="E60" s="1"/>
+      <x:c r="F60" s="1"/>
+      <x:c r="G60" s="1"/>
+      <x:c r="H60" s="1"/>
+      <x:c r="I60" s="1"/>
+      <x:c r="J60" s="1"/>
+      <x:c r="K60" s="1"/>
+      <x:c r="L60" s="1"/>
+    </x:row>
+    <x:row r="61" ht="22" customHeight="1">
+      <x:c r="A61" s="1"/>
+      <x:c r="B61" s="1"/>
+      <x:c r="C61" s="1"/>
+      <x:c r="D61" s="1"/>
+      <x:c r="E61" s="1"/>
+      <x:c r="F61" s="1"/>
+      <x:c r="G61" s="1"/>
+      <x:c r="H61" s="1"/>
+      <x:c r="I61" s="1"/>
+      <x:c r="J61" s="1"/>
+      <x:c r="K61" s="1"/>
+      <x:c r="L61" s="1"/>
+    </x:row>
+    <x:row r="62" ht="22" customHeight="1">
+      <x:c r="A62" s="1"/>
+      <x:c r="B62" s="1"/>
+      <x:c r="C62" s="1"/>
+      <x:c r="D62" s="1"/>
+      <x:c r="E62" s="1"/>
+      <x:c r="F62" s="1"/>
+      <x:c r="G62" s="1"/>
+      <x:c r="H62" s="1"/>
+      <x:c r="I62" s="1"/>
+      <x:c r="J62" s="1"/>
+      <x:c r="K62" s="1"/>
+      <x:c r="L62" s="1"/>
+    </x:row>
+    <x:row r="63" ht="22" customHeight="1">
+      <x:c r="A63" s="1"/>
+      <x:c r="B63" s="1"/>
+      <x:c r="C63" s="1"/>
+      <x:c r="D63" s="1"/>
+      <x:c r="E63" s="1"/>
+      <x:c r="F63" s="1"/>
+      <x:c r="G63" s="1"/>
+      <x:c r="H63" s="1"/>
+      <x:c r="I63" s="1"/>
+      <x:c r="J63" s="1"/>
+      <x:c r="K63" s="1"/>
+      <x:c r="L63" s="1"/>
+    </x:row>
+    <x:row r="64" ht="22" customHeight="1">
+      <x:c r="A64" s="1"/>
+      <x:c r="B64" s="1"/>
+      <x:c r="C64" s="1"/>
+      <x:c r="D64" s="1"/>
+      <x:c r="E64" s="1"/>
+      <x:c r="F64" s="1"/>
+      <x:c r="G64" s="1"/>
+      <x:c r="H64" s="1"/>
+      <x:c r="I64" s="1"/>
+      <x:c r="J64" s="1"/>
+      <x:c r="K64" s="1"/>
+      <x:c r="L64" s="1"/>
+    </x:row>
+    <x:row r="65" ht="22" customHeight="1">
+      <x:c r="A65" s="1"/>
+      <x:c r="B65" s="1"/>
+      <x:c r="C65" s="1"/>
+      <x:c r="D65" s="1"/>
+      <x:c r="E65" s="1"/>
+      <x:c r="F65" s="1"/>
+      <x:c r="G65" s="1"/>
+      <x:c r="H65" s="1"/>
+      <x:c r="I65" s="1"/>
+      <x:c r="J65" s="1"/>
+      <x:c r="K65" s="1"/>
+      <x:c r="L65" s="1"/>
+    </x:row>
+  </x:sheetData>
+  <x:conditionalFormatting sqref="D7:D9">
+    <x:cfRule type="expression" dxfId="0" priority="1">
+      <x:formula>ABS(D7)&gt;E7</x:formula>
+    </x:cfRule>
+  </x:conditionalFormatting>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
 
@@ -1939,9 +5751,9 @@
     <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="23" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="23" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="23" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="32" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="32" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="32" hidden="0" customWidth="1"/>
     <x:col min="9" max="9" width="23" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
@@ -2050,7 +5862,7 @@
       <x:c r="D7" s="1"/>
       <x:c r="E7" s="1"/>
       <x:c r="F7" s="1"/>
-      <x:c r="G7" s="1"/>
+      <x:c r="G7" s="42"/>
       <x:c r="H7" s="1"/>
       <x:c r="I7" s="1"/>
       <x:c r="J7" s="1"/>
@@ -2068,18 +5880,12 @@
         <x:v>0.012</x:v>
       </x:c>
       <x:c r="E8" s="1"/>
-      <x:c r="F8" s="14" t="str">
-        <x:v>Cash driver</x:v>
-      </x:c>
-      <x:c r="G8" s="14" t="str">
-        <x:v>Value</x:v>
-      </x:c>
-      <x:c r="H8" s="14" t="str">
-        <x:v>Units</x:v>
-      </x:c>
-      <x:c r="I8" s="14" t="str">
-        <x:v>Basis</x:v>
-      </x:c>
+      <x:c r="F8" s="19" t="str">
+        <x:v>Cash assumptions are in the expanded driver block below.</x:v>
+      </x:c>
+      <x:c r="G8" s="43"/>
+      <x:c r="H8" s="19"/>
+      <x:c r="I8" s="19"/>
       <x:c r="J8" s="1"/>
       <x:c r="K8" s="1"/>
       <x:c r="L8" s="1"/>
@@ -2094,18 +5900,10 @@
         <x:v>0.012</x:v>
       </x:c>
       <x:c r="E9" s="1"/>
-      <x:c r="F9" s="5" t="str">
-        <x:v>Opening July cash</x:v>
-      </x:c>
-      <x:c r="G9" s="15" t="n">
-        <x:v>500000</x:v>
-      </x:c>
-      <x:c r="H9" s="5" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I9" s="5" t="str">
-        <x:v>Synthetic assumption</x:v>
-      </x:c>
+      <x:c r="F9" s="19"/>
+      <x:c r="G9" s="43"/>
+      <x:c r="H9" s="19"/>
+      <x:c r="I9" s="19"/>
       <x:c r="J9" s="1"/>
       <x:c r="K9" s="1"/>
       <x:c r="L9" s="1"/>
@@ -2120,18 +5918,10 @@
         <x:v>-0.012</x:v>
       </x:c>
       <x:c r="E10" s="1"/>
-      <x:c r="F10" s="5" t="str">
-        <x:v>Receivable days</x:v>
-      </x:c>
-      <x:c r="G10" s="15" t="n">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="H10" s="5" t="str">
-        <x:v>days</x:v>
-      </x:c>
-      <x:c r="I10" s="5" t="str">
-        <x:v>30-day month approximation</x:v>
-      </x:c>
+      <x:c r="F10" s="19"/>
+      <x:c r="G10" s="19"/>
+      <x:c r="H10" s="19"/>
+      <x:c r="I10" s="19"/>
       <x:c r="J10" s="1"/>
       <x:c r="K10" s="1"/>
       <x:c r="L10" s="1"/>
@@ -2146,18 +5936,10 @@
         <x:v>0.027</x:v>
       </x:c>
       <x:c r="E11" s="1"/>
-      <x:c r="F11" s="5" t="str">
-        <x:v>Payable days</x:v>
-      </x:c>
-      <x:c r="G11" s="15" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="H11" s="5" t="str">
-        <x:v>days</x:v>
-      </x:c>
-      <x:c r="I11" s="5" t="str">
-        <x:v>Variable costs only</x:v>
-      </x:c>
+      <x:c r="F11"/>
+      <x:c r="G11"/>
+      <x:c r="H11"/>
+      <x:c r="I11"/>
       <x:c r="J11" s="1"/>
       <x:c r="K11" s="1"/>
       <x:c r="L11" s="1"/>
@@ -2168,18 +5950,10 @@
       <x:c r="C12" s="1"/>
       <x:c r="D12" s="1"/>
       <x:c r="E12" s="1"/>
-      <x:c r="F12" s="5" t="str">
-        <x:v>Monthly depreciation</x:v>
-      </x:c>
-      <x:c r="G12" s="15" t="n">
-        <x:v>20000</x:v>
-      </x:c>
-      <x:c r="H12" s="5" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I12" s="5" t="str">
-        <x:v>Existing asset base simplified</x:v>
-      </x:c>
+      <x:c r="F12"/>
+      <x:c r="G12"/>
+      <x:c r="H12"/>
+      <x:c r="I12"/>
       <x:c r="J12" s="1"/>
       <x:c r="K12" s="1"/>
       <x:c r="L12" s="1"/>
@@ -2195,18 +5969,10 @@
         <x:v>0.018</x:v>
       </x:c>
       <x:c r="E13" s="1"/>
-      <x:c r="F13" s="5" t="str">
-        <x:v>Monthly cash capex</x:v>
-      </x:c>
-      <x:c r="G13" s="15" t="n">
-        <x:v>25000</x:v>
-      </x:c>
-      <x:c r="H13" s="5" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I13" s="5" t="str">
-        <x:v>Maintenance capex assumption</x:v>
-      </x:c>
+      <x:c r="F13"/>
+      <x:c r="G13"/>
+      <x:c r="H13"/>
+      <x:c r="I13"/>
       <x:c r="J13" s="1"/>
       <x:c r="K13" s="1"/>
       <x:c r="L13" s="1"/>
@@ -2221,18 +5987,10 @@
         <x:v>0.018</x:v>
       </x:c>
       <x:c r="E14" s="1"/>
-      <x:c r="F14" s="5" t="str">
-        <x:v>Cash tax rate</x:v>
-      </x:c>
-      <x:c r="G14" s="15" t="n">
-        <x:v>0.25</x:v>
-      </x:c>
-      <x:c r="H14" s="5" t="str">
-        <x:v>fraction</x:v>
-      </x:c>
-      <x:c r="I14" s="5" t="str">
-        <x:v>Tax only on positive EBIT</x:v>
-      </x:c>
+      <x:c r="F14"/>
+      <x:c r="G14"/>
+      <x:c r="H14"/>
+      <x:c r="I14"/>
       <x:c r="J14" s="1"/>
       <x:c r="K14" s="1"/>
       <x:c r="L14" s="1"/>
@@ -2247,18 +6005,10 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="E15" s="1"/>
-      <x:c r="F15" s="5" t="str">
-        <x:v>Minimum cash</x:v>
-      </x:c>
-      <x:c r="G15" s="15" t="n">
-        <x:v>250000</x:v>
-      </x:c>
-      <x:c r="H15" s="5" t="str">
-        <x:v>USD</x:v>
-      </x:c>
-      <x:c r="I15" s="5" t="str">
-        <x:v>Illustrative management threshold</x:v>
-      </x:c>
+      <x:c r="F15"/>
+      <x:c r="G15"/>
+      <x:c r="H15"/>
+      <x:c r="I15"/>
       <x:c r="J15" s="1"/>
       <x:c r="K15" s="1"/>
       <x:c r="L15" s="1"/>
@@ -2515,7 +6265,7 @@
       <x:c r="A31" s="1"/>
       <x:c r="B31" s="1"/>
       <x:c r="C31" s="5" t="str">
-        <x:v>Monthly rates compound. No financing, dividends, or loss carryforwards.</x:v>
+        <x:v>Expanded schedules use explicit collection lags, debt and asset balances.</x:v>
       </x:c>
       <x:c r="D31" s="5"/>
       <x:c r="E31" s="5"/>
@@ -2639,268 +6389,438 @@
       <x:c r="K39" s="1"/>
       <x:c r="L39" s="1"/>
     </x:row>
-    <x:row r="40" ht="22" customHeight="1">
+    <x:row r="40" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A40" s="1"/>
       <x:c r="B40" s="1"/>
       <x:c r="C40" s="1"/>
       <x:c r="D40" s="1"/>
       <x:c r="E40" s="1"/>
-      <x:c r="F40" s="1"/>
-      <x:c r="G40" s="1"/>
-      <x:c r="H40" s="1"/>
-      <x:c r="I40" s="1"/>
+      <x:c r="F40" s="14" t="str">
+        <x:v>Expanded driver</x:v>
+      </x:c>
+      <x:c r="G40" s="14" t="str">
+        <x:v>Value</x:v>
+      </x:c>
+      <x:c r="H40" s="14" t="str">
+        <x:v>Synthetic opening / policy assumption</x:v>
+      </x:c>
+      <x:c r="I40" s="46" t="str">
+        <x:v>Validated value</x:v>
+      </x:c>
       <x:c r="J40" s="1"/>
       <x:c r="K40" s="1"/>
       <x:c r="L40" s="1"/>
     </x:row>
-    <x:row r="41" ht="22" customHeight="1">
+    <x:row r="41" ht="15" hidden="0" customHeight="1">
       <x:c r="A41" s="1"/>
       <x:c r="B41" s="1"/>
       <x:c r="C41" s="1"/>
       <x:c r="D41" s="1"/>
       <x:c r="E41" s="1"/>
-      <x:c r="F41" s="1"/>
-      <x:c r="G41" s="1"/>
-      <x:c r="H41" s="1"/>
-      <x:c r="I41" s="1"/>
+      <x:c r="F41" s="5" t="str">
+        <x:v>Opening AR</x:v>
+      </x:c>
+      <x:c r="G41" s="34" t="n">
+        <x:v>1020000</x:v>
+      </x:c>
+      <x:c r="H41" s="5" t="str">
+        <x:v>Outstanding credit sales</x:v>
+      </x:c>
+      <x:c r="I41" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G41),G41&gt;=0),G41,NA())</x:f>
+        <x:v>1020000</x:v>
+      </x:c>
       <x:c r="J41" s="1"/>
       <x:c r="K41" s="1"/>
       <x:c r="L41" s="1"/>
     </x:row>
-    <x:row r="42" ht="22" customHeight="1">
+    <x:row r="42" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A42" s="1"/>
       <x:c r="B42" s="1"/>
       <x:c r="C42" s="1"/>
       <x:c r="D42" s="1"/>
       <x:c r="E42" s="1"/>
-      <x:c r="F42" s="1"/>
-      <x:c r="G42" s="1"/>
-      <x:c r="H42" s="1"/>
-      <x:c r="I42" s="1"/>
+      <x:c r="F42" s="5" t="str">
+        <x:v>Opening AR collected in July</x:v>
+      </x:c>
+      <x:c r="G42" s="34" t="n">
+        <x:v>550000</x:v>
+      </x:c>
+      <x:c r="H42" s="5" t="str">
+        <x:v>Remaining balance collected August</x:v>
+      </x:c>
+      <x:c r="I42" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G42),G42&gt;=0,ISNUMBER(G41),G42&lt;=G41),G42,NA())</x:f>
+        <x:v>550000</x:v>
+      </x:c>
       <x:c r="J42" s="1"/>
       <x:c r="K42" s="1"/>
       <x:c r="L42" s="1"/>
     </x:row>
-    <x:row r="43" ht="22" customHeight="1">
+    <x:row r="43" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A43" s="1"/>
       <x:c r="B43" s="1"/>
       <x:c r="C43" s="1"/>
       <x:c r="D43" s="1"/>
       <x:c r="E43" s="1"/>
-      <x:c r="F43" s="1"/>
-      <x:c r="G43" s="1"/>
-      <x:c r="H43" s="1"/>
-      <x:c r="I43" s="1"/>
+      <x:c r="F43" s="5" t="str">
+        <x:v>Current-month collection fraction</x:v>
+      </x:c>
+      <x:c r="G43" s="37" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="H43" s="5" t="str">
+        <x:v>Credit sales</x:v>
+      </x:c>
+      <x:c r="I43" s="8" t="n">
+        <x:f>IF(AND(ISNUMBER(G43),G43&gt;=0,G43&lt;=1,ISNUMBER(G43),ISNUMBER(G44),G43+G44&lt;=1),G43,NA())</x:f>
+        <x:v>0.25</x:v>
+      </x:c>
       <x:c r="J43" s="1"/>
       <x:c r="K43" s="1"/>
       <x:c r="L43" s="1"/>
     </x:row>
-    <x:row r="44" ht="22" customHeight="1">
+    <x:row r="44" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A44" s="1"/>
       <x:c r="B44" s="1"/>
       <x:c r="C44" s="1"/>
       <x:c r="D44" s="1"/>
       <x:c r="E44" s="1"/>
-      <x:c r="F44" s="1"/>
-      <x:c r="G44" s="1"/>
-      <x:c r="H44" s="1"/>
-      <x:c r="I44" s="1"/>
+      <x:c r="F44" s="5" t="str">
+        <x:v>Next-month collection fraction</x:v>
+      </x:c>
+      <x:c r="G44" s="37" t="n">
+        <x:v>0.65</x:v>
+      </x:c>
+      <x:c r="H44" s="5" t="str">
+        <x:v>Credit sales; remainder month two</x:v>
+      </x:c>
+      <x:c r="I44" s="8" t="n">
+        <x:f>IF(AND(ISNUMBER(G44),G44&gt;=0,G44&lt;=1,ISNUMBER(G43),ISNUMBER(G44),G43+G44&lt;=1),G44,NA())</x:f>
+        <x:v>0.65</x:v>
+      </x:c>
       <x:c r="J44" s="1"/>
       <x:c r="K44" s="1"/>
       <x:c r="L44" s="1"/>
     </x:row>
-    <x:row r="45" ht="22" customHeight="1">
+    <x:row r="45" ht="15" hidden="0" customHeight="1">
       <x:c r="A45" s="1"/>
       <x:c r="B45" s="1"/>
       <x:c r="C45" s="1"/>
       <x:c r="D45" s="1"/>
       <x:c r="E45" s="1"/>
-      <x:c r="F45" s="1"/>
-      <x:c r="G45" s="1"/>
-      <x:c r="H45" s="1"/>
-      <x:c r="I45" s="1"/>
+      <x:c r="F45" s="5" t="str">
+        <x:v>Opening AP</x:v>
+      </x:c>
+      <x:c r="G45" s="34" t="n">
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="H45" s="5" t="str">
+        <x:v>Paid July</x:v>
+      </x:c>
+      <x:c r="I45" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G45),G45&gt;=0),G45,NA())</x:f>
+        <x:v>300000</x:v>
+      </x:c>
       <x:c r="J45" s="1"/>
       <x:c r="K45" s="1"/>
       <x:c r="L45" s="1"/>
     </x:row>
-    <x:row r="46" ht="22" customHeight="1">
+    <x:row r="46" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A46" s="1"/>
       <x:c r="B46" s="1"/>
       <x:c r="C46" s="1"/>
       <x:c r="D46" s="1"/>
       <x:c r="E46" s="1"/>
-      <x:c r="F46" s="1"/>
-      <x:c r="G46" s="1"/>
-      <x:c r="H46" s="1"/>
-      <x:c r="I46" s="1"/>
+      <x:c r="F46" s="5" t="str">
+        <x:v>Current-month supplier payment fraction</x:v>
+      </x:c>
+      <x:c r="G46" s="37" t="n">
+        <x:v>0.5</x:v>
+      </x:c>
+      <x:c r="H46" s="5" t="str">
+        <x:v>Variable costs; remainder next month</x:v>
+      </x:c>
+      <x:c r="I46" s="8" t="n">
+        <x:f>IF(AND(ISNUMBER(G46),G46&gt;=0,G46&lt;=1),G46,NA())</x:f>
+        <x:v>0.5</x:v>
+      </x:c>
       <x:c r="J46" s="1"/>
       <x:c r="K46" s="1"/>
       <x:c r="L46" s="1"/>
     </x:row>
-    <x:row r="47" ht="22" customHeight="1">
+    <x:row r="47" ht="15" hidden="0" customHeight="1">
       <x:c r="A47" s="1"/>
       <x:c r="B47" s="1"/>
       <x:c r="C47" s="1"/>
       <x:c r="D47" s="1"/>
       <x:c r="E47" s="1"/>
-      <x:c r="F47" s="1"/>
-      <x:c r="G47" s="1"/>
-      <x:c r="H47" s="1"/>
-      <x:c r="I47" s="1"/>
+      <x:c r="F47" s="5" t="str">
+        <x:v>Opening gross PP&amp;E</x:v>
+      </x:c>
+      <x:c r="G47" s="34" t="n">
+        <x:v>1200000</x:v>
+      </x:c>
+      <x:c r="H47" s="5" t="str">
+        <x:v>June 30</x:v>
+      </x:c>
+      <x:c r="I47" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G47),G47&gt;=0),G47,NA())</x:f>
+        <x:v>1200000</x:v>
+      </x:c>
       <x:c r="J47" s="1"/>
       <x:c r="K47" s="1"/>
       <x:c r="L47" s="1"/>
     </x:row>
-    <x:row r="48" ht="22" customHeight="1">
+    <x:row r="48" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A48" s="1"/>
       <x:c r="B48" s="1"/>
       <x:c r="C48" s="1"/>
       <x:c r="D48" s="1"/>
       <x:c r="E48" s="1"/>
-      <x:c r="F48" s="1"/>
-      <x:c r="G48" s="1"/>
-      <x:c r="H48" s="1"/>
-      <x:c r="I48" s="1"/>
+      <x:c r="F48" s="5" t="str">
+        <x:v>Opening accumulated depreciation</x:v>
+      </x:c>
+      <x:c r="G48" s="34" t="n">
+        <x:v>480000</x:v>
+      </x:c>
+      <x:c r="H48" s="5" t="str">
+        <x:v>June 30</x:v>
+      </x:c>
+      <x:c r="I48" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G48),G48&gt;=0,ISNUMBER(G47),G48&lt;=G47),G48,NA())</x:f>
+        <x:v>480000</x:v>
+      </x:c>
       <x:c r="J48" s="1"/>
       <x:c r="K48" s="1"/>
       <x:c r="L48" s="1"/>
     </x:row>
-    <x:row r="49" ht="22" customHeight="1">
+    <x:row r="49" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A49" s="1"/>
       <x:c r="B49" s="1"/>
       <x:c r="C49" s="1"/>
       <x:c r="D49" s="1"/>
       <x:c r="E49" s="1"/>
-      <x:c r="F49" s="1"/>
-      <x:c r="G49" s="1"/>
-      <x:c r="H49" s="1"/>
-      <x:c r="I49" s="1"/>
+      <x:c r="F49" s="5" t="str">
+        <x:v>New asset useful life (months)</x:v>
+      </x:c>
+      <x:c r="G49" s="41" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H49" s="5" t="str">
+        <x:v>Month-end additions depreciate next month</x:v>
+      </x:c>
+      <x:c r="I49" s="47" t="n">
+        <x:f>IF(AND(ISNUMBER(G49),G49&gt;=0,MOD(G49,1)=0,G49&gt;0),G49,NA())</x:f>
+        <x:v>60</x:v>
+      </x:c>
       <x:c r="J49" s="1"/>
       <x:c r="K49" s="1"/>
       <x:c r="L49" s="1"/>
     </x:row>
-    <x:row r="50" ht="22" customHeight="1">
+    <x:row r="50" ht="15" hidden="0" customHeight="1">
       <x:c r="A50" s="1"/>
       <x:c r="B50" s="1"/>
       <x:c r="C50" s="1"/>
       <x:c r="D50" s="1"/>
       <x:c r="E50" s="1"/>
-      <x:c r="F50" s="1"/>
-      <x:c r="G50" s="1"/>
-      <x:c r="H50" s="1"/>
-      <x:c r="I50" s="1"/>
+      <x:c r="F50" s="5" t="str">
+        <x:v>Opening debt</x:v>
+      </x:c>
+      <x:c r="G50" s="34" t="n">
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="H50" s="5" t="str">
+        <x:v>June 30</x:v>
+      </x:c>
+      <x:c r="I50" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G50),G50&gt;=0),G50,NA())</x:f>
+        <x:v>600000</x:v>
+      </x:c>
       <x:c r="J50" s="1"/>
       <x:c r="K50" s="1"/>
       <x:c r="L50" s="1"/>
     </x:row>
-    <x:row r="51" ht="22" customHeight="1">
+    <x:row r="51" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A51" s="1"/>
       <x:c r="B51" s="1"/>
       <x:c r="C51" s="1"/>
       <x:c r="D51" s="1"/>
       <x:c r="E51" s="1"/>
-      <x:c r="F51" s="1"/>
-      <x:c r="G51" s="1"/>
-      <x:c r="H51" s="1"/>
-      <x:c r="I51" s="1"/>
+      <x:c r="F51" s="5" t="str">
+        <x:v>Annual debt interest</x:v>
+      </x:c>
+      <x:c r="G51" s="37" t="n">
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="H51" s="5" t="str">
+        <x:v>Opening monthly principal basis</x:v>
+      </x:c>
+      <x:c r="I51" s="8" t="n">
+        <x:f>IF(AND(ISNUMBER(G51),G51&gt;=0,G51&lt;=1),G51,NA())</x:f>
+        <x:v>0.08</x:v>
+      </x:c>
       <x:c r="J51" s="1"/>
       <x:c r="K51" s="1"/>
       <x:c r="L51" s="1"/>
     </x:row>
-    <x:row r="52" ht="22" customHeight="1">
+    <x:row r="52" ht="15" hidden="0" customHeight="1">
       <x:c r="A52" s="1"/>
       <x:c r="B52" s="1"/>
       <x:c r="C52" s="1"/>
       <x:c r="D52" s="1"/>
       <x:c r="E52" s="1"/>
-      <x:c r="F52" s="1"/>
-      <x:c r="G52" s="1"/>
-      <x:c r="H52" s="1"/>
-      <x:c r="I52" s="1"/>
+      <x:c r="F52" s="5" t="str">
+        <x:v>Monthly principal repayment</x:v>
+      </x:c>
+      <x:c r="G52" s="34" t="n">
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="H52" s="5" t="str">
+        <x:v>No new borrowing</x:v>
+      </x:c>
+      <x:c r="I52" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G52),G52&gt;=0),G52,NA())</x:f>
+        <x:v>10000</x:v>
+      </x:c>
       <x:c r="J52" s="1"/>
       <x:c r="K52" s="1"/>
       <x:c r="L52" s="1"/>
     </x:row>
-    <x:row r="53" ht="22" customHeight="1">
+    <x:row r="53" ht="15" hidden="0" customHeight="1">
       <x:c r="A53" s="1"/>
       <x:c r="B53" s="1"/>
       <x:c r="C53" s="1"/>
       <x:c r="D53" s="1"/>
       <x:c r="E53" s="1"/>
-      <x:c r="F53" s="1"/>
-      <x:c r="G53" s="1"/>
-      <x:c r="H53" s="1"/>
-      <x:c r="I53" s="1"/>
+      <x:c r="F53" s="5" t="str">
+        <x:v>Share capital</x:v>
+      </x:c>
+      <x:c r="G53" s="34" t="n">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="H53" s="5" t="str">
+        <x:v>No issuance or dividends</x:v>
+      </x:c>
+      <x:c r="I53" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G53),G53&gt;=0),G53,NA())</x:f>
+        <x:v>500000</x:v>
+      </x:c>
       <x:c r="J53" s="1"/>
       <x:c r="K53" s="1"/>
       <x:c r="L53" s="1"/>
     </x:row>
-    <x:row r="54" ht="22" customHeight="1">
+    <x:row r="54" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A54" s="1"/>
       <x:c r="B54" s="1"/>
       <x:c r="C54" s="1"/>
       <x:c r="D54" s="1"/>
       <x:c r="E54" s="1"/>
-      <x:c r="F54" s="1"/>
-      <x:c r="G54" s="1"/>
-      <x:c r="H54" s="1"/>
-      <x:c r="I54" s="1"/>
+      <x:c r="F54" s="5" t="str">
+        <x:v>Opening tax losses</x:v>
+      </x:c>
+      <x:c r="G54" s="34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H54" s="5" t="str">
+        <x:v>Forecast-only simplified tax-loss pool</x:v>
+      </x:c>
+      <x:c r="I54" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G54),G54&gt;=0),G54,NA())</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J54" s="1"/>
       <x:c r="K54" s="1"/>
       <x:c r="L54" s="1"/>
     </x:row>
-    <x:row r="55" ht="22" customHeight="1">
+    <x:row r="55" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A55" s="1"/>
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
       <x:c r="D55" s="1"/>
       <x:c r="E55" s="1"/>
-      <x:c r="F55" s="1"/>
-      <x:c r="G55" s="1"/>
-      <x:c r="H55" s="1"/>
-      <x:c r="I55" s="1"/>
+      <x:c r="F55" s="5" t="str">
+        <x:v>Tax rate</x:v>
+      </x:c>
+      <x:c r="G55" s="37" t="n">
+        <x:v>0.25</x:v>
+      </x:c>
+      <x:c r="H55" s="5" t="str">
+        <x:v>Positive income after loss offset</x:v>
+      </x:c>
+      <x:c r="I55" s="8" t="n">
+        <x:f>IF(AND(ISNUMBER(G55),G55&gt;=0,G55&lt;=1),G55,NA())</x:f>
+        <x:v>0.25</x:v>
+      </x:c>
       <x:c r="J55" s="1"/>
       <x:c r="K55" s="1"/>
       <x:c r="L55" s="1"/>
     </x:row>
-    <x:row r="56" ht="22" customHeight="1">
+    <x:row r="56" ht="15" hidden="0" customHeight="1">
       <x:c r="A56" s="1"/>
       <x:c r="B56" s="1"/>
       <x:c r="C56" s="1"/>
       <x:c r="D56" s="1"/>
       <x:c r="E56" s="1"/>
-      <x:c r="F56" s="1"/>
-      <x:c r="G56" s="1"/>
-      <x:c r="H56" s="1"/>
-      <x:c r="I56" s="1"/>
+      <x:c r="F56" s="5" t="str">
+        <x:v>Opening cash</x:v>
+      </x:c>
+      <x:c r="G56" s="34" t="n">
+        <x:v>500000</x:v>
+      </x:c>
+      <x:c r="H56" s="5" t="str">
+        <x:v>June 30 bank assumption</x:v>
+      </x:c>
+      <x:c r="I56" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G56),G56&gt;=0),G56,NA())</x:f>
+        <x:v>500000</x:v>
+      </x:c>
       <x:c r="J56" s="1"/>
       <x:c r="K56" s="1"/>
       <x:c r="L56" s="1"/>
     </x:row>
-    <x:row r="57" ht="22" customHeight="1">
+    <x:row r="57" ht="15" hidden="0" customHeight="1">
       <x:c r="A57" s="1"/>
       <x:c r="B57" s="1"/>
       <x:c r="C57" s="1"/>
       <x:c r="D57" s="1"/>
       <x:c r="E57" s="1"/>
-      <x:c r="F57" s="1"/>
-      <x:c r="G57" s="1"/>
-      <x:c r="H57" s="1"/>
-      <x:c r="I57" s="1"/>
+      <x:c r="F57" s="5" t="str">
+        <x:v>Monthly capex</x:v>
+      </x:c>
+      <x:c r="G57" s="34" t="n">
+        <x:v>25000</x:v>
+      </x:c>
+      <x:c r="H57" s="5" t="str">
+        <x:v>Paid at month-end</x:v>
+      </x:c>
+      <x:c r="I57" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G57),G57&gt;=0),G57,NA())</x:f>
+        <x:v>25000</x:v>
+      </x:c>
       <x:c r="J57" s="1"/>
       <x:c r="K57" s="1"/>
       <x:c r="L57" s="1"/>
     </x:row>
-    <x:row r="58" ht="22" customHeight="1">
+    <x:row r="58" ht="26.399999618530273" hidden="0" customHeight="1">
       <x:c r="A58" s="1"/>
       <x:c r="B58" s="1"/>
       <x:c r="C58" s="1"/>
       <x:c r="D58" s="1"/>
       <x:c r="E58" s="1"/>
-      <x:c r="F58" s="1"/>
-      <x:c r="G58" s="1"/>
-      <x:c r="H58" s="1"/>
-      <x:c r="I58" s="1"/>
+      <x:c r="F58" s="5" t="str">
+        <x:v>Existing monthly depreciation</x:v>
+      </x:c>
+      <x:c r="G58" s="34" t="n">
+        <x:v>20000</x:v>
+      </x:c>
+      <x:c r="H58" s="5" t="str">
+        <x:v>Remaining old asset basis capped</x:v>
+      </x:c>
+      <x:c r="I58" s="28" t="n">
+        <x:f>IF(AND(ISNUMBER(G58),G58&gt;=0),G58,NA())</x:f>
+        <x:v>20000</x:v>
+      </x:c>
       <x:c r="J58" s="1"/>
       <x:c r="K58" s="1"/>
       <x:c r="L58" s="1"/>
@@ -3007,6 +6927,7 @@
   <x:mergeCells>
     <x:mergeCell ref="F5:K6"/>
     <x:mergeCell ref="C31:K32"/>
+    <x:mergeCell ref="F8:I10"/>
   </x:mergeCells>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="D5">
@@ -3205,7 +7126,7 @@
         <x:f>J7-SUM(K7,H7:I7)</x:f>
         <x:v>-15327.159999999974</x:v>
       </x:c>
-      <x:c r="M7" s="24" t="n">
+      <x:c r="M7" s="44" t="n">
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="N7" s="24" t="n">
@@ -3253,7 +7174,7 @@
         <x:f>J8-SUM(K8,H8:I8)</x:f>
         <x:v>-16485.75</x:v>
       </x:c>
-      <x:c r="M8" s="24" t="n">
+      <x:c r="M8" s="44" t="n">
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="N8" s="24" t="n">
@@ -3301,7 +7222,7 @@
         <x:f>J9-SUM(K9,H9:I9)</x:f>
         <x:v>-5247.8399999999965</x:v>
       </x:c>
-      <x:c r="M9" s="24" t="n">
+      <x:c r="M9" s="44" t="n">
         <x:v>0.94</x:v>
       </x:c>
       <x:c r="N9" s="24" t="n">
@@ -3349,7 +7270,7 @@
         <x:f>J10-SUM(K10,H10:I10)</x:f>
         <x:v>-17547.440000000002</x:v>
       </x:c>
-      <x:c r="M10" s="24" t="n">
+      <x:c r="M10" s="44" t="n">
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="N10" s="24" t="n">
@@ -3397,7 +7318,7 @@
         <x:f>J11-SUM(K11,H11:I11)</x:f>
         <x:v>-18660.25999999995</x:v>
       </x:c>
-      <x:c r="M11" s="24" t="n">
+      <x:c r="M11" s="44" t="n">
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="N11" s="24" t="n">
@@ -3445,7 +7366,7 @@
         <x:f>J12-SUM(K12,H12:I12)</x:f>
         <x:v>-6707.039999999979</x:v>
       </x:c>
-      <x:c r="M12" s="24" t="n">
+      <x:c r="M12" s="44" t="n">
         <x:v>0.92</x:v>
       </x:c>
       <x:c r="N12" s="24" t="n">
@@ -3493,7 +7414,7 @@
         <x:f>J13-SUM(K13,H13:I13)</x:f>
         <x:v>-5167.4000000000815</x:v>
       </x:c>
-      <x:c r="M13" s="24" t="n">
+      <x:c r="M13" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N13" s="24" t="n">
@@ -3541,7 +7462,7 @@
         <x:f>J14-SUM(K14,H14:I14)</x:f>
         <x:v>-5862.640000000014</x:v>
       </x:c>
-      <x:c r="M14" s="24" t="n">
+      <x:c r="M14" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N14" s="24" t="n">
@@ -3589,7 +7510,7 @@
         <x:f>J15-SUM(K15,H15:I15)</x:f>
         <x:v>1422.4199999999837</x:v>
       </x:c>
-      <x:c r="M15" s="24" t="n">
+      <x:c r="M15" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N15" s="24" t="n">
@@ -3637,7 +7558,7 @@
         <x:f>J16-SUM(K16,H16:I16)</x:f>
         <x:v>-7374.159999999974</x:v>
       </x:c>
-      <x:c r="M16" s="24" t="n">
+      <x:c r="M16" s="44" t="n">
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="N16" s="24" t="n">
@@ -3685,7 +7606,7 @@
         <x:f>J17-SUM(K17,H17:I17)</x:f>
         <x:v>-8031.040000000037</x:v>
       </x:c>
-      <x:c r="M17" s="24" t="n">
+      <x:c r="M17" s="44" t="n">
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="N17" s="24" t="n">
@@ -3733,7 +7654,7 @@
         <x:f>J18-SUM(K18,H18:I18)</x:f>
         <x:v>-26.89999999999418</x:v>
       </x:c>
-      <x:c r="M18" s="24" t="n">
+      <x:c r="M18" s="44" t="n">
         <x:v>0.98</x:v>
       </x:c>
       <x:c r="N18" s="24" t="n">
@@ -3781,7 +7702,7 @@
         <x:f>J19-SUM(K19,H19:I19)</x:f>
         <x:v>-650</x:v>
       </x:c>
-      <x:c r="M19" s="24" t="n">
+      <x:c r="M19" s="44" t="n">
         <x:v>1.02</x:v>
       </x:c>
       <x:c r="N19" s="24" t="n">
@@ -3829,7 +7750,7 @@
         <x:f>J20-SUM(K20,H20:I20)</x:f>
         <x:v>-890.8999999999651</x:v>
       </x:c>
-      <x:c r="M20" s="24" t="n">
+      <x:c r="M20" s="44" t="n">
         <x:v>1.02</x:v>
       </x:c>
       <x:c r="N20" s="24" t="n">
@@ -3877,7 +7798,7 @@
         <x:f>J21-SUM(K21,H21:I21)</x:f>
         <x:v>4391.059999999969</x:v>
       </x:c>
-      <x:c r="M21" s="24" t="n">
+      <x:c r="M21" s="44" t="n">
         <x:v>1.02</x:v>
       </x:c>
       <x:c r="N21" s="24" t="n">
@@ -3925,7 +7846,7 @@
         <x:f>J22-SUM(K22,H22:I22)</x:f>
         <x:v>-2874.4800000000396</x:v>
       </x:c>
-      <x:c r="M22" s="24" t="n">
+      <x:c r="M22" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N22" s="24" t="n">
@@ -3973,7 +7894,7 @@
         <x:f>J23-SUM(K23,H23:I23)</x:f>
         <x:v>-3058.3600000000442</x:v>
       </x:c>
-      <x:c r="M23" s="24" t="n">
+      <x:c r="M23" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N23" s="24" t="n">
@@ -4021,7 +7942,7 @@
         <x:f>J24-SUM(K24,H24:I24)</x:f>
         <x:v>2931.179999999993</x:v>
       </x:c>
-      <x:c r="M24" s="24" t="n">
+      <x:c r="M24" s="44" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="N24" s="24" t="n">
@@ -4069,7 +7990,7 @@
         <x:f>J25-SUM(K25,H25:I25)</x:f>
         <x:v>-760.3318099999451</x:v>
       </x:c>
-      <x:c r="M25" s="24" t="n">
+      <x:c r="M25" s="44" t="n">
         <x:v>1.01</x:v>
       </x:c>
       <x:c r="N25" s="24" t="n">
@@ -4117,7 +8038,7 @@
         <x:f>J26-SUM(K26,H26:I26)</x:f>
         <x:v>-450.43854000000283</x:v>
       </x:c>
-      <x:c r="M26" s="24" t="n">
+      <x:c r="M26" s="44" t="n">
         <x:v>1.01</x:v>
       </x:c>
       <x:c r="N26" s="24" t="n">
@@ -4165,7 +8086,7 @@
         <x:f>J27-SUM(K27,H27:I27)</x:f>
         <x:v>4878.13440000001</x:v>
       </x:c>
-      <x:c r="M27" s="24" t="n">
+      <x:c r="M27" s="44" t="n">
         <x:v>1.01</x:v>
       </x:c>
       <x:c r="N27" s="24" t="n">
@@ -4213,7 +8134,7 @@
         <x:f>J28-SUM(K28,H28:I28)</x:f>
         <x:v>4476.454706260003</x:v>
       </x:c>
-      <x:c r="M28" s="24" t="n">
+      <x:c r="M28" s="44" t="n">
         <x:v>1.04</x:v>
       </x:c>
       <x:c r="N28" s="24" t="n">
@@ -4261,7 +8182,7 @@
         <x:f>J29-SUM(K29,H29:I29)</x:f>
         <x:v>5342.912921239971</x:v>
       </x:c>
-      <x:c r="M29" s="24" t="n">
+      <x:c r="M29" s="44" t="n">
         <x:v>1.04</x:v>
       </x:c>
       <x:c r="N29" s="24" t="n">
@@ -4309,7 +8230,7 @@
         <x:f>J30-SUM(K30,H30:I30)</x:f>
         <x:v>8883.938041320012</x:v>
       </x:c>
-      <x:c r="M30" s="24" t="n">
+      <x:c r="M30" s="44" t="n">
         <x:v>1.04</x:v>
       </x:c>
       <x:c r="N30" s="24" t="n">
@@ -4357,7 +8278,7 @@
         <x:f>J31-SUM(K31,H31:I31)</x:f>
         <x:v>600.9036351472023</x:v>
       </x:c>
-      <x:c r="M31" s="24" t="n">
+      <x:c r="M31" s="44" t="n">
         <x:v>1.01</x:v>
       </x:c>
       <x:c r="N31" s="24" t="n">
@@ -4405,7 +8326,7 @@
         <x:f>J32-SUM(K32,H32:I32)</x:f>
         <x:v>1087.6262698639184</x:v>
       </x:c>
-      <x:c r="M32" s="24" t="n">
+      <x:c r="M32" s="44" t="n">
         <x:v>1.01</x:v>
       </x:c>
       <x:c r="N32" s="24" t="n">
@@ -4453,7 +8374,7 @@
         <x:f>J33-SUM(K33,H33:I33)</x:f>
         <x:v>6861.897541790357</x:v>
       </x:c>
-      <x:c r="M33" s="24" t="n">
+      <x:c r="M33" s="44" t="n">
         <x:v>1.01</x:v>
       </x:c>
       <x:c r="N33" s="24" t="n">
@@ -4501,7 +8422,7 @@
         <x:f>J34-SUM(K34,H34:I34)</x:f>
         <x:v>12347.417166740692</x:v>
       </x:c>
-      <x:c r="M34" s="24" t="n">
+      <x:c r="M34" s="44" t="n">
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="N34" s="24" t="n">
@@ -4549,7 +8470,7 @@
         <x:f>J35-SUM(K35,H35:I35)</x:f>
         <x:v>13927.539965096395</x:v>
       </x:c>
-      <x:c r="M35" s="24" t="n">
+      <x:c r="M35" s="44" t="n">
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="N35" s="24" t="n">
@@ -4597,7 +8518,7 @@
         <x:f>J36-SUM(K36,H36:I36)</x:f>
         <x:v>15500.323968276673</x:v>
       </x:c>
-      <x:c r="M36" s="24" t="n">
+      <x:c r="M36" s="44" t="n">
         <x:v>1.08</x:v>
       </x:c>
       <x:c r="N36" s="24" t="n">
@@ -4645,7 +8566,7 @@
         <x:f>J37-SUM(K37,H37:I37)</x:f>
         <x:v>21332.92522801197</x:v>
       </x:c>
-      <x:c r="M37" s="24" t="n">
+      <x:c r="M37" s="44" t="n">
         <x:v>1.13</x:v>
       </x:c>
       <x:c r="N37" s="24" t="n">
@@ -4693,7 +8614,7 @@
         <x:f>J38-SUM(K38,H38:I38)</x:f>
         <x:v>23709.991745545936</x:v>
       </x:c>
-      <x:c r="M38" s="24" t="n">
+      <x:c r="M38" s="44" t="n">
         <x:v>1.13</x:v>
       </x:c>
       <x:c r="N38" s="24" t="n">
@@ -4741,7 +8662,7 @@
         <x:f>J39-SUM(K39,H39:I39)</x:f>
         <x:v>22263.282456913672</x:v>
       </x:c>
-      <x:c r="M39" s="24" t="n">
+      <x:c r="M39" s="44" t="n">
         <x:v>1.13</x:v>
       </x:c>
       <x:c r="N39" s="24" t="n">
@@ -4789,7 +8710,7 @@
         <x:f>J40-SUM(K40,H40:I40)</x:f>
         <x:v>28850.020471755066</x:v>
       </x:c>
-      <x:c r="M40" s="24" t="n">
+      <x:c r="M40" s="44" t="n">
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="N40" s="24" t="n">
@@ -4837,7 +8758,7 @@
         <x:f>J41-SUM(K41,H41:I41)</x:f>
         <x:v>32532.953805316705</x:v>
       </x:c>
-      <x:c r="M41" s="24" t="n">
+      <x:c r="M41" s="44" t="n">
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="N41" s="24" t="n">
@@ -4885,7 +8806,7 @@
         <x:f>J42-SUM(K42,H42:I42)</x:f>
         <x:v>28228.63352903165</x:v>
       </x:c>
-      <x:c r="M42" s="24" t="n">
+      <x:c r="M42" s="44" t="n">
         <x:v>1.17</x:v>
       </x:c>
       <x:c r="N42" s="24" t="n">
@@ -5765,28 +9686,28 @@
       <x:c r="H13" s="21"/>
       <x:c r="I13" s="21"/>
       <x:c r="J13" s="27" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
+        <x:f>'Statements'!D14</x:f>
         <x:v>20000</x:v>
       </x:c>
       <x:c r="K13" s="27" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Statements'!E14</x:f>
+        <x:v>20416.666666666668</x:v>
       </x:c>
       <x:c r="L13" s="27" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Statements'!F14</x:f>
+        <x:v>20833.333333333332</x:v>
       </x:c>
       <x:c r="M13" s="27" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Statements'!G14</x:f>
+        <x:v>21250</x:v>
       </x:c>
       <x:c r="N13" s="27" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Statements'!H14</x:f>
+        <x:v>21666.666666666668</x:v>
       </x:c>
       <x:c r="O13" s="27" t="n">
-        <x:f>'Assumptions'!$G$12</x:f>
-        <x:v>20000</x:v>
+        <x:f>'Statements'!I14</x:f>
+        <x:v>22083.333333333332</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="22" customHeight="1">
@@ -5801,29 +9722,29 @@
       <x:c r="G14" s="21"/>
       <x:c r="H14" s="21"/>
       <x:c r="I14" s="21"/>
-      <x:c r="J14" s="28" t="n">
-        <x:f>J11-J13</x:f>
+      <x:c r="J14" s="27" t="n">
+        <x:f>'Statements'!D15</x:f>
         <x:v>-16332.635949999938</x:v>
       </x:c>
-      <x:c r="K14" s="28" t="n">
-        <x:f>K11-K13</x:f>
-        <x:v>-1296.6943311800133</x:v>
-      </x:c>
-      <x:c r="L14" s="28" t="n">
-        <x:f>L11-L13</x:f>
-        <x:v>-11449.572553198523</x:v>
-      </x:c>
-      <x:c r="M14" s="28" t="n">
-        <x:f>M11-M13</x:f>
-        <x:v>21775.28110011376</x:v>
-      </x:c>
-      <x:c r="N14" s="28" t="n">
-        <x:f>N11-N13</x:f>
-        <x:v>47306.19943047158</x:v>
-      </x:c>
-      <x:c r="O14" s="28" t="n">
-        <x:f>O11-O13</x:f>
-        <x:v>69611.60780610342</x:v>
+      <x:c r="K14" s="27" t="n">
+        <x:f>'Statements'!E15</x:f>
+        <x:v>-1713.3609978466811</x:v>
+      </x:c>
+      <x:c r="L14" s="27" t="n">
+        <x:f>'Statements'!F15</x:f>
+        <x:v>-12282.905886531855</x:v>
+      </x:c>
+      <x:c r="M14" s="27" t="n">
+        <x:f>'Statements'!G15</x:f>
+        <x:v>20525.28110011376</x:v>
+      </x:c>
+      <x:c r="N14" s="27" t="n">
+        <x:f>'Statements'!H15</x:f>
+        <x:v>45639.532763804906</x:v>
+      </x:c>
+      <x:c r="O14" s="27" t="n">
+        <x:f>'Statements'!I15</x:f>
+        <x:v>67528.27447277009</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="22" customHeight="1">
@@ -5839,28 +9760,28 @@
       <x:c r="H15" s="21"/>
       <x:c r="I15" s="21"/>
       <x:c r="J15" s="27" t="n">
-        <x:f>MAX(0,J14)*'Assumptions'!$G$14</x:f>
+        <x:f>'Statements'!D21</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="K15" s="27" t="n">
-        <x:f>MAX(0,K14)*'Assumptions'!$G$14</x:f>
+        <x:f>'Statements'!E21</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="L15" s="27" t="n">
-        <x:f>MAX(0,L14)*'Assumptions'!$G$14</x:f>
+        <x:f>'Statements'!F21</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="M15" s="27" t="n">
-        <x:f>MAX(0,M14)*'Assumptions'!$G$14</x:f>
-        <x:v>5443.82027502844</x:v>
+        <x:f>'Statements'!G21</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="N15" s="27" t="n">
-        <x:f>MAX(0,N14)*'Assumptions'!$G$14</x:f>
-        <x:v>11826.549857617894</x:v>
+        <x:f>'Statements'!H21</x:f>
+        <x:v>4125.644424051714</x:v>
       </x:c>
       <x:c r="O15" s="27" t="n">
-        <x:f>MAX(0,O14)*'Assumptions'!$G$14</x:f>
-        <x:v>17402.901951525855</x:v>
+        <x:f>'Statements'!I21</x:f>
+        <x:v>15965.401951525857</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="22" customHeight="1">
@@ -5876,28 +9797,28 @@
       <x:c r="H16" s="21"/>
       <x:c r="I16" s="21"/>
       <x:c r="J16" s="27" t="n">
-        <x:f>J7*'Assumptions'!$G$10/30</x:f>
-        <x:v>1062189.2082666666</x:v>
+        <x:f>'Working Capital'!D14</x:f>
+        <x:v>1152835.9196000001</x:v>
       </x:c>
       <x:c r="K16" s="27" t="n">
-        <x:f>K7*'Assumptions'!$G$10/30</x:f>
-        <x:v>1126573.8317532064</x:v>
+        <x:f>'Working Capital'!E14</x:f>
+        <x:v>815270.8239784902</x:v>
       </x:c>
       <x:c r="L16" s="27" t="n">
-        <x:f>L7*'Assumptions'!$G$10/30</x:f>
-        <x:v>1126820.6214427678</x:v>
+        <x:f>'Working Capital'!F14</x:f>
+        <x:v>820948.1565063401</x:v>
       </x:c>
       <x:c r="M16" s="27" t="n">
-        <x:f>M7*'Assumptions'!$G$10/30</x:f>
-        <x:v>1241282.5573966268</x:v>
+        <x:f>'Working Capital'!G14</x:f>
+        <x:v>894551.9830214974</x:v>
       </x:c>
       <x:c r="N16" s="27" t="n">
-        <x:f>N7*'Assumptions'!$G$10/30</x:f>
-        <x:v>1337846.413129588</x:v>
+        <x:f>'Working Capital'!H14</x:f>
+        <x:v>966439.7705030178</x:v>
       </x:c>
       <x:c r="O16" s="27" t="n">
-        <x:f>O7*'Assumptions'!$G$10/30</x:f>
-        <x:v>1427848.191395222</x:v>
+        <x:f>'Working Capital'!I14</x:f>
+        <x:v>1032574.9584508934</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="22" customHeight="1">
@@ -5913,28 +9834,28 @@
       <x:c r="H17" s="21"/>
       <x:c r="I17" s="21"/>
       <x:c r="J17" s="27" t="n">
-        <x:f>J8*'Assumptions'!$G$11/30</x:f>
-        <x:v>330571.5199999999</x:v>
+        <x:f>'Working Capital'!D22</x:f>
+        <x:v>247928.64</x:v>
       </x:c>
       <x:c r="K17" s="27" t="n">
-        <x:f>K8*'Assumptions'!$G$11/30</x:f>
-        <x:v>353027.3002916667</x:v>
+        <x:f>'Working Capital'!E22</x:f>
+        <x:v>264770.47521875007</x:v>
       </x:c>
       <x:c r="L17" s="27" t="n">
-        <x:f>L8*'Assumptions'!$G$11/30</x:f>
-        <x:v>355547.97485062486</x:v>
+        <x:f>'Working Capital'!F22</x:f>
+        <x:v>266660.9811379687</x:v>
       </x:c>
       <x:c r="M17" s="27" t="n">
-        <x:f>M8*'Assumptions'!$G$11/30</x:f>
-        <x:v>394336.97856571863</x:v>
+        <x:f>'Working Capital'!G22</x:f>
+        <x:v>295752.733924289</x:v>
       </x:c>
       <x:c r="N17" s="27" t="n">
-        <x:f>N8*'Assumptions'!$G$11/30</x:f>
-        <x:v>427947.26683927415</x:v>
+        <x:f>'Working Capital'!H22</x:f>
+        <x:v>320960.45012945565</x:v>
       </x:c>
       <x:c r="O17" s="27" t="n">
-        <x:f>O8*'Assumptions'!$G$11/30</x:f>
-        <x:v>459876.02296526986</x:v>
+        <x:f>'Working Capital'!I22</x:f>
+        <x:v>344907.01722395245</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="22" customHeight="1">
@@ -5950,28 +9871,28 @@
       <x:c r="H18" s="21"/>
       <x:c r="I18" s="21"/>
       <x:c r="J18" s="27" t="n">
-        <x:f>(J16-J17)-(I7*'Assumptions'!$G$10/30-I8*'Assumptions'!$G$11/30)</x:f>
-        <x:v>26548.201600000146</x:v>
-      </x:c>
-      <x:c r="K18" s="28" t="n">
-        <x:f>(K16-K17)-(J16-J17)</x:f>
-        <x:v>41928.843194872956</x:v>
-      </x:c>
-      <x:c r="L18" s="28" t="n">
-        <x:f>(L16-L17)-(K16-K17)</x:f>
-        <x:v>-2273.8848693966866</x:v>
-      </x:c>
-      <x:c r="M18" s="28" t="n">
-        <x:f>(M16-M17)-(L16-L17)</x:f>
-        <x:v>75672.93223876518</x:v>
-      </x:c>
-      <x:c r="N18" s="28" t="n">
-        <x:f>(N16-N17)-(M16-M17)</x:f>
-        <x:v>62953.567459405516</x:v>
-      </x:c>
-      <x:c r="O18" s="28" t="n">
-        <x:f>(O16-O17)-(N16-N17)</x:f>
-        <x:v>58073.02213963843</x:v>
+        <x:f>'Statements'!D29-'Statements'!D30</x:f>
+        <x:v>184907.27960000013</x:v>
+      </x:c>
+      <x:c r="K18" s="27" t="n">
+        <x:f>'Statements'!E29-'Statements'!E30</x:f>
+        <x:v>-354406.93084026</x:v>
+      </x:c>
+      <x:c r="L18" s="27" t="n">
+        <x:f>'Statements'!F29-'Statements'!F30</x:f>
+        <x:v>3786.826608631294</x:v>
+      </x:c>
+      <x:c r="M18" s="27" t="n">
+        <x:f>'Statements'!G29-'Statements'!G30</x:f>
+        <x:v>44512.07372883696</x:v>
+      </x:c>
+      <x:c r="N18" s="27" t="n">
+        <x:f>'Statements'!H29-'Statements'!H30</x:f>
+        <x:v>46680.07127635379</x:v>
+      </x:c>
+      <x:c r="O18" s="27" t="n">
+        <x:f>'Statements'!I29-'Statements'!I30</x:f>
+        <x:v>42188.62085337879</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="22" customHeight="1">
@@ -5987,27 +9908,27 @@
       <x:c r="H19" s="21"/>
       <x:c r="I19" s="21"/>
       <x:c r="J19" s="27" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
+        <x:f>'Statements'!D32</x:f>
         <x:v>25000</x:v>
       </x:c>
       <x:c r="K19" s="27" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
+        <x:f>'Statements'!E32</x:f>
         <x:v>25000</x:v>
       </x:c>
       <x:c r="L19" s="27" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
+        <x:f>'Statements'!F32</x:f>
         <x:v>25000</x:v>
       </x:c>
       <x:c r="M19" s="27" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
+        <x:f>'Statements'!G32</x:f>
         <x:v>25000</x:v>
       </x:c>
       <x:c r="N19" s="27" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
+        <x:f>'Statements'!H32</x:f>
         <x:v>25000</x:v>
       </x:c>
       <x:c r="O19" s="27" t="n">
-        <x:f>'Assumptions'!$G$13</x:f>
+        <x:f>'Statements'!I32</x:f>
         <x:v>25000</x:v>
       </x:c>
     </x:row>
@@ -6015,7 +9936,7 @@
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="1"/>
       <x:c r="C20" s="1" t="str">
-        <x:v>Operating cash after capex</x:v>
+        <x:v>Net change in cash after principal</x:v>
       </x:c>
       <x:c r="D20" s="21"/>
       <x:c r="E20" s="21"/>
@@ -6023,29 +9944,29 @@
       <x:c r="G20" s="21"/>
       <x:c r="H20" s="21"/>
       <x:c r="I20" s="21"/>
-      <x:c r="J20" s="28" t="n">
-        <x:f>J14-J15+J13-J18-J19</x:f>
-        <x:v>-47880.837550000084</x:v>
-      </x:c>
-      <x:c r="K20" s="28" t="n">
-        <x:f>K14-K15+K13-K18-K19</x:f>
-        <x:v>-48225.53752605297</x:v>
-      </x:c>
-      <x:c r="L20" s="28" t="n">
-        <x:f>L14-L15+L13-L18-L19</x:f>
-        <x:v>-14175.687683801836</x:v>
-      </x:c>
-      <x:c r="M20" s="28" t="n">
-        <x:f>M14-M15+M13-M18-M19</x:f>
-        <x:v>-64341.47141367986</x:v>
-      </x:c>
-      <x:c r="N20" s="28" t="n">
-        <x:f>N14-N15+N13-N18-N19</x:f>
-        <x:v>-32473.917886551833</x:v>
-      </x:c>
-      <x:c r="O20" s="28" t="n">
-        <x:f>O14-O15+O13-O18-O19</x:f>
-        <x:v>-10864.316285060864</x:v>
+      <x:c r="J20" s="27" t="n">
+        <x:f>'Statements'!D34</x:f>
+        <x:v>-220239.91555000006</x:v>
+      </x:c>
+      <x:c r="K20" s="27" t="n">
+        <x:f>'Statements'!E34</x:f>
+        <x:v>334176.9031757467</x:v>
+      </x:c>
+      <x:c r="L20" s="27" t="n">
+        <x:f>'Statements'!F34</x:f>
+        <x:v>-34103.06582849648</x:v>
+      </x:c>
+      <x:c r="M20" s="27" t="n">
+        <x:f>'Statements'!G34</x:f>
+        <x:v>-41536.7926287232</x:v>
+      </x:c>
+      <x:c r="N20" s="27" t="n">
+        <x:f>'Statements'!H34</x:f>
+        <x:v>-22232.84960326727</x:v>
+      </x:c>
+      <x:c r="O20" s="27" t="n">
+        <x:f>'Statements'!I34</x:f>
+        <x:v>-7209.081665467878</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="22" customHeight="1">
@@ -6061,28 +9982,28 @@
       <x:c r="H21" s="21"/>
       <x:c r="I21" s="21"/>
       <x:c r="J21" s="27" t="n">
-        <x:f>'Assumptions'!$G$9</x:f>
+        <x:f>'Statements'!D26</x:f>
         <x:v>500000</x:v>
       </x:c>
-      <x:c r="K21" s="28" t="n">
-        <x:f>J22</x:f>
-        <x:v>452119.16244999995</x:v>
-      </x:c>
-      <x:c r="L21" s="28" t="n">
-        <x:f>K22</x:f>
-        <x:v>403893.624923947</x:v>
-      </x:c>
-      <x:c r="M21" s="28" t="n">
-        <x:f>L22</x:f>
-        <x:v>389717.93724014517</x:v>
-      </x:c>
-      <x:c r="N21" s="28" t="n">
-        <x:f>M22</x:f>
-        <x:v>325376.4658264653</x:v>
-      </x:c>
-      <x:c r="O21" s="28" t="n">
-        <x:f>N22</x:f>
-        <x:v>292902.54793991346</x:v>
+      <x:c r="K21" s="27" t="n">
+        <x:f>'Statements'!E26</x:f>
+        <x:v>279760.08444999997</x:v>
+      </x:c>
+      <x:c r="L21" s="27" t="n">
+        <x:f>'Statements'!F26</x:f>
+        <x:v>613936.9876257466</x:v>
+      </x:c>
+      <x:c r="M21" s="27" t="n">
+        <x:f>'Statements'!G26</x:f>
+        <x:v>579833.9217972502</x:v>
+      </x:c>
+      <x:c r="N21" s="27" t="n">
+        <x:f>'Statements'!H26</x:f>
+        <x:v>538297.129168527</x:v>
+      </x:c>
+      <x:c r="O21" s="27" t="n">
+        <x:f>'Statements'!I26</x:f>
+        <x:v>516064.2795652597</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="22" customHeight="1">
@@ -6097,29 +10018,29 @@
       <x:c r="G22" s="21"/>
       <x:c r="H22" s="21"/>
       <x:c r="I22" s="21"/>
-      <x:c r="J22" s="28" t="n">
-        <x:f>SUM(J20:J21)</x:f>
-        <x:v>452119.16244999995</x:v>
-      </x:c>
-      <x:c r="K22" s="28" t="n">
-        <x:f>SUM(K20:K21)</x:f>
-        <x:v>403893.624923947</x:v>
-      </x:c>
-      <x:c r="L22" s="28" t="n">
-        <x:f>SUM(L20:L21)</x:f>
-        <x:v>389717.93724014517</x:v>
-      </x:c>
-      <x:c r="M22" s="28" t="n">
-        <x:f>SUM(M20:M21)</x:f>
-        <x:v>325376.4658264653</x:v>
-      </x:c>
-      <x:c r="N22" s="28" t="n">
-        <x:f>SUM(N20:N21)</x:f>
-        <x:v>292902.54793991346</x:v>
-      </x:c>
-      <x:c r="O22" s="28" t="n">
-        <x:f>SUM(O20:O21)</x:f>
-        <x:v>282038.2316548526</x:v>
+      <x:c r="J22" s="27" t="n">
+        <x:f>'Statements'!D35</x:f>
+        <x:v>279760.08444999997</x:v>
+      </x:c>
+      <x:c r="K22" s="27" t="n">
+        <x:f>'Statements'!E35</x:f>
+        <x:v>613936.9876257466</x:v>
+      </x:c>
+      <x:c r="L22" s="27" t="n">
+        <x:f>'Statements'!F35</x:f>
+        <x:v>579833.9217972502</x:v>
+      </x:c>
+      <x:c r="M22" s="27" t="n">
+        <x:f>'Statements'!G35</x:f>
+        <x:v>538297.129168527</x:v>
+      </x:c>
+      <x:c r="N22" s="27" t="n">
+        <x:f>'Statements'!H35</x:f>
+        <x:v>516064.2795652597</x:v>
+      </x:c>
+      <x:c r="O22" s="27" t="n">
+        <x:f>'Statements'!I35</x:f>
+        <x:v>508855.1978997918</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="22" customHeight="1">
@@ -10022,13 +13943,13 @@
   <x:cols>
     <x:col min="1" max="1" width="3" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="3" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="27" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="27" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="27" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="27" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="27" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="27" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="27" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="42" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="17" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="17" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="17" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="17" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="17" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="17" hidden="0" customWidth="1"/>
     <x:col min="10" max="10" width="17" hidden="0" customWidth="1"/>
     <x:col min="11" max="11" width="17" hidden="0" customWidth="1"/>
     <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
@@ -10052,7 +13973,7 @@
       <x:c r="A2" s="1"/>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="2" t="str">
-        <x:v>Decision ownership and approval</x:v>
+        <x:v>Collections and supplier payments</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
       <x:c r="E2" s="1"/>
@@ -10082,9 +14003,12 @@
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1"/>
       <x:c r="C4" s="1" t="str">
-        <x:v>Roles and deadlines are proposed within a synthetic case.</x:v>
-      </x:c>
-      <x:c r="D4" s="1"/>
+        <x:v>Case selected</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:f>'Assumptions'!D4</x:f>
+        <x:v>Base</x:v>
+      </x:c>
       <x:c r="E4" s="1"/>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1"/>
@@ -10108,134 +14032,164 @@
       <x:c r="K5" s="1"/>
       <x:c r="L5" s="1"/>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+    <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1"/>
-      <x:c r="C6" s="14" t="str">
-        <x:v>Action</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>Proposed owner</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>Due from approval</x:v>
-      </x:c>
-      <x:c r="F6" s="14" t="str">
-        <x:v>Trigger / evidence</x:v>
-      </x:c>
-      <x:c r="G6" s="14" t="str">
-        <x:v>Approval needed</x:v>
-      </x:c>
-      <x:c r="H6" s="14" t="str">
-        <x:v>Status</x:v>
-      </x:c>
-      <x:c r="I6" s="14" t="str">
-        <x:v>Evidence link</x:v>
+      <x:c r="C6" s="1"/>
+      <x:c r="D6" s="20" t="d">
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="d">
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="d">
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G6" s="20" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H6" s="20" t="d">
+        <x:v>2026-11-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I6" s="20" t="d">
+        <x:v>2026-12-01T00:00:00.000Z</x:v>
       </x:c>
       <x:c r="J6" s="1"/>
       <x:c r="K6" s="1"/>
       <x:c r="L6" s="1"/>
     </x:row>
-    <x:row r="7" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1"/>
-      <x:c r="C7" s="5" t="str">
-        <x:v>Validate price and cost assumptions</x:v>
-      </x:c>
-      <x:c r="D7" s="5" t="str">
-        <x:v>Finance + Sales</x:v>
-      </x:c>
-      <x:c r="E7" s="5" t="str">
-        <x:v>Day 5</x:v>
-      </x:c>
-      <x:c r="F7" s="5" t="str">
-        <x:v>July driver variance reconciled</x:v>
-      </x:c>
-      <x:c r="G7" s="5" t="str">
-        <x:v>Finance lead</x:v>
-      </x:c>
-      <x:c r="H7" s="5" t="str">
-        <x:v>Proposed</x:v>
-      </x:c>
-      <x:c r="I7" s="5" t="str"/>
+      <x:c r="C7" s="1" t="str">
+        <x:v>Credit revenue</x:v>
+      </x:c>
+      <x:c r="D7" s="27" t="n">
+        <x:f>'Monthly'!J7</x:f>
+        <x:v>910447.8928</x:v>
+      </x:c>
+      <x:c r="E7" s="27" t="n">
+        <x:f>'Monthly'!K7</x:f>
+        <x:v>965634.71293132</x:v>
+      </x:c>
+      <x:c r="F7" s="27" t="n">
+        <x:f>'Monthly'!L7</x:f>
+        <x:v>965846.2469509438</x:v>
+      </x:c>
+      <x:c r="G7" s="27" t="n">
+        <x:f>'Monthly'!M7</x:f>
+        <x:v>1063956.4777685371</x:v>
+      </x:c>
+      <x:c r="H7" s="27" t="n">
+        <x:f>'Monthly'!N7</x:f>
+        <x:v>1146725.4969682184</x:v>
+      </x:c>
+      <x:c r="I7" s="27" t="n">
+        <x:f>'Monthly'!O7</x:f>
+        <x:v>1223869.8783387616</x:v>
+      </x:c>
       <x:c r="J7" s="1"/>
       <x:c r="K7" s="1"/>
       <x:c r="L7" s="1"/>
     </x:row>
-    <x:row r="8" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1"/>
-      <x:c r="C8" s="5" t="str">
-        <x:v>Review low-margin contracts</x:v>
-      </x:c>
-      <x:c r="D8" s="5" t="str">
-        <x:v>Commercial + Operations</x:v>
-      </x:c>
-      <x:c r="E8" s="5" t="str">
-        <x:v>Day 10</x:v>
-      </x:c>
-      <x:c r="F8" s="5" t="str">
-        <x:v>EBITDA margin below 3%</x:v>
-      </x:c>
-      <x:c r="G8" s="5" t="str">
-        <x:v>Commercial lead</x:v>
-      </x:c>
-      <x:c r="H8" s="5" t="str">
-        <x:v>Proposed</x:v>
-      </x:c>
-      <x:c r="I8" s="5" t="str"/>
+      <x:c r="C8" s="1" t="str">
+        <x:v>Current-month collections</x:v>
+      </x:c>
+      <x:c r="D8" s="27" t="n">
+        <x:f>D7*'Assumptions'!$I$43</x:f>
+        <x:v>227611.9732</x:v>
+      </x:c>
+      <x:c r="E8" s="27" t="n">
+        <x:f>E7*'Assumptions'!$I$43</x:f>
+        <x:v>241408.67823283</x:v>
+      </x:c>
+      <x:c r="F8" s="27" t="n">
+        <x:f>F7*'Assumptions'!$I$43</x:f>
+        <x:v>241461.56173773596</x:v>
+      </x:c>
+      <x:c r="G8" s="27" t="n">
+        <x:f>G7*'Assumptions'!$I$43</x:f>
+        <x:v>265989.1194421343</x:v>
+      </x:c>
+      <x:c r="H8" s="27" t="n">
+        <x:f>H7*'Assumptions'!$I$43</x:f>
+        <x:v>286681.3742420546</x:v>
+      </x:c>
+      <x:c r="I8" s="27" t="n">
+        <x:f>I7*'Assumptions'!$I$43</x:f>
+        <x:v>305967.4695846904</x:v>
+      </x:c>
       <x:c r="J8" s="1"/>
       <x:c r="K8" s="1"/>
       <x:c r="L8" s="1"/>
     </x:row>
-    <x:row r="9" ht="26.399999618530273" hidden="0" customHeight="1">
+    <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1"/>
-      <x:c r="C9" s="5" t="str">
-        <x:v>Reforecast and approve actions</x:v>
-      </x:c>
-      <x:c r="D9" s="5" t="str">
-        <x:v>Finance lead</x:v>
-      </x:c>
-      <x:c r="E9" s="5" t="str">
-        <x:v>Monthly close + 5 days</x:v>
-      </x:c>
-      <x:c r="F9" s="5" t="str">
-        <x:v>Volume misses plan &gt;5%</x:v>
-      </x:c>
-      <x:c r="G9" s="5" t="str">
-        <x:v>Business unit lead</x:v>
-      </x:c>
-      <x:c r="H9" s="5" t="str">
-        <x:v>Proposed</x:v>
-      </x:c>
-      <x:c r="I9" s="5" t="str"/>
+      <x:c r="C9" s="1" t="str">
+        <x:v>Prior-month collections</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E9" s="27" t="n">
+        <x:f>D7*'Assumptions'!$I$44</x:f>
+        <x:v>591791.13032</x:v>
+      </x:c>
+      <x:c r="F9" s="27" t="n">
+        <x:f>E7*'Assumptions'!$I$44</x:f>
+        <x:v>627662.563405358</x:v>
+      </x:c>
+      <x:c r="G9" s="27" t="n">
+        <x:f>F7*'Assumptions'!$I$44</x:f>
+        <x:v>627800.0605181135</x:v>
+      </x:c>
+      <x:c r="H9" s="27" t="n">
+        <x:f>G7*'Assumptions'!$I$44</x:f>
+        <x:v>691571.7105495492</x:v>
+      </x:c>
+      <x:c r="I9" s="27" t="n">
+        <x:f>H7*'Assumptions'!$I$44</x:f>
+        <x:v>745371.573029342</x:v>
+      </x:c>
       <x:c r="J9" s="1"/>
       <x:c r="K9" s="1"/>
       <x:c r="L9" s="1"/>
     </x:row>
-    <x:row r="10" ht="15" hidden="0" customHeight="1">
+    <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1"/>
-      <x:c r="C10" s="5" t="str">
-        <x:v>Monitor cash and capex</x:v>
-      </x:c>
-      <x:c r="D10" s="5" t="str">
-        <x:v>Treasury + Operations</x:v>
-      </x:c>
-      <x:c r="E10" s="5" t="str">
-        <x:v>Weekly</x:v>
-      </x:c>
-      <x:c r="F10" s="5" t="str">
-        <x:v>Cash below $250,000</x:v>
-      </x:c>
-      <x:c r="G10" s="5" t="str">
-        <x:v>Finance lead</x:v>
-      </x:c>
-      <x:c r="H10" s="5" t="str">
-        <x:v>Proposed</x:v>
-      </x:c>
-      <x:c r="I10" s="5" t="str"/>
+      <x:c r="C10" s="1" t="str">
+        <x:v>Two-month prior collections</x:v>
+      </x:c>
+      <x:c r="D10" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E10" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="n">
+        <x:f>D7*(1-SUM('Assumptions'!$I$43:$I$44))</x:f>
+        <x:v>91044.78927999998</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="n">
+        <x:f>E7*(1-SUM('Assumptions'!$I$43:$I$44))</x:f>
+        <x:v>96563.47129313198</x:v>
+      </x:c>
+      <x:c r="H10" s="27" t="n">
+        <x:f>F7*(1-SUM('Assumptions'!$I$43:$I$44))</x:f>
+        <x:v>96584.62469509436</x:v>
+      </x:c>
+      <x:c r="I10" s="27" t="n">
+        <x:f>G7*(1-SUM('Assumptions'!$I$43:$I$44))</x:f>
+        <x:v>106395.64777685369</x:v>
+      </x:c>
       <x:c r="J10" s="1"/>
       <x:c r="K10" s="1"/>
       <x:c r="L10" s="1"/>
@@ -10243,13 +14197,33 @@
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
-      <x:c r="H11" s="1"/>
-      <x:c r="I11" s="1"/>
+      <x:c r="C11" s="1" t="str">
+        <x:v>Opening AR collections</x:v>
+      </x:c>
+      <x:c r="D11" s="27" t="n">
+        <x:f>'Assumptions'!I42</x:f>
+        <x:v>550000</x:v>
+      </x:c>
+      <x:c r="E11" s="27" t="n">
+        <x:f>'Assumptions'!I41-'Assumptions'!I42</x:f>
+        <x:v>470000</x:v>
+      </x:c>
+      <x:c r="F11" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G11" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H11" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I11" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J11" s="1"/>
       <x:c r="K11" s="1"/>
       <x:c r="L11" s="1"/>
@@ -10257,13 +14231,33 @@
     <x:row r="12" ht="22" customHeight="1">
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1"/>
-      <x:c r="C12" s="1"/>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
-      <x:c r="H12" s="1"/>
-      <x:c r="I12" s="1"/>
+      <x:c r="C12" s="1" t="str">
+        <x:v>Total receipts</x:v>
+      </x:c>
+      <x:c r="D12" s="28" t="n">
+        <x:f>SUM(D8:D11)</x:f>
+        <x:v>777611.9732</x:v>
+      </x:c>
+      <x:c r="E12" s="28" t="n">
+        <x:f>SUM(E8:E11)</x:f>
+        <x:v>1303199.80855283</x:v>
+      </x:c>
+      <x:c r="F12" s="28" t="n">
+        <x:f>SUM(F8:F11)</x:f>
+        <x:v>960168.914423094</x:v>
+      </x:c>
+      <x:c r="G12" s="28" t="n">
+        <x:f>SUM(G8:G11)</x:f>
+        <x:v>990352.6512533798</x:v>
+      </x:c>
+      <x:c r="H12" s="28" t="n">
+        <x:f>SUM(H8:H11)</x:f>
+        <x:v>1074837.709486698</x:v>
+      </x:c>
+      <x:c r="I12" s="28" t="n">
+        <x:f>SUM(I8:I11)</x:f>
+        <x:v>1157734.6903908863</x:v>
+      </x:c>
       <x:c r="J12" s="1"/>
       <x:c r="K12" s="1"/>
       <x:c r="L12" s="1"/>
@@ -10271,13 +14265,33 @@
     <x:row r="13" ht="22" customHeight="1">
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1"/>
-      <x:c r="C13" s="1"/>
-      <x:c r="D13" s="1"/>
-      <x:c r="E13" s="1"/>
-      <x:c r="F13" s="1"/>
-      <x:c r="G13" s="1"/>
-      <x:c r="H13" s="1"/>
-      <x:c r="I13" s="1"/>
+      <x:c r="C13" s="1" t="str">
+        <x:v>Opening AR</x:v>
+      </x:c>
+      <x:c r="D13" s="27" t="n">
+        <x:f>'Assumptions'!I41</x:f>
+        <x:v>1020000</x:v>
+      </x:c>
+      <x:c r="E13" s="28" t="n">
+        <x:f>D14</x:f>
+        <x:v>1152835.9196000001</x:v>
+      </x:c>
+      <x:c r="F13" s="28" t="n">
+        <x:f>E14</x:f>
+        <x:v>815270.8239784902</x:v>
+      </x:c>
+      <x:c r="G13" s="28" t="n">
+        <x:f>F14</x:f>
+        <x:v>820948.1565063401</x:v>
+      </x:c>
+      <x:c r="H13" s="28" t="n">
+        <x:f>G14</x:f>
+        <x:v>894551.9830214974</x:v>
+      </x:c>
+      <x:c r="I13" s="28" t="n">
+        <x:f>H14</x:f>
+        <x:v>966439.7705030178</x:v>
+      </x:c>
       <x:c r="J13" s="1"/>
       <x:c r="K13" s="1"/>
       <x:c r="L13" s="1"/>
@@ -10285,13 +14299,33 @@
     <x:row r="14" ht="22" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
-      <x:c r="C14" s="1"/>
-      <x:c r="D14" s="1"/>
-      <x:c r="E14" s="1"/>
-      <x:c r="F14" s="1"/>
-      <x:c r="G14" s="1"/>
-      <x:c r="H14" s="1"/>
-      <x:c r="I14" s="1"/>
+      <x:c r="C14" s="1" t="str">
+        <x:v>Closing AR</x:v>
+      </x:c>
+      <x:c r="D14" s="28" t="n">
+        <x:f>D13+D7-D12</x:f>
+        <x:v>1152835.9196000001</x:v>
+      </x:c>
+      <x:c r="E14" s="28" t="n">
+        <x:f>E13+E7-E12</x:f>
+        <x:v>815270.8239784902</x:v>
+      </x:c>
+      <x:c r="F14" s="28" t="n">
+        <x:f>F13+F7-F12</x:f>
+        <x:v>820948.1565063401</x:v>
+      </x:c>
+      <x:c r="G14" s="28" t="n">
+        <x:f>G13+G7-G12</x:f>
+        <x:v>894551.9830214974</x:v>
+      </x:c>
+      <x:c r="H14" s="28" t="n">
+        <x:f>H13+H7-H12</x:f>
+        <x:v>966439.7705030178</x:v>
+      </x:c>
+      <x:c r="I14" s="28" t="n">
+        <x:f>I13+I7-I12</x:f>
+        <x:v>1032574.9584508934</x:v>
+      </x:c>
       <x:c r="J14" s="1"/>
       <x:c r="K14" s="1"/>
       <x:c r="L14" s="1"/>
@@ -10300,12 +14334,12 @@
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
       <x:c r="C15" s="1"/>
-      <x:c r="D15" s="1"/>
-      <x:c r="E15" s="1"/>
-      <x:c r="F15" s="1"/>
-      <x:c r="G15" s="1"/>
-      <x:c r="H15" s="1"/>
-      <x:c r="I15" s="1"/>
+      <x:c r="D15" s="21"/>
+      <x:c r="E15" s="21"/>
+      <x:c r="F15" s="21"/>
+      <x:c r="G15" s="21"/>
+      <x:c r="H15" s="21"/>
+      <x:c r="I15" s="21"/>
       <x:c r="J15" s="1"/>
       <x:c r="K15" s="1"/>
       <x:c r="L15" s="1"/>
@@ -10313,13 +14347,33 @@
     <x:row r="16" ht="22" customHeight="1">
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1"/>
-      <x:c r="C16" s="1"/>
-      <x:c r="D16" s="1"/>
-      <x:c r="E16" s="1"/>
-      <x:c r="F16" s="1"/>
-      <x:c r="G16" s="1"/>
-      <x:c r="H16" s="1"/>
-      <x:c r="I16" s="1"/>
+      <x:c r="C16" s="1" t="str">
+        <x:v>Supplier purchases</x:v>
+      </x:c>
+      <x:c r="D16" s="27" t="n">
+        <x:f>'Monthly'!J8</x:f>
+        <x:v>495857.2799999999</x:v>
+      </x:c>
+      <x:c r="E16" s="27" t="n">
+        <x:f>'Monthly'!K8</x:f>
+        <x:v>529540.9504375</x:v>
+      </x:c>
+      <x:c r="F16" s="27" t="n">
+        <x:f>'Monthly'!L8</x:f>
+        <x:v>533321.9622759373</x:v>
+      </x:c>
+      <x:c r="G16" s="27" t="n">
+        <x:f>'Monthly'!M8</x:f>
+        <x:v>591505.4678485779</x:v>
+      </x:c>
+      <x:c r="H16" s="27" t="n">
+        <x:f>'Monthly'!N8</x:f>
+        <x:v>641920.9002589112</x:v>
+      </x:c>
+      <x:c r="I16" s="27" t="n">
+        <x:f>'Monthly'!O8</x:f>
+        <x:v>689814.0344479048</x:v>
+      </x:c>
       <x:c r="J16" s="1"/>
       <x:c r="K16" s="1"/>
       <x:c r="L16" s="1"/>
@@ -10327,13 +14381,33 @@
     <x:row r="17" ht="22" customHeight="1">
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1"/>
-      <x:c r="C17" s="1"/>
-      <x:c r="D17" s="1"/>
-      <x:c r="E17" s="1"/>
-      <x:c r="F17" s="1"/>
-      <x:c r="G17" s="1"/>
-      <x:c r="H17" s="1"/>
-      <x:c r="I17" s="1"/>
+      <x:c r="C17" s="1" t="str">
+        <x:v>Current-month payments</x:v>
+      </x:c>
+      <x:c r="D17" s="27" t="n">
+        <x:f>D16*'Assumptions'!$I$46</x:f>
+        <x:v>247928.63999999996</x:v>
+      </x:c>
+      <x:c r="E17" s="27" t="n">
+        <x:f>E16*'Assumptions'!$I$46</x:f>
+        <x:v>264770.47521875</x:v>
+      </x:c>
+      <x:c r="F17" s="27" t="n">
+        <x:f>F16*'Assumptions'!$I$46</x:f>
+        <x:v>266660.98113796866</x:v>
+      </x:c>
+      <x:c r="G17" s="27" t="n">
+        <x:f>G16*'Assumptions'!$I$46</x:f>
+        <x:v>295752.73392428894</x:v>
+      </x:c>
+      <x:c r="H17" s="27" t="n">
+        <x:f>H16*'Assumptions'!$I$46</x:f>
+        <x:v>320960.4501294556</x:v>
+      </x:c>
+      <x:c r="I17" s="27" t="n">
+        <x:f>I16*'Assumptions'!$I$46</x:f>
+        <x:v>344907.0172239524</x:v>
+      </x:c>
       <x:c r="J17" s="1"/>
       <x:c r="K17" s="1"/>
       <x:c r="L17" s="1"/>
@@ -10341,13 +14415,33 @@
     <x:row r="18" ht="22" customHeight="1">
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1"/>
-      <x:c r="C18" s="1"/>
-      <x:c r="D18" s="1"/>
-      <x:c r="E18" s="1"/>
-      <x:c r="F18" s="1"/>
-      <x:c r="G18" s="1"/>
-      <x:c r="H18" s="1"/>
-      <x:c r="I18" s="1"/>
+      <x:c r="C18" s="1" t="str">
+        <x:v>Prior-month payments</x:v>
+      </x:c>
+      <x:c r="D18" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="E18" s="27" t="n">
+        <x:f>D16*(1-'Assumptions'!$I$46)</x:f>
+        <x:v>247928.63999999996</x:v>
+      </x:c>
+      <x:c r="F18" s="27" t="n">
+        <x:f>E16*(1-'Assumptions'!$I$46)</x:f>
+        <x:v>264770.47521875</x:v>
+      </x:c>
+      <x:c r="G18" s="27" t="n">
+        <x:f>F16*(1-'Assumptions'!$I$46)</x:f>
+        <x:v>266660.98113796866</x:v>
+      </x:c>
+      <x:c r="H18" s="27" t="n">
+        <x:f>G16*(1-'Assumptions'!$I$46)</x:f>
+        <x:v>295752.73392428894</x:v>
+      </x:c>
+      <x:c r="I18" s="27" t="n">
+        <x:f>H16*(1-'Assumptions'!$I$46)</x:f>
+        <x:v>320960.4501294556</x:v>
+      </x:c>
       <x:c r="J18" s="1"/>
       <x:c r="K18" s="1"/>
       <x:c r="L18" s="1"/>
@@ -10355,13 +14449,33 @@
     <x:row r="19" ht="22" customHeight="1">
       <x:c r="A19" s="1"/>
       <x:c r="B19" s="1"/>
-      <x:c r="C19" s="1"/>
-      <x:c r="D19" s="1"/>
-      <x:c r="E19" s="1"/>
-      <x:c r="F19" s="1"/>
-      <x:c r="G19" s="1"/>
-      <x:c r="H19" s="1"/>
-      <x:c r="I19" s="1"/>
+      <x:c r="C19" s="1" t="str">
+        <x:v>Opening AP payment</x:v>
+      </x:c>
+      <x:c r="D19" s="27" t="n">
+        <x:f>'Assumptions'!I45</x:f>
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="E19" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G19" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="H19" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="I19" s="28" t="n">
+        <x:f>0</x:f>
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="J19" s="1"/>
       <x:c r="K19" s="1"/>
       <x:c r="L19" s="1"/>
@@ -10369,13 +14483,33 @@
     <x:row r="20" ht="22" customHeight="1">
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="1"/>
-      <x:c r="C20" s="1"/>
-      <x:c r="D20" s="1"/>
-      <x:c r="E20" s="1"/>
-      <x:c r="F20" s="1"/>
-      <x:c r="G20" s="1"/>
-      <x:c r="H20" s="1"/>
-      <x:c r="I20" s="1"/>
+      <x:c r="C20" s="1" t="str">
+        <x:v>Total supplier payments</x:v>
+      </x:c>
+      <x:c r="D20" s="28" t="n">
+        <x:f>SUM(D17:D19)</x:f>
+        <x:v>547928.6399999999</x:v>
+      </x:c>
+      <x:c r="E20" s="28" t="n">
+        <x:f>SUM(E17:E19)</x:f>
+        <x:v>512699.11521874997</x:v>
+      </x:c>
+      <x:c r="F20" s="28" t="n">
+        <x:f>SUM(F17:F19)</x:f>
+        <x:v>531431.4563567187</x:v>
+      </x:c>
+      <x:c r="G20" s="28" t="n">
+        <x:f>SUM(G17:G19)</x:f>
+        <x:v>562413.7150622576</x:v>
+      </x:c>
+      <x:c r="H20" s="28" t="n">
+        <x:f>SUM(H17:H19)</x:f>
+        <x:v>616713.1840537445</x:v>
+      </x:c>
+      <x:c r="I20" s="28" t="n">
+        <x:f>SUM(I17:I19)</x:f>
+        <x:v>665867.467353408</x:v>
+      </x:c>
       <x:c r="J20" s="1"/>
       <x:c r="K20" s="1"/>
       <x:c r="L20" s="1"/>
@@ -10383,13 +14517,33 @@
     <x:row r="21" ht="22" customHeight="1">
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="1"/>
-      <x:c r="C21" s="1"/>
-      <x:c r="D21" s="1"/>
-      <x:c r="E21" s="1"/>
-      <x:c r="F21" s="1"/>
-      <x:c r="G21" s="1"/>
-      <x:c r="H21" s="1"/>
-      <x:c r="I21" s="1"/>
+      <x:c r="C21" s="1" t="str">
+        <x:v>Opening AP</x:v>
+      </x:c>
+      <x:c r="D21" s="27" t="n">
+        <x:f>'Assumptions'!I45</x:f>
+        <x:v>300000</x:v>
+      </x:c>
+      <x:c r="E21" s="28" t="n">
+        <x:f>D22</x:f>
+        <x:v>247928.64</x:v>
+      </x:c>
+      <x:c r="F21" s="28" t="n">
+        <x:f>E22</x:f>
+        <x:v>264770.47521875007</x:v>
+      </x:c>
+      <x:c r="G21" s="28" t="n">
+        <x:f>F22</x:f>
+        <x:v>266660.9811379687</x:v>
+      </x:c>
+      <x:c r="H21" s="28" t="n">
+        <x:f>G22</x:f>
+        <x:v>295752.733924289</x:v>
+      </x:c>
+      <x:c r="I21" s="28" t="n">
+        <x:f>H22</x:f>
+        <x:v>320960.45012945565</x:v>
+      </x:c>
       <x:c r="J21" s="1"/>
       <x:c r="K21" s="1"/>
       <x:c r="L21" s="1"/>
@@ -10397,13 +14551,33 @@
     <x:row r="22" ht="22" customHeight="1">
       <x:c r="A22" s="1"/>
       <x:c r="B22" s="1"/>
-      <x:c r="C22" s="1"/>
-      <x:c r="D22" s="1"/>
-      <x:c r="E22" s="1"/>
-      <x:c r="F22" s="1"/>
-      <x:c r="G22" s="1"/>
-      <x:c r="H22" s="1"/>
-      <x:c r="I22" s="1"/>
+      <x:c r="C22" s="1" t="str">
+        <x:v>Closing AP</x:v>
+      </x:c>
+      <x:c r="D22" s="28" t="n">
+        <x:f>D21+D16-D20</x:f>
+        <x:v>247928.64</x:v>
+      </x:c>
+      <x:c r="E22" s="28" t="n">
+        <x:f>E21+E16-E20</x:f>
+        <x:v>264770.47521875007</x:v>
+      </x:c>
+      <x:c r="F22" s="28" t="n">
+        <x:f>F21+F16-F20</x:f>
+        <x:v>266660.9811379687</x:v>
+      </x:c>
+      <x:c r="G22" s="28" t="n">
+        <x:f>G21+G16-G20</x:f>
+        <x:v>295752.733924289</x:v>
+      </x:c>
+      <x:c r="H22" s="28" t="n">
+        <x:f>H21+H16-H20</x:f>
+        <x:v>320960.45012945565</x:v>
+      </x:c>
+      <x:c r="I22" s="28" t="n">
+        <x:f>I21+I16-I20</x:f>
+        <x:v>344907.01722395245</x:v>
+      </x:c>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="1"/>
       <x:c r="L22" s="1"/>
@@ -10412,12 +14586,12 @@
       <x:c r="A23" s="1"/>
       <x:c r="B23" s="1"/>
       <x:c r="C23" s="1"/>
-      <x:c r="D23" s="1"/>
-      <x:c r="E23" s="1"/>
-      <x:c r="F23" s="1"/>
-      <x:c r="G23" s="1"/>
-      <x:c r="H23" s="1"/>
-      <x:c r="I23" s="1"/>
+      <x:c r="D23" s="21"/>
+      <x:c r="E23" s="21"/>
+      <x:c r="F23" s="21"/>
+      <x:c r="G23" s="21"/>
+      <x:c r="H23" s="21"/>
+      <x:c r="I23" s="21"/>
       <x:c r="J23" s="1"/>
       <x:c r="K23" s="1"/>
       <x:c r="L23" s="1"/>
@@ -10426,12 +14600,12 @@
       <x:c r="A24" s="1"/>
       <x:c r="B24" s="1"/>
       <x:c r="C24" s="1"/>
-      <x:c r="D24" s="1"/>
-      <x:c r="E24" s="1"/>
-      <x:c r="F24" s="1"/>
-      <x:c r="G24" s="1"/>
-      <x:c r="H24" s="1"/>
-      <x:c r="I24" s="1"/>
+      <x:c r="D24" s="21"/>
+      <x:c r="E24" s="21"/>
+      <x:c r="F24" s="21"/>
+      <x:c r="G24" s="21"/>
+      <x:c r="H24" s="21"/>
+      <x:c r="I24" s="21"/>
       <x:c r="J24" s="1"/>
       <x:c r="K24" s="1"/>
       <x:c r="L24" s="1"/>
@@ -10440,12 +14614,12 @@
       <x:c r="A25" s="1"/>
       <x:c r="B25" s="1"/>
       <x:c r="C25" s="1"/>
-      <x:c r="D25" s="1"/>
-      <x:c r="E25" s="1"/>
-      <x:c r="F25" s="1"/>
-      <x:c r="G25" s="1"/>
-      <x:c r="H25" s="1"/>
-      <x:c r="I25" s="1"/>
+      <x:c r="D25" s="21"/>
+      <x:c r="E25" s="21"/>
+      <x:c r="F25" s="21"/>
+      <x:c r="G25" s="21"/>
+      <x:c r="H25" s="21"/>
+      <x:c r="I25" s="21"/>
       <x:c r="J25" s="1"/>
       <x:c r="K25" s="1"/>
       <x:c r="L25" s="1"/>
@@ -10453,41 +14627,43 @@
     <x:row r="26" ht="22" customHeight="1">
       <x:c r="A26" s="1"/>
       <x:c r="B26" s="1"/>
-      <x:c r="C26" s="1"/>
-      <x:c r="D26" s="1"/>
-      <x:c r="E26" s="1"/>
-      <x:c r="F26" s="1"/>
-      <x:c r="G26" s="1"/>
-      <x:c r="H26" s="1"/>
-      <x:c r="I26" s="1"/>
-      <x:c r="J26" s="1"/>
-      <x:c r="K26" s="1"/>
+      <x:c r="C26" s="5" t="str">
+        <x:v>Opening AR uses two dated collection buckets. Sales collect 25% / 65% / 10%.</x:v>
+      </x:c>
+      <x:c r="D26" s="35"/>
+      <x:c r="E26" s="35"/>
+      <x:c r="F26" s="35"/>
+      <x:c r="G26" s="35"/>
+      <x:c r="H26" s="35"/>
+      <x:c r="I26" s="35"/>
+      <x:c r="J26" s="5"/>
+      <x:c r="K26" s="5"/>
       <x:c r="L26" s="1"/>
     </x:row>
     <x:row r="27" ht="22" customHeight="1">
       <x:c r="A27" s="1"/>
       <x:c r="B27" s="1"/>
-      <x:c r="C27" s="1"/>
-      <x:c r="D27" s="1"/>
-      <x:c r="E27" s="1"/>
-      <x:c r="F27" s="1"/>
-      <x:c r="G27" s="1"/>
-      <x:c r="H27" s="1"/>
-      <x:c r="I27" s="1"/>
-      <x:c r="J27" s="1"/>
-      <x:c r="K27" s="1"/>
+      <x:c r="C27" s="5"/>
+      <x:c r="D27" s="35"/>
+      <x:c r="E27" s="35"/>
+      <x:c r="F27" s="35"/>
+      <x:c r="G27" s="35"/>
+      <x:c r="H27" s="35"/>
+      <x:c r="I27" s="35"/>
+      <x:c r="J27" s="5"/>
+      <x:c r="K27" s="5"/>
       <x:c r="L27" s="1"/>
     </x:row>
     <x:row r="28" ht="22" customHeight="1">
       <x:c r="A28" s="1"/>
       <x:c r="B28" s="1"/>
       <x:c r="C28" s="1"/>
-      <x:c r="D28" s="1"/>
-      <x:c r="E28" s="1"/>
-      <x:c r="F28" s="1"/>
-      <x:c r="G28" s="1"/>
-      <x:c r="H28" s="1"/>
-      <x:c r="I28" s="1"/>
+      <x:c r="D28" s="21"/>
+      <x:c r="E28" s="21"/>
+      <x:c r="F28" s="21"/>
+      <x:c r="G28" s="21"/>
+      <x:c r="H28" s="21"/>
+      <x:c r="I28" s="21"/>
       <x:c r="J28" s="1"/>
       <x:c r="K28" s="1"/>
       <x:c r="L28" s="1"/>
@@ -10496,12 +14672,12 @@
       <x:c r="A29" s="1"/>
       <x:c r="B29" s="1"/>
       <x:c r="C29" s="1"/>
-      <x:c r="D29" s="1"/>
-      <x:c r="E29" s="1"/>
-      <x:c r="F29" s="1"/>
-      <x:c r="G29" s="1"/>
-      <x:c r="H29" s="1"/>
-      <x:c r="I29" s="1"/>
+      <x:c r="D29" s="21"/>
+      <x:c r="E29" s="21"/>
+      <x:c r="F29" s="21"/>
+      <x:c r="G29" s="21"/>
+      <x:c r="H29" s="21"/>
+      <x:c r="I29" s="21"/>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="1"/>
       <x:c r="L29" s="1"/>
@@ -10510,12 +14686,12 @@
       <x:c r="A30" s="1"/>
       <x:c r="B30" s="1"/>
       <x:c r="C30" s="1"/>
-      <x:c r="D30" s="1"/>
-      <x:c r="E30" s="1"/>
-      <x:c r="F30" s="1"/>
-      <x:c r="G30" s="1"/>
-      <x:c r="H30" s="1"/>
-      <x:c r="I30" s="1"/>
+      <x:c r="D30" s="21"/>
+      <x:c r="E30" s="21"/>
+      <x:c r="F30" s="21"/>
+      <x:c r="G30" s="21"/>
+      <x:c r="H30" s="21"/>
+      <x:c r="I30" s="21"/>
       <x:c r="J30" s="1"/>
       <x:c r="K30" s="1"/>
       <x:c r="L30" s="1"/>
@@ -10524,12 +14700,12 @@
       <x:c r="A31" s="1"/>
       <x:c r="B31" s="1"/>
       <x:c r="C31" s="1"/>
-      <x:c r="D31" s="1"/>
-      <x:c r="E31" s="1"/>
-      <x:c r="F31" s="1"/>
-      <x:c r="G31" s="1"/>
-      <x:c r="H31" s="1"/>
-      <x:c r="I31" s="1"/>
+      <x:c r="D31" s="21"/>
+      <x:c r="E31" s="21"/>
+      <x:c r="F31" s="21"/>
+      <x:c r="G31" s="21"/>
+      <x:c r="H31" s="21"/>
+      <x:c r="I31" s="21"/>
       <x:c r="J31" s="1"/>
       <x:c r="K31" s="1"/>
       <x:c r="L31" s="1"/>
@@ -10538,12 +14714,12 @@
       <x:c r="A32" s="1"/>
       <x:c r="B32" s="1"/>
       <x:c r="C32" s="1"/>
-      <x:c r="D32" s="1"/>
-      <x:c r="E32" s="1"/>
-      <x:c r="F32" s="1"/>
-      <x:c r="G32" s="1"/>
-      <x:c r="H32" s="1"/>
-      <x:c r="I32" s="1"/>
+      <x:c r="D32" s="21"/>
+      <x:c r="E32" s="21"/>
+      <x:c r="F32" s="21"/>
+      <x:c r="G32" s="21"/>
+      <x:c r="H32" s="21"/>
+      <x:c r="I32" s="21"/>
       <x:c r="J32" s="1"/>
       <x:c r="K32" s="1"/>
       <x:c r="L32" s="1"/>
@@ -10552,12 +14728,12 @@
       <x:c r="A33" s="1"/>
       <x:c r="B33" s="1"/>
       <x:c r="C33" s="1"/>
-      <x:c r="D33" s="1"/>
-      <x:c r="E33" s="1"/>
-      <x:c r="F33" s="1"/>
-      <x:c r="G33" s="1"/>
-      <x:c r="H33" s="1"/>
-      <x:c r="I33" s="1"/>
+      <x:c r="D33" s="21"/>
+      <x:c r="E33" s="21"/>
+      <x:c r="F33" s="21"/>
+      <x:c r="G33" s="21"/>
+      <x:c r="H33" s="21"/>
+      <x:c r="I33" s="21"/>
       <x:c r="J33" s="1"/>
       <x:c r="K33" s="1"/>
       <x:c r="L33" s="1"/>
@@ -10566,12 +14742,12 @@
       <x:c r="A34" s="1"/>
       <x:c r="B34" s="1"/>
       <x:c r="C34" s="1"/>
-      <x:c r="D34" s="1"/>
-      <x:c r="E34" s="1"/>
-      <x:c r="F34" s="1"/>
-      <x:c r="G34" s="1"/>
-      <x:c r="H34" s="1"/>
-      <x:c r="I34" s="1"/>
+      <x:c r="D34" s="21"/>
+      <x:c r="E34" s="21"/>
+      <x:c r="F34" s="21"/>
+      <x:c r="G34" s="21"/>
+      <x:c r="H34" s="21"/>
+      <x:c r="I34" s="21"/>
       <x:c r="J34" s="1"/>
       <x:c r="K34" s="1"/>
       <x:c r="L34" s="1"/>
@@ -10580,12 +14756,12 @@
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="1"/>
       <x:c r="C35" s="1"/>
-      <x:c r="D35" s="1"/>
-      <x:c r="E35" s="1"/>
-      <x:c r="F35" s="1"/>
-      <x:c r="G35" s="1"/>
-      <x:c r="H35" s="1"/>
-      <x:c r="I35" s="1"/>
+      <x:c r="D35" s="21"/>
+      <x:c r="E35" s="21"/>
+      <x:c r="F35" s="21"/>
+      <x:c r="G35" s="21"/>
+      <x:c r="H35" s="21"/>
+      <x:c r="I35" s="21"/>
       <x:c r="J35" s="1"/>
       <x:c r="K35" s="1"/>
       <x:c r="L35" s="1"/>
@@ -10594,12 +14770,12 @@
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="1"/>
       <x:c r="C36" s="1"/>
-      <x:c r="D36" s="1"/>
-      <x:c r="E36" s="1"/>
-      <x:c r="F36" s="1"/>
-      <x:c r="G36" s="1"/>
-      <x:c r="H36" s="1"/>
-      <x:c r="I36" s="1"/>
+      <x:c r="D36" s="21"/>
+      <x:c r="E36" s="21"/>
+      <x:c r="F36" s="21"/>
+      <x:c r="G36" s="21"/>
+      <x:c r="H36" s="21"/>
+      <x:c r="I36" s="21"/>
       <x:c r="J36" s="1"/>
       <x:c r="K36" s="1"/>
       <x:c r="L36" s="1"/>
@@ -10608,12 +14784,12 @@
       <x:c r="A37" s="1"/>
       <x:c r="B37" s="1"/>
       <x:c r="C37" s="1"/>
-      <x:c r="D37" s="1"/>
-      <x:c r="E37" s="1"/>
-      <x:c r="F37" s="1"/>
-      <x:c r="G37" s="1"/>
-      <x:c r="H37" s="1"/>
-      <x:c r="I37" s="1"/>
+      <x:c r="D37" s="21"/>
+      <x:c r="E37" s="21"/>
+      <x:c r="F37" s="21"/>
+      <x:c r="G37" s="21"/>
+      <x:c r="H37" s="21"/>
+      <x:c r="I37" s="21"/>
       <x:c r="J37" s="1"/>
       <x:c r="K37" s="1"/>
       <x:c r="L37" s="1"/>
@@ -10622,12 +14798,12 @@
       <x:c r="A38" s="1"/>
       <x:c r="B38" s="1"/>
       <x:c r="C38" s="1"/>
-      <x:c r="D38" s="1"/>
-      <x:c r="E38" s="1"/>
-      <x:c r="F38" s="1"/>
-      <x:c r="G38" s="1"/>
-      <x:c r="H38" s="1"/>
-      <x:c r="I38" s="1"/>
+      <x:c r="D38" s="21"/>
+      <x:c r="E38" s="21"/>
+      <x:c r="F38" s="21"/>
+      <x:c r="G38" s="21"/>
+      <x:c r="H38" s="21"/>
+      <x:c r="I38" s="21"/>
       <x:c r="J38" s="1"/>
       <x:c r="K38" s="1"/>
       <x:c r="L38" s="1"/>
@@ -10636,12 +14812,12 @@
       <x:c r="A39" s="1"/>
       <x:c r="B39" s="1"/>
       <x:c r="C39" s="1"/>
-      <x:c r="D39" s="1"/>
-      <x:c r="E39" s="1"/>
-      <x:c r="F39" s="1"/>
-      <x:c r="G39" s="1"/>
-      <x:c r="H39" s="1"/>
-      <x:c r="I39" s="1"/>
+      <x:c r="D39" s="21"/>
+      <x:c r="E39" s="21"/>
+      <x:c r="F39" s="21"/>
+      <x:c r="G39" s="21"/>
+      <x:c r="H39" s="21"/>
+      <x:c r="I39" s="21"/>
       <x:c r="J39" s="1"/>
       <x:c r="K39" s="1"/>
       <x:c r="L39" s="1"/>
@@ -10650,12 +14826,12 @@
       <x:c r="A40" s="1"/>
       <x:c r="B40" s="1"/>
       <x:c r="C40" s="1"/>
-      <x:c r="D40" s="1"/>
-      <x:c r="E40" s="1"/>
-      <x:c r="F40" s="1"/>
-      <x:c r="G40" s="1"/>
-      <x:c r="H40" s="1"/>
-      <x:c r="I40" s="1"/>
+      <x:c r="D40" s="21"/>
+      <x:c r="E40" s="21"/>
+      <x:c r="F40" s="21"/>
+      <x:c r="G40" s="21"/>
+      <x:c r="H40" s="21"/>
+      <x:c r="I40" s="21"/>
       <x:c r="J40" s="1"/>
       <x:c r="K40" s="1"/>
       <x:c r="L40" s="1"/>
@@ -10664,12 +14840,12 @@
       <x:c r="A41" s="1"/>
       <x:c r="B41" s="1"/>
       <x:c r="C41" s="1"/>
-      <x:c r="D41" s="1"/>
-      <x:c r="E41" s="1"/>
-      <x:c r="F41" s="1"/>
-      <x:c r="G41" s="1"/>
-      <x:c r="H41" s="1"/>
-      <x:c r="I41" s="1"/>
+      <x:c r="D41" s="21"/>
+      <x:c r="E41" s="21"/>
+      <x:c r="F41" s="21"/>
+      <x:c r="G41" s="21"/>
+      <x:c r="H41" s="21"/>
+      <x:c r="I41" s="21"/>
       <x:c r="J41" s="1"/>
       <x:c r="K41" s="1"/>
       <x:c r="L41" s="1"/>
@@ -10678,12 +14854,12 @@
       <x:c r="A42" s="1"/>
       <x:c r="B42" s="1"/>
       <x:c r="C42" s="1"/>
-      <x:c r="D42" s="1"/>
-      <x:c r="E42" s="1"/>
-      <x:c r="F42" s="1"/>
-      <x:c r="G42" s="1"/>
-      <x:c r="H42" s="1"/>
-      <x:c r="I42" s="1"/>
+      <x:c r="D42" s="21"/>
+      <x:c r="E42" s="21"/>
+      <x:c r="F42" s="21"/>
+      <x:c r="G42" s="21"/>
+      <x:c r="H42" s="21"/>
+      <x:c r="I42" s="21"/>
       <x:c r="J42" s="1"/>
       <x:c r="K42" s="1"/>
       <x:c r="L42" s="1"/>
@@ -10692,12 +14868,12 @@
       <x:c r="A43" s="1"/>
       <x:c r="B43" s="1"/>
       <x:c r="C43" s="1"/>
-      <x:c r="D43" s="1"/>
-      <x:c r="E43" s="1"/>
-      <x:c r="F43" s="1"/>
-      <x:c r="G43" s="1"/>
-      <x:c r="H43" s="1"/>
-      <x:c r="I43" s="1"/>
+      <x:c r="D43" s="21"/>
+      <x:c r="E43" s="21"/>
+      <x:c r="F43" s="21"/>
+      <x:c r="G43" s="21"/>
+      <x:c r="H43" s="21"/>
+      <x:c r="I43" s="21"/>
       <x:c r="J43" s="1"/>
       <x:c r="K43" s="1"/>
       <x:c r="L43" s="1"/>
@@ -10706,12 +14882,12 @@
       <x:c r="A44" s="1"/>
       <x:c r="B44" s="1"/>
       <x:c r="C44" s="1"/>
-      <x:c r="D44" s="1"/>
-      <x:c r="E44" s="1"/>
-      <x:c r="F44" s="1"/>
-      <x:c r="G44" s="1"/>
-      <x:c r="H44" s="1"/>
-      <x:c r="I44" s="1"/>
+      <x:c r="D44" s="21"/>
+      <x:c r="E44" s="21"/>
+      <x:c r="F44" s="21"/>
+      <x:c r="G44" s="21"/>
+      <x:c r="H44" s="21"/>
+      <x:c r="I44" s="21"/>
       <x:c r="J44" s="1"/>
       <x:c r="K44" s="1"/>
       <x:c r="L44" s="1"/>
@@ -10720,12 +14896,12 @@
       <x:c r="A45" s="1"/>
       <x:c r="B45" s="1"/>
       <x:c r="C45" s="1"/>
-      <x:c r="D45" s="1"/>
-      <x:c r="E45" s="1"/>
-      <x:c r="F45" s="1"/>
-      <x:c r="G45" s="1"/>
-      <x:c r="H45" s="1"/>
-      <x:c r="I45" s="1"/>
+      <x:c r="D45" s="21"/>
+      <x:c r="E45" s="21"/>
+      <x:c r="F45" s="21"/>
+      <x:c r="G45" s="21"/>
+      <x:c r="H45" s="21"/>
+      <x:c r="I45" s="21"/>
       <x:c r="J45" s="1"/>
       <x:c r="K45" s="1"/>
       <x:c r="L45" s="1"/>
@@ -10734,12 +14910,12 @@
       <x:c r="A46" s="1"/>
       <x:c r="B46" s="1"/>
       <x:c r="C46" s="1"/>
-      <x:c r="D46" s="1"/>
-      <x:c r="E46" s="1"/>
-      <x:c r="F46" s="1"/>
-      <x:c r="G46" s="1"/>
-      <x:c r="H46" s="1"/>
-      <x:c r="I46" s="1"/>
+      <x:c r="D46" s="21"/>
+      <x:c r="E46" s="21"/>
+      <x:c r="F46" s="21"/>
+      <x:c r="G46" s="21"/>
+      <x:c r="H46" s="21"/>
+      <x:c r="I46" s="21"/>
       <x:c r="J46" s="1"/>
       <x:c r="K46" s="1"/>
       <x:c r="L46" s="1"/>
@@ -10748,12 +14924,12 @@
       <x:c r="A47" s="1"/>
       <x:c r="B47" s="1"/>
       <x:c r="C47" s="1"/>
-      <x:c r="D47" s="1"/>
-      <x:c r="E47" s="1"/>
-      <x:c r="F47" s="1"/>
-      <x:c r="G47" s="1"/>
-      <x:c r="H47" s="1"/>
-      <x:c r="I47" s="1"/>
+      <x:c r="D47" s="21"/>
+      <x:c r="E47" s="21"/>
+      <x:c r="F47" s="21"/>
+      <x:c r="G47" s="21"/>
+      <x:c r="H47" s="21"/>
+      <x:c r="I47" s="21"/>
       <x:c r="J47" s="1"/>
       <x:c r="K47" s="1"/>
       <x:c r="L47" s="1"/>
@@ -10762,12 +14938,12 @@
       <x:c r="A48" s="1"/>
       <x:c r="B48" s="1"/>
       <x:c r="C48" s="1"/>
-      <x:c r="D48" s="1"/>
-      <x:c r="E48" s="1"/>
-      <x:c r="F48" s="1"/>
-      <x:c r="G48" s="1"/>
-      <x:c r="H48" s="1"/>
-      <x:c r="I48" s="1"/>
+      <x:c r="D48" s="21"/>
+      <x:c r="E48" s="21"/>
+      <x:c r="F48" s="21"/>
+      <x:c r="G48" s="21"/>
+      <x:c r="H48" s="21"/>
+      <x:c r="I48" s="21"/>
       <x:c r="J48" s="1"/>
       <x:c r="K48" s="1"/>
       <x:c r="L48" s="1"/>
@@ -10776,12 +14952,12 @@
       <x:c r="A49" s="1"/>
       <x:c r="B49" s="1"/>
       <x:c r="C49" s="1"/>
-      <x:c r="D49" s="1"/>
-      <x:c r="E49" s="1"/>
-      <x:c r="F49" s="1"/>
-      <x:c r="G49" s="1"/>
-      <x:c r="H49" s="1"/>
-      <x:c r="I49" s="1"/>
+      <x:c r="D49" s="21"/>
+      <x:c r="E49" s="21"/>
+      <x:c r="F49" s="21"/>
+      <x:c r="G49" s="21"/>
+      <x:c r="H49" s="21"/>
+      <x:c r="I49" s="21"/>
       <x:c r="J49" s="1"/>
       <x:c r="K49" s="1"/>
       <x:c r="L49" s="1"/>
@@ -10790,12 +14966,12 @@
       <x:c r="A50" s="1"/>
       <x:c r="B50" s="1"/>
       <x:c r="C50" s="1"/>
-      <x:c r="D50" s="1"/>
-      <x:c r="E50" s="1"/>
-      <x:c r="F50" s="1"/>
-      <x:c r="G50" s="1"/>
-      <x:c r="H50" s="1"/>
-      <x:c r="I50" s="1"/>
+      <x:c r="D50" s="21"/>
+      <x:c r="E50" s="21"/>
+      <x:c r="F50" s="21"/>
+      <x:c r="G50" s="21"/>
+      <x:c r="H50" s="21"/>
+      <x:c r="I50" s="21"/>
       <x:c r="J50" s="1"/>
       <x:c r="K50" s="1"/>
       <x:c r="L50" s="1"/>
@@ -10804,12 +14980,12 @@
       <x:c r="A51" s="1"/>
       <x:c r="B51" s="1"/>
       <x:c r="C51" s="1"/>
-      <x:c r="D51" s="1"/>
-      <x:c r="E51" s="1"/>
-      <x:c r="F51" s="1"/>
-      <x:c r="G51" s="1"/>
-      <x:c r="H51" s="1"/>
-      <x:c r="I51" s="1"/>
+      <x:c r="D51" s="21"/>
+      <x:c r="E51" s="21"/>
+      <x:c r="F51" s="21"/>
+      <x:c r="G51" s="21"/>
+      <x:c r="H51" s="21"/>
+      <x:c r="I51" s="21"/>
       <x:c r="J51" s="1"/>
       <x:c r="K51" s="1"/>
       <x:c r="L51" s="1"/>
@@ -10818,12 +14994,12 @@
       <x:c r="A52" s="1"/>
       <x:c r="B52" s="1"/>
       <x:c r="C52" s="1"/>
-      <x:c r="D52" s="1"/>
-      <x:c r="E52" s="1"/>
-      <x:c r="F52" s="1"/>
-      <x:c r="G52" s="1"/>
-      <x:c r="H52" s="1"/>
-      <x:c r="I52" s="1"/>
+      <x:c r="D52" s="21"/>
+      <x:c r="E52" s="21"/>
+      <x:c r="F52" s="21"/>
+      <x:c r="G52" s="21"/>
+      <x:c r="H52" s="21"/>
+      <x:c r="I52" s="21"/>
       <x:c r="J52" s="1"/>
       <x:c r="K52" s="1"/>
       <x:c r="L52" s="1"/>
@@ -10832,12 +15008,12 @@
       <x:c r="A53" s="1"/>
       <x:c r="B53" s="1"/>
       <x:c r="C53" s="1"/>
-      <x:c r="D53" s="1"/>
-      <x:c r="E53" s="1"/>
-      <x:c r="F53" s="1"/>
-      <x:c r="G53" s="1"/>
-      <x:c r="H53" s="1"/>
-      <x:c r="I53" s="1"/>
+      <x:c r="D53" s="21"/>
+      <x:c r="E53" s="21"/>
+      <x:c r="F53" s="21"/>
+      <x:c r="G53" s="21"/>
+      <x:c r="H53" s="21"/>
+      <x:c r="I53" s="21"/>
       <x:c r="J53" s="1"/>
       <x:c r="K53" s="1"/>
       <x:c r="L53" s="1"/>
@@ -10846,12 +15022,12 @@
       <x:c r="A54" s="1"/>
       <x:c r="B54" s="1"/>
       <x:c r="C54" s="1"/>
-      <x:c r="D54" s="1"/>
-      <x:c r="E54" s="1"/>
-      <x:c r="F54" s="1"/>
-      <x:c r="G54" s="1"/>
-      <x:c r="H54" s="1"/>
-      <x:c r="I54" s="1"/>
+      <x:c r="D54" s="21"/>
+      <x:c r="E54" s="21"/>
+      <x:c r="F54" s="21"/>
+      <x:c r="G54" s="21"/>
+      <x:c r="H54" s="21"/>
+      <x:c r="I54" s="21"/>
       <x:c r="J54" s="1"/>
       <x:c r="K54" s="1"/>
       <x:c r="L54" s="1"/>
@@ -10860,12 +15036,12 @@
       <x:c r="A55" s="1"/>
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
-      <x:c r="D55" s="1"/>
-      <x:c r="E55" s="1"/>
-      <x:c r="F55" s="1"/>
-      <x:c r="G55" s="1"/>
-      <x:c r="H55" s="1"/>
-      <x:c r="I55" s="1"/>
+      <x:c r="D55" s="21"/>
+      <x:c r="E55" s="21"/>
+      <x:c r="F55" s="21"/>
+      <x:c r="G55" s="21"/>
+      <x:c r="H55" s="21"/>
+      <x:c r="I55" s="21"/>
       <x:c r="J55" s="1"/>
       <x:c r="K55" s="1"/>
       <x:c r="L55" s="1"/>
@@ -11012,13 +15188,9 @@
     </x:row>
   </x:sheetData>
   <x:mergeCells>
-    <x:mergeCell ref="C4:I4"/>
+    <x:mergeCell ref="D4:F4"/>
+    <x:mergeCell ref="C26:K27"/>
   </x:mergeCells>
-  <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H7:H10">
-      <x:formula1>"Proposed,In progress,Completed,Blocked"</x:formula1>
-    </x:dataValidation>
-  </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>
@@ -11059,7 +15231,7 @@
       <x:c r="A2" s="1"/>
       <x:c r="B2" s="1"/>
       <x:c r="C2" s="2" t="str">
-        <x:v>Reconciliation checks</x:v>
+        <x:v>Debt and interest</x:v>
       </x:c>
       <x:c r="D2" s="1"/>
       <x:c r="E2" s="1"/>
@@ -11088,8 +15260,13 @@
     <x:row r="4" ht="22" customHeight="1">
       <x:c r="A4" s="1"/>
       <x:c r="B4" s="1"/>
-      <x:c r="C4" s="1"/>
-      <x:c r="D4" s="1"/>
+      <x:c r="C4" s="1" t="str">
+        <x:v>Case selected</x:v>
+      </x:c>
+      <x:c r="D4" s="7" t="str">
+        <x:f>'Assumptions'!D4</x:f>
+        <x:v>Base</x:v>
+      </x:c>
       <x:c r="E4" s="1"/>
       <x:c r="F4" s="1"/>
       <x:c r="G4" s="1"/>
@@ -11113,85 +15290,130 @@
       <x:c r="K5" s="1"/>
       <x:c r="L5" s="1"/>
     </x:row>
-    <x:row r="6" ht="15" hidden="0" customHeight="1">
+    <x:row r="6" ht="22" customHeight="1">
       <x:c r="A6" s="1"/>
       <x:c r="B6" s="1"/>
-      <x:c r="C6" s="14" t="str">
-        <x:v>Check</x:v>
-      </x:c>
-      <x:c r="D6" s="14" t="str">
-        <x:v>Difference</x:v>
-      </x:c>
-      <x:c r="E6" s="14" t="str">
-        <x:v>Tolerance (USD)</x:v>
-      </x:c>
-      <x:c r="F6" s="1"/>
-      <x:c r="G6" s="1"/>
-      <x:c r="H6" s="1"/>
-      <x:c r="I6" s="1"/>
+      <x:c r="C6" s="1"/>
+      <x:c r="D6" s="20" t="d">
+        <x:v>2026-07-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="E6" s="20" t="d">
+        <x:v>2026-08-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="F6" s="20" t="d">
+        <x:v>2026-09-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="G6" s="20" t="d">
+        <x:v>2026-10-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="H6" s="20" t="d">
+        <x:v>2026-11-01T00:00:00.000Z</x:v>
+      </x:c>
+      <x:c r="I6" s="20" t="d">
+        <x:v>2026-12-01T00:00:00.000Z</x:v>
+      </x:c>
       <x:c r="J6" s="1"/>
       <x:c r="K6" s="1"/>
       <x:c r="L6" s="1"/>
     </x:row>
-    <x:row r="7" ht="15" hidden="0" customHeight="1">
+    <x:row r="7" ht="22" customHeight="1">
       <x:c r="A7" s="1"/>
       <x:c r="B7" s="1"/>
-      <x:c r="C7" s="5" t="str">
-        <x:v>July bridge</x:v>
-      </x:c>
-      <x:c r="D7" s="37" t="n">
-        <x:f>'Variance'!D13-'Variance'!D12-'Variance'!D14</x:f>
-        <x:v>1.291482476517558e-10</x:v>
-      </x:c>
-      <x:c r="E7" s="18" t="n">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="F7" s="1"/>
-      <x:c r="G7" s="1"/>
-      <x:c r="H7" s="1"/>
-      <x:c r="I7" s="1"/>
+      <x:c r="C7" s="1" t="str">
+        <x:v>Opening debt</x:v>
+      </x:c>
+      <x:c r="D7" s="27" t="n">
+        <x:f>'Assumptions'!I50</x:f>
+        <x:v>600000</x:v>
+      </x:c>
+      <x:c r="E7" s="28" t="n">
+        <x:f>D11</x:f>
+        <x:v>590000</x:v>
+      </x:c>
+      <x:c r="F7" s="28" t="n">
+        <x:f>E11</x:f>
+        <x:v>580000</x:v>
+      </x:c>
+      <x:c r="G7" s="28" t="n">
+        <x:f>F11</x:f>
+        <x:v>570000</x:v>
+      </x:c>
+      <x:c r="H7" s="28" t="n">
+        <x:f>G11</x:f>
+        <x:v>560000</x:v>
+      </x:c>
+      <x:c r="I7" s="28" t="n">
+        <x:f>H11</x:f>
+        <x:v>550000</x:v>
+      </x:c>
       <x:c r="J7" s="1"/>
       <x:c r="K7" s="1"/>
       <x:c r="L7" s="1"/>
     </x:row>
-    <x:row r="8" ht="15" hidden="0" customHeight="1">
+    <x:row r="8" ht="22" customHeight="1">
       <x:c r="A8" s="1"/>
       <x:c r="B8" s="1"/>
-      <x:c r="C8" s="5" t="str">
-        <x:v>Cash roll-forward</x:v>
-      </x:c>
-      <x:c r="D8" s="37" t="n">
-        <x:f>'Monthly'!O22-'Assumptions'!G9-SUM('Monthly'!J20:O20)</x:f>
-        <x:v>8.731149137020111e-11</x:v>
-      </x:c>
-      <x:c r="E8" s="18" t="n">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="F8" s="1"/>
-      <x:c r="G8" s="1"/>
-      <x:c r="H8" s="1"/>
-      <x:c r="I8" s="1"/>
+      <x:c r="C8" s="1" t="str">
+        <x:v>Annual interest rate</x:v>
+      </x:c>
+      <x:c r="D8" s="38" t="n">
+        <x:f>'Assumptions'!$I$51</x:f>
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="E8" s="38" t="n">
+        <x:f>'Assumptions'!$I$51</x:f>
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="F8" s="38" t="n">
+        <x:f>'Assumptions'!$I$51</x:f>
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="G8" s="38" t="n">
+        <x:f>'Assumptions'!$I$51</x:f>
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="H8" s="38" t="n">
+        <x:f>'Assumptions'!$I$51</x:f>
+        <x:v>0.08</x:v>
+      </x:c>
+      <x:c r="I8" s="38" t="n">
+        <x:f>'Assumptions'!$I$51</x:f>
+        <x:v>0.08</x:v>
+      </x:c>
       <x:c r="J8" s="1"/>
       <x:c r="K8" s="1"/>
       <x:c r="L8" s="1"/>
     </x:row>
-    <x:row r="9" ht="15" hidden="0" customHeight="1">
+    <x:row r="9" ht="22" customHeight="1">
       <x:c r="A9" s="1"/>
       <x:c r="B9" s="1"/>
-      <x:c r="C9" s="5" t="str">
-        <x:v>H1 revenue to raw inputs</x:v>
-      </x:c>
-      <x:c r="D9" s="37" t="n">
-        <x:f>SUM('Monthly'!D7:I7)-SUMPRODUCT('Source'!E7:E24,'Source'!F7:F24)</x:f>
-        <x:v>-9.313225746154785e-10</x:v>
-      </x:c>
-      <x:c r="E9" s="18" t="n">
-        <x:v>0.01</x:v>
-      </x:c>
-      <x:c r="F9" s="1"/>
-      <x:c r="G9" s="1"/>
-      <x:c r="H9" s="1"/>
-      <x:c r="I9" s="1"/>
+      <x:c r="C9" s="1" t="str">
+        <x:v>Interest expense / cash paid</x:v>
+      </x:c>
+      <x:c r="D9" s="28" t="n">
+        <x:f>D7*D8/12</x:f>
+        <x:v>4000</x:v>
+      </x:c>
+      <x:c r="E9" s="28" t="n">
+        <x:f>E7*E8/12</x:f>
+        <x:v>3933.3333333333335</x:v>
+      </x:c>
+      <x:c r="F9" s="28" t="n">
+        <x:f>F7*F8/12</x:f>
+        <x:v>3866.6666666666665</x:v>
+      </x:c>
+      <x:c r="G9" s="28" t="n">
+        <x:f>G7*G8/12</x:f>
+        <x:v>3800</x:v>
+      </x:c>
+      <x:c r="H9" s="28" t="n">
+        <x:f>H7*H8/12</x:f>
+        <x:v>3733.3333333333335</x:v>
+      </x:c>
+      <x:c r="I9" s="28" t="n">
+        <x:f>I7*I8/12</x:f>
+        <x:v>3666.6666666666665</x:v>
+      </x:c>
       <x:c r="J9" s="1"/>
       <x:c r="K9" s="1"/>
       <x:c r="L9" s="1"/>
@@ -11199,13 +15421,33 @@
     <x:row r="10" ht="22" customHeight="1">
       <x:c r="A10" s="1"/>
       <x:c r="B10" s="1"/>
-      <x:c r="C10" s="1"/>
-      <x:c r="D10" s="1"/>
-      <x:c r="E10" s="1"/>
-      <x:c r="F10" s="1"/>
-      <x:c r="G10" s="1"/>
-      <x:c r="H10" s="1"/>
-      <x:c r="I10" s="1"/>
+      <x:c r="C10" s="1" t="str">
+        <x:v>Principal repayment</x:v>
+      </x:c>
+      <x:c r="D10" s="27" t="n">
+        <x:f>MIN(D7,'Assumptions'!$I$52)</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="E10" s="27" t="n">
+        <x:f>MIN(E7,'Assumptions'!$I$52)</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="F10" s="27" t="n">
+        <x:f>MIN(F7,'Assumptions'!$I$52)</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="G10" s="27" t="n">
+        <x:f>MIN(G7,'Assumptions'!$I$52)</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="H10" s="27" t="n">
+        <x:f>MIN(H7,'Assumptions'!$I$52)</x:f>
+        <x:v>10000</x:v>
+      </x:c>
+      <x:c r="I10" s="27" t="n">
+        <x:f>MIN(I7,'Assumptions'!$I$52)</x:f>
+        <x:v>10000</x:v>
+      </x:c>
       <x:c r="J10" s="1"/>
       <x:c r="K10" s="1"/>
       <x:c r="L10" s="1"/>
@@ -11213,13 +15455,33 @@
     <x:row r="11" ht="22" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
-      <x:c r="C11" s="1"/>
-      <x:c r="D11" s="1"/>
-      <x:c r="E11" s="1"/>
-      <x:c r="F11" s="1"/>
-      <x:c r="G11" s="1"/>
-      <x:c r="H11" s="1"/>
-      <x:c r="I11" s="1"/>
+      <x:c r="C11" s="1" t="str">
+        <x:v>Closing debt</x:v>
+      </x:c>
+      <x:c r="D11" s="28" t="n">
+        <x:f>D7-D10</x:f>
+        <x:v>590000</x:v>
+      </x:c>
+      <x:c r="E11" s="28" t="n">
+        <x:f>E7-E10</x:f>
+        <x:v>580000</x:v>
+      </x:c>
+      <x:c r="F11" s="28" t="n">
+        <x:f>F7-F10</x:f>
+        <x:v>570000</x:v>
+      </x:c>
+      <x:c r="G11" s="28" t="n">
+        <x:f>G7-G10</x:f>
+        <x:v>560000</x:v>
+      </x:c>
+      <x:c r="H11" s="28" t="n">
+        <x:f>H7-H10</x:f>
+        <x:v>550000</x:v>
+      </x:c>
+      <x:c r="I11" s="28" t="n">
+        <x:f>I7-I10</x:f>
+        <x:v>540000</x:v>
+      </x:c>
       <x:c r="J11" s="1"/>
       <x:c r="K11" s="1"/>
       <x:c r="L11" s="1"/>
@@ -11228,12 +15490,12 @@
       <x:c r="A12" s="1"/>
       <x:c r="B12" s="1"/>
       <x:c r="C12" s="1"/>
-      <x:c r="D12" s="1"/>
-      <x:c r="E12" s="1"/>
-      <x:c r="F12" s="1"/>
-      <x:c r="G12" s="1"/>
-      <x:c r="H12" s="1"/>
-      <x:c r="I12" s="1"/>
+      <x:c r="D12" s="21"/>
+      <x:c r="E12" s="21"/>
+      <x:c r="F12" s="21"/>
+      <x:c r="G12" s="21"/>
+      <x:c r="H12" s="21"/>
+      <x:c r="I12" s="21"/>
       <x:c r="J12" s="1"/>
       <x:c r="K12" s="1"/>
       <x:c r="L12" s="1"/>
@@ -11242,12 +15504,12 @@
       <x:c r="A13" s="1"/>
       <x:c r="B13" s="1"/>
       <x:c r="C13" s="1"/>
-      <x:c r="D13" s="1"/>
-      <x:c r="E13" s="1"/>
-      <x:c r="F13" s="1"/>
-      <x:c r="G13" s="1"/>
-      <x:c r="H13" s="1"/>
-      <x:c r="I13" s="1"/>
+      <x:c r="D13" s="21"/>
+      <x:c r="E13" s="21"/>
+      <x:c r="F13" s="21"/>
+      <x:c r="G13" s="21"/>
+      <x:c r="H13" s="21"/>
+      <x:c r="I13" s="21"/>
       <x:c r="J13" s="1"/>
       <x:c r="K13" s="1"/>
       <x:c r="L13" s="1"/>
@@ -11256,12 +15518,12 @@
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
       <x:c r="C14" s="1"/>
-      <x:c r="D14" s="1"/>
-      <x:c r="E14" s="1"/>
-      <x:c r="F14" s="1"/>
-      <x:c r="G14" s="1"/>
-      <x:c r="H14" s="1"/>
-      <x:c r="I14" s="1"/>
+      <x:c r="D14" s="21"/>
+      <x:c r="E14" s="21"/>
+      <x:c r="F14" s="21"/>
+      <x:c r="G14" s="21"/>
+      <x:c r="H14" s="21"/>
+      <x:c r="I14" s="21"/>
       <x:c r="J14" s="1"/>
       <x:c r="K14" s="1"/>
       <x:c r="L14" s="1"/>
@@ -11270,12 +15532,12 @@
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
       <x:c r="C15" s="1"/>
-      <x:c r="D15" s="1"/>
-      <x:c r="E15" s="1"/>
-      <x:c r="F15" s="1"/>
-      <x:c r="G15" s="1"/>
-      <x:c r="H15" s="1"/>
-      <x:c r="I15" s="1"/>
+      <x:c r="D15" s="21"/>
+      <x:c r="E15" s="21"/>
+      <x:c r="F15" s="21"/>
+      <x:c r="G15" s="21"/>
+      <x:c r="H15" s="21"/>
+      <x:c r="I15" s="21"/>
       <x:c r="J15" s="1"/>
       <x:c r="K15" s="1"/>
       <x:c r="L15" s="1"/>
@@ -11284,12 +15546,12 @@
       <x:c r="A16" s="1"/>
       <x:c r="B16" s="1"/>
       <x:c r="C16" s="1"/>
-      <x:c r="D16" s="1"/>
-      <x:c r="E16" s="1"/>
-      <x:c r="F16" s="1"/>
-      <x:c r="G16" s="1"/>
-      <x:c r="H16" s="1"/>
-      <x:c r="I16" s="1"/>
+      <x:c r="D16" s="21"/>
+      <x:c r="E16" s="21"/>
+      <x:c r="F16" s="21"/>
+      <x:c r="G16" s="21"/>
+      <x:c r="H16" s="21"/>
+      <x:c r="I16" s="21"/>
       <x:c r="J16" s="1"/>
       <x:c r="K16" s="1"/>
       <x:c r="L16" s="1"/>
@@ -11298,12 +15560,12 @@
       <x:c r="A17" s="1"/>
       <x:c r="B17" s="1"/>
       <x:c r="C17" s="1"/>
-      <x:c r="D17" s="1"/>
-      <x:c r="E17" s="1"/>
-      <x:c r="F17" s="1"/>
-      <x:c r="G17" s="1"/>
-      <x:c r="H17" s="1"/>
-      <x:c r="I17" s="1"/>
+      <x:c r="D17" s="21"/>
+      <x:c r="E17" s="21"/>
+      <x:c r="F17" s="21"/>
+      <x:c r="G17" s="21"/>
+      <x:c r="H17" s="21"/>
+      <x:c r="I17" s="21"/>
       <x:c r="J17" s="1"/>
       <x:c r="K17" s="1"/>
       <x:c r="L17" s="1"/>
@@ -11312,12 +15574,12 @@
       <x:c r="A18" s="1"/>
       <x:c r="B18" s="1"/>
       <x:c r="C18" s="1"/>
-      <x:c r="D18" s="1"/>
-      <x:c r="E18" s="1"/>
-      <x:c r="F18" s="1"/>
-      <x:c r="G18" s="1"/>
-      <x:c r="H18" s="1"/>
-      <x:c r="I18" s="1"/>
+      <x:c r="D18" s="21"/>
+      <x:c r="E18" s="21"/>
+      <x:c r="F18" s="21"/>
+      <x:c r="G18" s="21"/>
+      <x:c r="H18" s="21"/>
+      <x:c r="I18" s="21"/>
       <x:c r="J18" s="1"/>
       <x:c r="K18" s="1"/>
       <x:c r="L18" s="1"/>
@@ -11326,12 +15588,12 @@
       <x:c r="A19" s="1"/>
       <x:c r="B19" s="1"/>
       <x:c r="C19" s="1"/>
-      <x:c r="D19" s="1"/>
-      <x:c r="E19" s="1"/>
-      <x:c r="F19" s="1"/>
-      <x:c r="G19" s="1"/>
-      <x:c r="H19" s="1"/>
-      <x:c r="I19" s="1"/>
+      <x:c r="D19" s="21"/>
+      <x:c r="E19" s="21"/>
+      <x:c r="F19" s="21"/>
+      <x:c r="G19" s="21"/>
+      <x:c r="H19" s="21"/>
+      <x:c r="I19" s="21"/>
       <x:c r="J19" s="1"/>
       <x:c r="K19" s="1"/>
       <x:c r="L19" s="1"/>
@@ -11340,12 +15602,12 @@
       <x:c r="A20" s="1"/>
       <x:c r="B20" s="1"/>
       <x:c r="C20" s="1"/>
-      <x:c r="D20" s="1"/>
-      <x:c r="E20" s="1"/>
-      <x:c r="F20" s="1"/>
-      <x:c r="G20" s="1"/>
-      <x:c r="H20" s="1"/>
-      <x:c r="I20" s="1"/>
+      <x:c r="D20" s="21"/>
+      <x:c r="E20" s="21"/>
+      <x:c r="F20" s="21"/>
+      <x:c r="G20" s="21"/>
+      <x:c r="H20" s="21"/>
+      <x:c r="I20" s="21"/>
       <x:c r="J20" s="1"/>
       <x:c r="K20" s="1"/>
       <x:c r="L20" s="1"/>
@@ -11354,12 +15616,12 @@
       <x:c r="A21" s="1"/>
       <x:c r="B21" s="1"/>
       <x:c r="C21" s="1"/>
-      <x:c r="D21" s="1"/>
-      <x:c r="E21" s="1"/>
-      <x:c r="F21" s="1"/>
-      <x:c r="G21" s="1"/>
-      <x:c r="H21" s="1"/>
-      <x:c r="I21" s="1"/>
+      <x:c r="D21" s="21"/>
+      <x:c r="E21" s="21"/>
+      <x:c r="F21" s="21"/>
+      <x:c r="G21" s="21"/>
+      <x:c r="H21" s="21"/>
+      <x:c r="I21" s="21"/>
       <x:c r="J21" s="1"/>
       <x:c r="K21" s="1"/>
       <x:c r="L21" s="1"/>
@@ -11368,12 +15630,12 @@
       <x:c r="A22" s="1"/>
       <x:c r="B22" s="1"/>
       <x:c r="C22" s="1"/>
-      <x:c r="D22" s="1"/>
-      <x:c r="E22" s="1"/>
-      <x:c r="F22" s="1"/>
-      <x:c r="G22" s="1"/>
-      <x:c r="H22" s="1"/>
-      <x:c r="I22" s="1"/>
+      <x:c r="D22" s="21"/>
+      <x:c r="E22" s="21"/>
+      <x:c r="F22" s="21"/>
+      <x:c r="G22" s="21"/>
+      <x:c r="H22" s="21"/>
+      <x:c r="I22" s="21"/>
       <x:c r="J22" s="1"/>
       <x:c r="K22" s="1"/>
       <x:c r="L22" s="1"/>
@@ -11382,12 +15644,12 @@
       <x:c r="A23" s="1"/>
       <x:c r="B23" s="1"/>
       <x:c r="C23" s="1"/>
-      <x:c r="D23" s="1"/>
-      <x:c r="E23" s="1"/>
-      <x:c r="F23" s="1"/>
-      <x:c r="G23" s="1"/>
-      <x:c r="H23" s="1"/>
-      <x:c r="I23" s="1"/>
+      <x:c r="D23" s="21"/>
+      <x:c r="E23" s="21"/>
+      <x:c r="F23" s="21"/>
+      <x:c r="G23" s="21"/>
+      <x:c r="H23" s="21"/>
+      <x:c r="I23" s="21"/>
       <x:c r="J23" s="1"/>
       <x:c r="K23" s="1"/>
       <x:c r="L23" s="1"/>
@@ -11396,12 +15658,12 @@
       <x:c r="A24" s="1"/>
       <x:c r="B24" s="1"/>
       <x:c r="C24" s="1"/>
-      <x:c r="D24" s="1"/>
-      <x:c r="E24" s="1"/>
-      <x:c r="F24" s="1"/>
-      <x:c r="G24" s="1"/>
-      <x:c r="H24" s="1"/>
-      <x:c r="I24" s="1"/>
+      <x:c r="D24" s="21"/>
+      <x:c r="E24" s="21"/>
+      <x:c r="F24" s="21"/>
+      <x:c r="G24" s="21"/>
+      <x:c r="H24" s="21"/>
+      <x:c r="I24" s="21"/>
       <x:c r="J24" s="1"/>
       <x:c r="K24" s="1"/>
       <x:c r="L24" s="1"/>
@@ -11410,12 +15672,12 @@
       <x:c r="A25" s="1"/>
       <x:c r="B25" s="1"/>
       <x:c r="C25" s="1"/>
-      <x:c r="D25" s="1"/>
-      <x:c r="E25" s="1"/>
-      <x:c r="F25" s="1"/>
-      <x:c r="G25" s="1"/>
-      <x:c r="H25" s="1"/>
-      <x:c r="I25" s="1"/>
+      <x:c r="D25" s="21"/>
+      <x:c r="E25" s="21"/>
+      <x:c r="F25" s="21"/>
+      <x:c r="G25" s="21"/>
+      <x:c r="H25" s="21"/>
+      <x:c r="I25" s="21"/>
       <x:c r="J25" s="1"/>
       <x:c r="K25" s="1"/>
       <x:c r="L25" s="1"/>
@@ -11424,12 +15686,12 @@
       <x:c r="A26" s="1"/>
       <x:c r="B26" s="1"/>
       <x:c r="C26" s="1"/>
-      <x:c r="D26" s="1"/>
-      <x:c r="E26" s="1"/>
-      <x:c r="F26" s="1"/>
-      <x:c r="G26" s="1"/>
-      <x:c r="H26" s="1"/>
-      <x:c r="I26" s="1"/>
+      <x:c r="D26" s="21"/>
+      <x:c r="E26" s="21"/>
+      <x:c r="F26" s="21"/>
+      <x:c r="G26" s="21"/>
+      <x:c r="H26" s="21"/>
+      <x:c r="I26" s="21"/>
       <x:c r="J26" s="1"/>
       <x:c r="K26" s="1"/>
       <x:c r="L26" s="1"/>
@@ -11438,12 +15700,12 @@
       <x:c r="A27" s="1"/>
       <x:c r="B27" s="1"/>
       <x:c r="C27" s="1"/>
-      <x:c r="D27" s="1"/>
-      <x:c r="E27" s="1"/>
-      <x:c r="F27" s="1"/>
-      <x:c r="G27" s="1"/>
-      <x:c r="H27" s="1"/>
-      <x:c r="I27" s="1"/>
+      <x:c r="D27" s="21"/>
+      <x:c r="E27" s="21"/>
+      <x:c r="F27" s="21"/>
+      <x:c r="G27" s="21"/>
+      <x:c r="H27" s="21"/>
+      <x:c r="I27" s="21"/>
       <x:c r="J27" s="1"/>
       <x:c r="K27" s="1"/>
       <x:c r="L27" s="1"/>
@@ -11452,12 +15714,12 @@
       <x:c r="A28" s="1"/>
       <x:c r="B28" s="1"/>
       <x:c r="C28" s="1"/>
-      <x:c r="D28" s="1"/>
-      <x:c r="E28" s="1"/>
-      <x:c r="F28" s="1"/>
-      <x:c r="G28" s="1"/>
-      <x:c r="H28" s="1"/>
-      <x:c r="I28" s="1"/>
+      <x:c r="D28" s="21"/>
+      <x:c r="E28" s="21"/>
+      <x:c r="F28" s="21"/>
+      <x:c r="G28" s="21"/>
+      <x:c r="H28" s="21"/>
+      <x:c r="I28" s="21"/>
       <x:c r="J28" s="1"/>
       <x:c r="K28" s="1"/>
       <x:c r="L28" s="1"/>
@@ -11466,12 +15728,12 @@
       <x:c r="A29" s="1"/>
       <x:c r="B29" s="1"/>
       <x:c r="C29" s="1"/>
-      <x:c r="D29" s="1"/>
-      <x:c r="E29" s="1"/>
-      <x:c r="F29" s="1"/>
-      <x:c r="G29" s="1"/>
-      <x:c r="H29" s="1"/>
-      <x:c r="I29" s="1"/>
+      <x:c r="D29" s="21"/>
+      <x:c r="E29" s="21"/>
+      <x:c r="F29" s="21"/>
+      <x:c r="G29" s="21"/>
+      <x:c r="H29" s="21"/>
+      <x:c r="I29" s="21"/>
       <x:c r="J29" s="1"/>
       <x:c r="K29" s="1"/>
       <x:c r="L29" s="1"/>
@@ -11480,12 +15742,12 @@
       <x:c r="A30" s="1"/>
       <x:c r="B30" s="1"/>
       <x:c r="C30" s="1"/>
-      <x:c r="D30" s="1"/>
-      <x:c r="E30" s="1"/>
-      <x:c r="F30" s="1"/>
-      <x:c r="G30" s="1"/>
-      <x:c r="H30" s="1"/>
-      <x:c r="I30" s="1"/>
+      <x:c r="D30" s="21"/>
+      <x:c r="E30" s="21"/>
+      <x:c r="F30" s="21"/>
+      <x:c r="G30" s="21"/>
+      <x:c r="H30" s="21"/>
+      <x:c r="I30" s="21"/>
       <x:c r="J30" s="1"/>
       <x:c r="K30" s="1"/>
       <x:c r="L30" s="1"/>
@@ -11494,12 +15756,12 @@
       <x:c r="A31" s="1"/>
       <x:c r="B31" s="1"/>
       <x:c r="C31" s="1"/>
-      <x:c r="D31" s="1"/>
-      <x:c r="E31" s="1"/>
-      <x:c r="F31" s="1"/>
-      <x:c r="G31" s="1"/>
-      <x:c r="H31" s="1"/>
-      <x:c r="I31" s="1"/>
+      <x:c r="D31" s="21"/>
+      <x:c r="E31" s="21"/>
+      <x:c r="F31" s="21"/>
+      <x:c r="G31" s="21"/>
+      <x:c r="H31" s="21"/>
+      <x:c r="I31" s="21"/>
       <x:c r="J31" s="1"/>
       <x:c r="K31" s="1"/>
       <x:c r="L31" s="1"/>
@@ -11508,12 +15770,12 @@
       <x:c r="A32" s="1"/>
       <x:c r="B32" s="1"/>
       <x:c r="C32" s="1"/>
-      <x:c r="D32" s="1"/>
-      <x:c r="E32" s="1"/>
-      <x:c r="F32" s="1"/>
-      <x:c r="G32" s="1"/>
-      <x:c r="H32" s="1"/>
-      <x:c r="I32" s="1"/>
+      <x:c r="D32" s="21"/>
+      <x:c r="E32" s="21"/>
+      <x:c r="F32" s="21"/>
+      <x:c r="G32" s="21"/>
+      <x:c r="H32" s="21"/>
+      <x:c r="I32" s="21"/>
       <x:c r="J32" s="1"/>
       <x:c r="K32" s="1"/>
       <x:c r="L32" s="1"/>
@@ -11522,12 +15784,12 @@
       <x:c r="A33" s="1"/>
       <x:c r="B33" s="1"/>
       <x:c r="C33" s="1"/>
-      <x:c r="D33" s="1"/>
-      <x:c r="E33" s="1"/>
-      <x:c r="F33" s="1"/>
-      <x:c r="G33" s="1"/>
-      <x:c r="H33" s="1"/>
-      <x:c r="I33" s="1"/>
+      <x:c r="D33" s="21"/>
+      <x:c r="E33" s="21"/>
+      <x:c r="F33" s="21"/>
+      <x:c r="G33" s="21"/>
+      <x:c r="H33" s="21"/>
+      <x:c r="I33" s="21"/>
       <x:c r="J33" s="1"/>
       <x:c r="K33" s="1"/>
       <x:c r="L33" s="1"/>
@@ -11536,12 +15798,12 @@
       <x:c r="A34" s="1"/>
       <x:c r="B34" s="1"/>
       <x:c r="C34" s="1"/>
-      <x:c r="D34" s="1"/>
-      <x:c r="E34" s="1"/>
-      <x:c r="F34" s="1"/>
-      <x:c r="G34" s="1"/>
-      <x:c r="H34" s="1"/>
-      <x:c r="I34" s="1"/>
+      <x:c r="D34" s="21"/>
+      <x:c r="E34" s="21"/>
+      <x:c r="F34" s="21"/>
+      <x:c r="G34" s="21"/>
+      <x:c r="H34" s="21"/>
+      <x:c r="I34" s="21"/>
       <x:c r="J34" s="1"/>
       <x:c r="K34" s="1"/>
       <x:c r="L34" s="1"/>
@@ -11550,12 +15812,12 @@
       <x:c r="A35" s="1"/>
       <x:c r="B35" s="1"/>
       <x:c r="C35" s="1"/>
-      <x:c r="D35" s="1"/>
-      <x:c r="E35" s="1"/>
-      <x:c r="F35" s="1"/>
-      <x:c r="G35" s="1"/>
-      <x:c r="H35" s="1"/>
-      <x:c r="I35" s="1"/>
+      <x:c r="D35" s="21"/>
+      <x:c r="E35" s="21"/>
+      <x:c r="F35" s="21"/>
+      <x:c r="G35" s="21"/>
+      <x:c r="H35" s="21"/>
+      <x:c r="I35" s="21"/>
       <x:c r="J35" s="1"/>
       <x:c r="K35" s="1"/>
       <x:c r="L35" s="1"/>
@@ -11564,12 +15826,12 @@
       <x:c r="A36" s="1"/>
       <x:c r="B36" s="1"/>
       <x:c r="C36" s="1"/>
-      <x:c r="D36" s="1"/>
-      <x:c r="E36" s="1"/>
-      <x:c r="F36" s="1"/>
-      <x:c r="G36" s="1"/>
-      <x:c r="H36" s="1"/>
-      <x:c r="I36" s="1"/>
+      <x:c r="D36" s="21"/>
+      <x:c r="E36" s="21"/>
+      <x:c r="F36" s="21"/>
+      <x:c r="G36" s="21"/>
+      <x:c r="H36" s="21"/>
+      <x:c r="I36" s="21"/>
       <x:c r="J36" s="1"/>
       <x:c r="K36" s="1"/>
       <x:c r="L36" s="1"/>
@@ -11578,12 +15840,12 @@
       <x:c r="A37" s="1"/>
       <x:c r="B37" s="1"/>
       <x:c r="C37" s="1"/>
-      <x:c r="D37" s="1"/>
-      <x:c r="E37" s="1"/>
-      <x:c r="F37" s="1"/>
-      <x:c r="G37" s="1"/>
-      <x:c r="H37" s="1"/>
-      <x:c r="I37" s="1"/>
+      <x:c r="D37" s="21"/>
+      <x:c r="E37" s="21"/>
+      <x:c r="F37" s="21"/>
+      <x:c r="G37" s="21"/>
+      <x:c r="H37" s="21"/>
+      <x:c r="I37" s="21"/>
       <x:c r="J37" s="1"/>
       <x:c r="K37" s="1"/>
       <x:c r="L37" s="1"/>
@@ -11592,12 +15854,12 @@
       <x:c r="A38" s="1"/>
       <x:c r="B38" s="1"/>
       <x:c r="C38" s="1"/>
-      <x:c r="D38" s="1"/>
-      <x:c r="E38" s="1"/>
-      <x:c r="F38" s="1"/>
-      <x:c r="G38" s="1"/>
-      <x:c r="H38" s="1"/>
-      <x:c r="I38" s="1"/>
+      <x:c r="D38" s="21"/>
+      <x:c r="E38" s="21"/>
+      <x:c r="F38" s="21"/>
+      <x:c r="G38" s="21"/>
+      <x:c r="H38" s="21"/>
+      <x:c r="I38" s="21"/>
       <x:c r="J38" s="1"/>
       <x:c r="K38" s="1"/>
       <x:c r="L38" s="1"/>
@@ -11606,12 +15868,12 @@
       <x:c r="A39" s="1"/>
       <x:c r="B39" s="1"/>
       <x:c r="C39" s="1"/>
-      <x:c r="D39" s="1"/>
-      <x:c r="E39" s="1"/>
-      <x:c r="F39" s="1"/>
-      <x:c r="G39" s="1"/>
-      <x:c r="H39" s="1"/>
-      <x:c r="I39" s="1"/>
+      <x:c r="D39" s="21"/>
+      <x:c r="E39" s="21"/>
+      <x:c r="F39" s="21"/>
+      <x:c r="G39" s="21"/>
+      <x:c r="H39" s="21"/>
+      <x:c r="I39" s="21"/>
       <x:c r="J39" s="1"/>
       <x:c r="K39" s="1"/>
       <x:c r="L39" s="1"/>
@@ -11620,12 +15882,12 @@
       <x:c r="A40" s="1"/>
       <x:c r="B40" s="1"/>
       <x:c r="C40" s="1"/>
-      <x:c r="D40" s="1"/>
-      <x:c r="E40" s="1"/>
-      <x:c r="F40" s="1"/>
-      <x:c r="G40" s="1"/>
-      <x:c r="H40" s="1"/>
-      <x:c r="I40" s="1"/>
+      <x:c r="D40" s="21"/>
+      <x:c r="E40" s="21"/>
+      <x:c r="F40" s="21"/>
+      <x:c r="G40" s="21"/>
+      <x:c r="H40" s="21"/>
+      <x:c r="I40" s="21"/>
       <x:c r="J40" s="1"/>
       <x:c r="K40" s="1"/>
       <x:c r="L40" s="1"/>
@@ -11634,12 +15896,12 @@
       <x:c r="A41" s="1"/>
       <x:c r="B41" s="1"/>
       <x:c r="C41" s="1"/>
-      <x:c r="D41" s="1"/>
-      <x:c r="E41" s="1"/>
-      <x:c r="F41" s="1"/>
-      <x:c r="G41" s="1"/>
-      <x:c r="H41" s="1"/>
-      <x:c r="I41" s="1"/>
+      <x:c r="D41" s="21"/>
+      <x:c r="E41" s="21"/>
+      <x:c r="F41" s="21"/>
+      <x:c r="G41" s="21"/>
+      <x:c r="H41" s="21"/>
+      <x:c r="I41" s="21"/>
       <x:c r="J41" s="1"/>
       <x:c r="K41" s="1"/>
       <x:c r="L41" s="1"/>
@@ -11648,12 +15910,12 @@
       <x:c r="A42" s="1"/>
       <x:c r="B42" s="1"/>
       <x:c r="C42" s="1"/>
-      <x:c r="D42" s="1"/>
-      <x:c r="E42" s="1"/>
-      <x:c r="F42" s="1"/>
-      <x:c r="G42" s="1"/>
-      <x:c r="H42" s="1"/>
-      <x:c r="I42" s="1"/>
+      <x:c r="D42" s="21"/>
+      <x:c r="E42" s="21"/>
+      <x:c r="F42" s="21"/>
+      <x:c r="G42" s="21"/>
+      <x:c r="H42" s="21"/>
+      <x:c r="I42" s="21"/>
       <x:c r="J42" s="1"/>
       <x:c r="K42" s="1"/>
       <x:c r="L42" s="1"/>
@@ -11662,12 +15924,12 @@
       <x:c r="A43" s="1"/>
       <x:c r="B43" s="1"/>
       <x:c r="C43" s="1"/>
-      <x:c r="D43" s="1"/>
-      <x:c r="E43" s="1"/>
-      <x:c r="F43" s="1"/>
-      <x:c r="G43" s="1"/>
-      <x:c r="H43" s="1"/>
-      <x:c r="I43" s="1"/>
+      <x:c r="D43" s="21"/>
+      <x:c r="E43" s="21"/>
+      <x:c r="F43" s="21"/>
+      <x:c r="G43" s="21"/>
+      <x:c r="H43" s="21"/>
+      <x:c r="I43" s="21"/>
       <x:c r="J43" s="1"/>
       <x:c r="K43" s="1"/>
       <x:c r="L43" s="1"/>
@@ -11676,12 +15938,12 @@
       <x:c r="A44" s="1"/>
       <x:c r="B44" s="1"/>
       <x:c r="C44" s="1"/>
-      <x:c r="D44" s="1"/>
-      <x:c r="E44" s="1"/>
-      <x:c r="F44" s="1"/>
-      <x:c r="G44" s="1"/>
-      <x:c r="H44" s="1"/>
-      <x:c r="I44" s="1"/>
+      <x:c r="D44" s="21"/>
+      <x:c r="E44" s="21"/>
+      <x:c r="F44" s="21"/>
+      <x:c r="G44" s="21"/>
+      <x:c r="H44" s="21"/>
+      <x:c r="I44" s="21"/>
       <x:c r="J44" s="1"/>
       <x:c r="K44" s="1"/>
       <x:c r="L44" s="1"/>
@@ -11690,12 +15952,12 @@
       <x:c r="A45" s="1"/>
       <x:c r="B45" s="1"/>
       <x:c r="C45" s="1"/>
-      <x:c r="D45" s="1"/>
-      <x:c r="E45" s="1"/>
-      <x:c r="F45" s="1"/>
-      <x:c r="G45" s="1"/>
-      <x:c r="H45" s="1"/>
-      <x:c r="I45" s="1"/>
+      <x:c r="D45" s="21"/>
+      <x:c r="E45" s="21"/>
+      <x:c r="F45" s="21"/>
+      <x:c r="G45" s="21"/>
+      <x:c r="H45" s="21"/>
+      <x:c r="I45" s="21"/>
       <x:c r="J45" s="1"/>
       <x:c r="K45" s="1"/>
       <x:c r="L45" s="1"/>
@@ -11704,12 +15966,12 @@
       <x:c r="A46" s="1"/>
       <x:c r="B46" s="1"/>
       <x:c r="C46" s="1"/>
-      <x:c r="D46" s="1"/>
-      <x:c r="E46" s="1"/>
-      <x:c r="F46" s="1"/>
-      <x:c r="G46" s="1"/>
-      <x:c r="H46" s="1"/>
-      <x:c r="I46" s="1"/>
+      <x:c r="D46" s="21"/>
+      <x:c r="E46" s="21"/>
+      <x:c r="F46" s="21"/>
+      <x:c r="G46" s="21"/>
+      <x:c r="H46" s="21"/>
+      <x:c r="I46" s="21"/>
       <x:c r="J46" s="1"/>
       <x:c r="K46" s="1"/>
       <x:c r="L46" s="1"/>
@@ -11718,12 +15980,12 @@
       <x:c r="A47" s="1"/>
       <x:c r="B47" s="1"/>
       <x:c r="C47" s="1"/>
-      <x:c r="D47" s="1"/>
-      <x:c r="E47" s="1"/>
-      <x:c r="F47" s="1"/>
-      <x:c r="G47" s="1"/>
-      <x:c r="H47" s="1"/>
-      <x:c r="I47" s="1"/>
+      <x:c r="D47" s="21"/>
+      <x:c r="E47" s="21"/>
+      <x:c r="F47" s="21"/>
+      <x:c r="G47" s="21"/>
+      <x:c r="H47" s="21"/>
+      <x:c r="I47" s="21"/>
       <x:c r="J47" s="1"/>
       <x:c r="K47" s="1"/>
       <x:c r="L47" s="1"/>
@@ -11732,12 +15994,12 @@
       <x:c r="A48" s="1"/>
       <x:c r="B48" s="1"/>
       <x:c r="C48" s="1"/>
-      <x:c r="D48" s="1"/>
-      <x:c r="E48" s="1"/>
-      <x:c r="F48" s="1"/>
-      <x:c r="G48" s="1"/>
-      <x:c r="H48" s="1"/>
-      <x:c r="I48" s="1"/>
+      <x:c r="D48" s="21"/>
+      <x:c r="E48" s="21"/>
+      <x:c r="F48" s="21"/>
+      <x:c r="G48" s="21"/>
+      <x:c r="H48" s="21"/>
+      <x:c r="I48" s="21"/>
       <x:c r="J48" s="1"/>
       <x:c r="K48" s="1"/>
       <x:c r="L48" s="1"/>
@@ -11746,12 +16008,12 @@
       <x:c r="A49" s="1"/>
       <x:c r="B49" s="1"/>
       <x:c r="C49" s="1"/>
-      <x:c r="D49" s="1"/>
-      <x:c r="E49" s="1"/>
-      <x:c r="F49" s="1"/>
-      <x:c r="G49" s="1"/>
-      <x:c r="H49" s="1"/>
-      <x:c r="I49" s="1"/>
+      <x:c r="D49" s="21"/>
+      <x:c r="E49" s="21"/>
+      <x:c r="F49" s="21"/>
+      <x:c r="G49" s="21"/>
+      <x:c r="H49" s="21"/>
+      <x:c r="I49" s="21"/>
       <x:c r="J49" s="1"/>
       <x:c r="K49" s="1"/>
       <x:c r="L49" s="1"/>
@@ -11760,12 +16022,12 @@
       <x:c r="A50" s="1"/>
       <x:c r="B50" s="1"/>
       <x:c r="C50" s="1"/>
-      <x:c r="D50" s="1"/>
-      <x:c r="E50" s="1"/>
-      <x:c r="F50" s="1"/>
-      <x:c r="G50" s="1"/>
-      <x:c r="H50" s="1"/>
-      <x:c r="I50" s="1"/>
+      <x:c r="D50" s="21"/>
+      <x:c r="E50" s="21"/>
+      <x:c r="F50" s="21"/>
+      <x:c r="G50" s="21"/>
+      <x:c r="H50" s="21"/>
+      <x:c r="I50" s="21"/>
       <x:c r="J50" s="1"/>
       <x:c r="K50" s="1"/>
       <x:c r="L50" s="1"/>
@@ -11774,12 +16036,12 @@
       <x:c r="A51" s="1"/>
       <x:c r="B51" s="1"/>
       <x:c r="C51" s="1"/>
-      <x:c r="D51" s="1"/>
-      <x:c r="E51" s="1"/>
-      <x:c r="F51" s="1"/>
-      <x:c r="G51" s="1"/>
-      <x:c r="H51" s="1"/>
-      <x:c r="I51" s="1"/>
+      <x:c r="D51" s="21"/>
+      <x:c r="E51" s="21"/>
+      <x:c r="F51" s="21"/>
+      <x:c r="G51" s="21"/>
+      <x:c r="H51" s="21"/>
+      <x:c r="I51" s="21"/>
       <x:c r="J51" s="1"/>
       <x:c r="K51" s="1"/>
       <x:c r="L51" s="1"/>
@@ -11788,12 +16050,12 @@
       <x:c r="A52" s="1"/>
       <x:c r="B52" s="1"/>
       <x:c r="C52" s="1"/>
-      <x:c r="D52" s="1"/>
-      <x:c r="E52" s="1"/>
-      <x:c r="F52" s="1"/>
-      <x:c r="G52" s="1"/>
-      <x:c r="H52" s="1"/>
-      <x:c r="I52" s="1"/>
+      <x:c r="D52" s="21"/>
+      <x:c r="E52" s="21"/>
+      <x:c r="F52" s="21"/>
+      <x:c r="G52" s="21"/>
+      <x:c r="H52" s="21"/>
+      <x:c r="I52" s="21"/>
       <x:c r="J52" s="1"/>
       <x:c r="K52" s="1"/>
       <x:c r="L52" s="1"/>
@@ -11802,12 +16064,12 @@
       <x:c r="A53" s="1"/>
       <x:c r="B53" s="1"/>
       <x:c r="C53" s="1"/>
-      <x:c r="D53" s="1"/>
-      <x:c r="E53" s="1"/>
-      <x:c r="F53" s="1"/>
-      <x:c r="G53" s="1"/>
-      <x:c r="H53" s="1"/>
-      <x:c r="I53" s="1"/>
+      <x:c r="D53" s="21"/>
+      <x:c r="E53" s="21"/>
+      <x:c r="F53" s="21"/>
+      <x:c r="G53" s="21"/>
+      <x:c r="H53" s="21"/>
+      <x:c r="I53" s="21"/>
       <x:c r="J53" s="1"/>
       <x:c r="K53" s="1"/>
       <x:c r="L53" s="1"/>
@@ -11816,12 +16078,12 @@
       <x:c r="A54" s="1"/>
       <x:c r="B54" s="1"/>
       <x:c r="C54" s="1"/>
-      <x:c r="D54" s="1"/>
-      <x:c r="E54" s="1"/>
-      <x:c r="F54" s="1"/>
-      <x:c r="G54" s="1"/>
-      <x:c r="H54" s="1"/>
-      <x:c r="I54" s="1"/>
+      <x:c r="D54" s="21"/>
+      <x:c r="E54" s="21"/>
+      <x:c r="F54" s="21"/>
+      <x:c r="G54" s="21"/>
+      <x:c r="H54" s="21"/>
+      <x:c r="I54" s="21"/>
       <x:c r="J54" s="1"/>
       <x:c r="K54" s="1"/>
       <x:c r="L54" s="1"/>
@@ -11830,12 +16092,12 @@
       <x:c r="A55" s="1"/>
       <x:c r="B55" s="1"/>
       <x:c r="C55" s="1"/>
-      <x:c r="D55" s="1"/>
-      <x:c r="E55" s="1"/>
-      <x:c r="F55" s="1"/>
-      <x:c r="G55" s="1"/>
-      <x:c r="H55" s="1"/>
-      <x:c r="I55" s="1"/>
+      <x:c r="D55" s="21"/>
+      <x:c r="E55" s="21"/>
+      <x:c r="F55" s="21"/>
+      <x:c r="G55" s="21"/>
+      <x:c r="H55" s="21"/>
+      <x:c r="I55" s="21"/>
       <x:c r="J55" s="1"/>
       <x:c r="K55" s="1"/>
       <x:c r="L55" s="1"/>
@@ -11981,11 +16243,9 @@
       <x:c r="L65" s="1"/>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="D7:D9">
-    <x:cfRule type="expression" dxfId="0" priority="1">
-      <x:formula>ABS(D7)&gt;E7</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
+  <x:mergeCells>
+    <x:mergeCell ref="D4:F4"/>
+  </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
 </file>